--- a/sp500 stocks.xlsx
+++ b/sp500 stocks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/monikakaczorowska/Desktop/finance_with_big_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA1C8BAC-3498-194E-87F0-5A43AEA194DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5152E00-E330-5149-93FD-88F41148246C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="760" windowWidth="28040" windowHeight="16580" xr2:uid="{31327611-E336-ED4D-9BE9-46A5E2D7D064}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="504">
   <si>
     <t>A</t>
   </si>
@@ -1545,6 +1545,9 @@
   </si>
   <si>
     <t>ZTS</t>
+  </si>
+  <si>
+    <t>Stock</t>
   </si>
 </sst>
 </file>
@@ -1927,3029 +1930,3034 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A952E22-5C72-6E4D-BDF8-1E6589CB1635}">
-  <dimension ref="A1:A503"/>
+  <dimension ref="A1:A504"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A195" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A196" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A200" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="203" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="204" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="205" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A205" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="206" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="207" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="208" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="210" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="211" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="212" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A212" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="213" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A213" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A215" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A216" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A217" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A218" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="219" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="220" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="221" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A221" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="222" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A222" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="223" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A225" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="226" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A226" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="227" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A227" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="228" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A228" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A230" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A231" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A232" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A233" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A234" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A236" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A237" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A238" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A239" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A240" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A241" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A242" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A243" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A245" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A246" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="247" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A247" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="248" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A248" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A249" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A250" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="251" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A251" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="252" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A252" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="253" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A253" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="254" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A254" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="255" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A255" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="256" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A256" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="257" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A257" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="258" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A258" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A259" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A260" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A261" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A262" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A263" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A264" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="265" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A265" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A266" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="267" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A267" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="268" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A268" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="269" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A269" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="270" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A270" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="271" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A271" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="272" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A272" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="273" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A273" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="274" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A274" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="275" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A275" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="276" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A276" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="277" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A277" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="278" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A278" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="279" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A279" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="280" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A280" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="281" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A281" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="282" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A282" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="283" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A283" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="284" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A284" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="285" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A285" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="286" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A286" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="287" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A287" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="288" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A288" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="289" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A289" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="290" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A290" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="291" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A291" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="292" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A292" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="293" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A293" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="294" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A294" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="295" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A295" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="296" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A296" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="297" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A297" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="298" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A298" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="299" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A299" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="300" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A300" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="301" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A301" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="302" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A302" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="303" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A303" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="304" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A304" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="305" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A305" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="306" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A306" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="307" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A307" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="308" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A308" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="309" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A309" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="310" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A310" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="311" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A311" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="312" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A312" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="313" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A313" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="314" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A314" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="315" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A315" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="316" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A316" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="317" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A317" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="318" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A318" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="319" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A319" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="320" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A320" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="321" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A321" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="322" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A322" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="323" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A323" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="324" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A324" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="325" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A325" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="326" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A326" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="327" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A327" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="328" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A328" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="329" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A329" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="330" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A330" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="331" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A331" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="332" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A332" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="333" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A333" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="334" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A334" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="335" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A335" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="336" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A336" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="337" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A337" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="338" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A338" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="339" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A339" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="340" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A340" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="341" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A341" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="342" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A342" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="343" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A343" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="344" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A344" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="345" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A345" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="346" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A346" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="347" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A347" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="348" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A348" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="349" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A349" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="350" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A350" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="351" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A351" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="352" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A352" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="353" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A353" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="354" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A354" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="355" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A355" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="356" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A356" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="357" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A357" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="358" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A358" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="359" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A359" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="360" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A360" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="361" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A361" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="362" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A362" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="363" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A363" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="364" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A364" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="365" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A365" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="366" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A366" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="367" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A367" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="368" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A368" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="369" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A369" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="370" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A370" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="371" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A371" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="372" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A372" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="373" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A373" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="374" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A374" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="375" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A375" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="376" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A376" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="377" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A377" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="378" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A378" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="379" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A379" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="380" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A380" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="381" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A381" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="382" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A382" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="383" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A383" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="384" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A384" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="385" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A385" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="386" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A386" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="387" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A387" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="388" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A388" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="389" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A389" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="390" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A390" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="391" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A391" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="392" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A392" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="393" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A393" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="394" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A394" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="395" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A395" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="396" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A396" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="397" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A397" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="398" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A398" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="399" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A399" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="400" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A400" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="401" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A401" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="402" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A402" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="403" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A403" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="404" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A404" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="405" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A405" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="406" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A406" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="407" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A407" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="408" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A408" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="409" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A409" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="410" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A410" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="411" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A411" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="412" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A412" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="413" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A413" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="414" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A414" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="415" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A415" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="416" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A416" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="417" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A417" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="418" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A418" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="419" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A419" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="420" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A420" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="421" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A421" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="422" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A422" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="423" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A423" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="424" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A424" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="425" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A425" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="426" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A426" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="427" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A427" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="428" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A428" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="429" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A429" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="430" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A430" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="431" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A431" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="432" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A432" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="433" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A433" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="434" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A434" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="435" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A435" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="436" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A436" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="437" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A437" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="438" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A438" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="439" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A439" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="440" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A440" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="441" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A441" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="442" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A442" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="443" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A443" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="444" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A444" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="445" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A445" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="446" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A446" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="447" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A447" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="448" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A448" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="449" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A449" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="450" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A450" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="451" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A451" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="452" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A452" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="453" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A453" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="454" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A454" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="455" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A455" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="456" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A456" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="457" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A457" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="458" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A458" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="459" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A459" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="460" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A460" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="461" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A461" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="462" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A462" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="463" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A463" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="464" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A464" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="465" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A465" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="466" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A466" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="467" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A467" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="468" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A468" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="469" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A469" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="470" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A470" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="471" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A471" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="472" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A472" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="473" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A473" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="474" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A474" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="475" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A475" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="476" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A476" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="477" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A477" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="478" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A478" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="479" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A479" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="480" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A480" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="481" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A481" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="482" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A482" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="483" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A483" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="484" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A484" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="485" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A485" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="486" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A486" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="487" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A487" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="488" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A488" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="489" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A489" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="490" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A490" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="491" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A491" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="492" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A492" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="493" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A493" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="494" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A494" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="495" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A495" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="496" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A496" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="497" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A497" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="498" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A498" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="499" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A499" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="500" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A500" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="501" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A501" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="502" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A502" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="503" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A503" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="504" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A504" s="1" t="s">
         <v>502</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1" display="https://www.nyse.com/quote/XNYS:A" xr:uid="{B677E7E2-D9A0-484D-AEBE-207B88E9E360}"/>
-    <hyperlink ref="A2" r:id="rId2" display="https://www.nasdaq.com/market-activity/stocks/aapl" xr:uid="{7DE6A81F-4C0C-2442-90EE-B0DC994F65DC}"/>
-    <hyperlink ref="A3" r:id="rId3" display="https://www.nyse.com/quote/XNYS:ABBV" xr:uid="{707B21A3-7AC5-F844-8283-80373766D5DD}"/>
-    <hyperlink ref="A4" r:id="rId4" display="https://www.nasdaq.com/market-activity/stocks/abnb" xr:uid="{D0CE58CB-6CE5-7F41-93F9-C2A93FE21B5D}"/>
-    <hyperlink ref="A5" r:id="rId5" display="https://www.nyse.com/quote/XNYS:ABT" xr:uid="{FEF90C77-2BFC-C349-BCBE-6FF80C8C38EE}"/>
-    <hyperlink ref="A6" r:id="rId6" display="https://www.nasdaq.com/market-activity/stocks/acgl" xr:uid="{86EB05E8-6F5A-4B4A-88AB-8736D053F62F}"/>
-    <hyperlink ref="A7" r:id="rId7" display="https://www.nyse.com/quote/XNYS:ACN" xr:uid="{206D1A09-61A0-FE4E-BE76-3950E0FFD219}"/>
-    <hyperlink ref="A8" r:id="rId8" display="https://www.nasdaq.com/market-activity/stocks/adbe" xr:uid="{D8F512C1-9031-D34F-A396-636D6EBC2CF4}"/>
-    <hyperlink ref="A9" r:id="rId9" display="https://www.nasdaq.com/market-activity/stocks/adi" xr:uid="{D9823A54-00AC-8F43-8405-494BB7E9B44E}"/>
-    <hyperlink ref="A10" r:id="rId10" display="https://www.nyse.com/quote/XNYS:ADM" xr:uid="{8DC53D66-2713-8B49-B853-63A8FCCA9126}"/>
-    <hyperlink ref="A11" r:id="rId11" display="https://www.nasdaq.com/market-activity/stocks/adp" xr:uid="{91EBE334-83F2-BA47-A1C7-BAF01F975088}"/>
-    <hyperlink ref="A12" r:id="rId12" display="https://www.nasdaq.com/market-activity/stocks/adsk" xr:uid="{D8C9118C-21E3-4249-AD03-95CE80DD109B}"/>
-    <hyperlink ref="A13" r:id="rId13" display="https://www.nyse.com/quote/XNYS:AEE" xr:uid="{AAA5D011-8033-AA4D-B7AC-3993C94805BB}"/>
-    <hyperlink ref="A14" r:id="rId14" display="https://www.nasdaq.com/market-activity/stocks/aep" xr:uid="{F6E4922F-DB65-4340-99EC-B16C5E0C4A62}"/>
-    <hyperlink ref="A15" r:id="rId15" display="https://www.nyse.com/quote/XNYS:AES" xr:uid="{2630E663-8BA5-D341-B229-275D211D791F}"/>
-    <hyperlink ref="A16" r:id="rId16" display="https://www.nyse.com/quote/XNYS:AFL" xr:uid="{878DBBC2-9931-DF46-AB3D-A33E271012A2}"/>
-    <hyperlink ref="A17" r:id="rId17" display="https://www.nyse.com/quote/XNYS:AIG" xr:uid="{35A39E0B-AD34-A743-86F3-38EE69C6C499}"/>
-    <hyperlink ref="A18" r:id="rId18" display="https://www.nyse.com/quote/XNYS:AIZ" xr:uid="{918BA76D-75FF-D94E-A2B9-B64D2F696416}"/>
-    <hyperlink ref="A19" r:id="rId19" display="https://www.nyse.com/quote/XNYS:AJG" xr:uid="{127B7D18-5DAE-C744-B072-03E0AEB25E5A}"/>
-    <hyperlink ref="A20" r:id="rId20" display="https://www.nasdaq.com/market-activity/stocks/akam" xr:uid="{959EDF9B-5B96-DB41-9809-5DFD91DC9105}"/>
-    <hyperlink ref="A21" r:id="rId21" display="https://www.nyse.com/quote/XNYS:ALB" xr:uid="{2E54EF01-4A06-4A4B-B67B-C5D76C6C1807}"/>
-    <hyperlink ref="A22" r:id="rId22" display="https://www.nasdaq.com/market-activity/stocks/algn" xr:uid="{5802A803-5C11-804B-9377-9884F56CB365}"/>
-    <hyperlink ref="A23" r:id="rId23" display="https://www.nyse.com/quote/XNYS:ALL" xr:uid="{B4FD8F12-052A-354C-9461-040431CB289A}"/>
-    <hyperlink ref="A24" r:id="rId24" display="https://www.nyse.com/quote/XNYS:ALLE" xr:uid="{A977F9BC-11F3-9141-B044-C5040F14152D}"/>
-    <hyperlink ref="A25" r:id="rId25" display="https://www.nasdaq.com/market-activity/stocks/amat" xr:uid="{7B29B435-FC6C-7448-9ADB-2ED6F4F7CC93}"/>
-    <hyperlink ref="A26" r:id="rId26" display="https://www.nyse.com/quote/XNYS:AMCR" xr:uid="{5E0C4903-FD03-9149-A61A-4E3BEC1113C1}"/>
-    <hyperlink ref="A27" r:id="rId27" display="https://www.nasdaq.com/market-activity/stocks/amd" xr:uid="{E8D094F5-BCDF-204F-B52C-A2B1DB34373A}"/>
-    <hyperlink ref="A28" r:id="rId28" display="https://www.nyse.com/quote/XNYS:AME" xr:uid="{9178BCA7-072F-A04B-9765-FDB1E68CFE76}"/>
-    <hyperlink ref="A29" r:id="rId29" display="https://www.nasdaq.com/market-activity/stocks/amgn" xr:uid="{5FB436CA-6101-CB4F-9297-17A9E7FA04CA}"/>
-    <hyperlink ref="A30" r:id="rId30" display="https://www.nyse.com/quote/XNYS:AMP" xr:uid="{A0E0B85B-0761-874C-8164-3E63E14B4D7E}"/>
-    <hyperlink ref="A31" r:id="rId31" display="https://www.nyse.com/quote/XNYS:AMT" xr:uid="{207965AF-2F4D-4F41-9382-404B67F58EA5}"/>
-    <hyperlink ref="A32" r:id="rId32" display="https://www.nasdaq.com/market-activity/stocks/amzn" xr:uid="{C0C3A928-E8CD-1344-9E9C-5F58FC88B2A6}"/>
-    <hyperlink ref="A33" r:id="rId33" display="https://www.nyse.com/quote/XNYS:ANET" xr:uid="{447B8518-A380-7645-81DE-D503DFE6D626}"/>
-    <hyperlink ref="A34" r:id="rId34" display="https://www.nyse.com/quote/XNYS:AON" xr:uid="{56C12CB8-3952-0240-97DF-FF77245D0D07}"/>
-    <hyperlink ref="A35" r:id="rId35" display="https://www.nyse.com/quote/XNYS:AOS" xr:uid="{8D913B35-64EE-4745-9861-E87D637F74B2}"/>
-    <hyperlink ref="A36" r:id="rId36" display="https://www.nasdaq.com/market-activity/stocks/apa" xr:uid="{2A534FB8-27D8-3D43-9EDC-8202B95E29FC}"/>
-    <hyperlink ref="A37" r:id="rId37" display="https://www.nyse.com/quote/XNYS:APD" xr:uid="{F27E7B99-FD07-4347-AED3-C2F60580A039}"/>
-    <hyperlink ref="A38" r:id="rId38" display="https://www.nyse.com/quote/XNYS:APH" xr:uid="{AFCD0056-A16B-8748-819C-8B811AE927EA}"/>
-    <hyperlink ref="A39" r:id="rId39" display="https://www.nyse.com/quote/XNYS:APO" xr:uid="{8EA4193A-0E89-4E49-88C3-00187C8B9B4A}"/>
-    <hyperlink ref="A40" r:id="rId40" display="https://www.nasdaq.com/market-activity/stocks/app" xr:uid="{7DA33E09-14F5-094B-9BC0-8B01746DA9D5}"/>
-    <hyperlink ref="A41" r:id="rId41" display="https://www.nyse.com/quote/XNYS:APTV" xr:uid="{9F123F4D-D4F0-E94A-A025-887D01818887}"/>
-    <hyperlink ref="A42" r:id="rId42" display="https://www.nyse.com/quote/XNYS:ARE" xr:uid="{7BF28F6A-FEE8-9D4B-AEB7-58C25CAF2C41}"/>
-    <hyperlink ref="A43" r:id="rId43" display="https://www.nyse.com/quote/XNYS:ATO" xr:uid="{5E3A94FB-9A80-9641-870E-55CD3B11C526}"/>
-    <hyperlink ref="A44" r:id="rId44" display="https://www.nyse.com/quote/XNYS:AVB" xr:uid="{72CC2DA4-C76E-B049-98BA-6B1CD0EF9E57}"/>
-    <hyperlink ref="A45" r:id="rId45" display="https://www.nasdaq.com/market-activity/stocks/avgo" xr:uid="{ABB2F68A-74D6-C44F-9E6D-D73FB4148AC2}"/>
-    <hyperlink ref="A46" r:id="rId46" display="https://www.nyse.com/quote/XNYS:AVY" xr:uid="{B3AC83C9-D20E-974A-AE30-404704C3BE4A}"/>
-    <hyperlink ref="A47" r:id="rId47" display="https://www.nyse.com/quote/XNYS:AWK" xr:uid="{D572A379-C1CC-7E4A-883E-AA0E3FA1126A}"/>
-    <hyperlink ref="A48" r:id="rId48" display="https://www.nasdaq.com/market-activity/stocks/axon" xr:uid="{5354A9C1-D9FF-8245-9263-52D99C6505AD}"/>
-    <hyperlink ref="A49" r:id="rId49" display="https://www.nyse.com/quote/XNYS:AXP" xr:uid="{DC6E6818-1A9D-6C40-BCAF-6F92E156C471}"/>
-    <hyperlink ref="A50" r:id="rId50" display="https://www.nyse.com/quote/XNYS:AZO" xr:uid="{150D9E7A-5F8E-EF47-8C3E-191467171DBE}"/>
-    <hyperlink ref="A51" r:id="rId51" display="https://www.nyse.com/quote/XNYS:BA" xr:uid="{4873D06A-7B6D-5F43-989B-8774E906E0E6}"/>
-    <hyperlink ref="A52" r:id="rId52" display="https://www.nyse.com/quote/XNYS:BAC" xr:uid="{4FB67CCF-7F84-E846-88C2-A91A5751B14A}"/>
-    <hyperlink ref="A53" r:id="rId53" display="https://www.nyse.com/quote/XNYS:BALL" xr:uid="{8DFFD3A5-C6DE-FE45-83BF-BA84DD058AB3}"/>
-    <hyperlink ref="A54" r:id="rId54" display="https://www.nyse.com/quote/XNYS:BAX" xr:uid="{D5EB5288-4DBB-9F4A-8AEB-2AD77A47187B}"/>
-    <hyperlink ref="A55" r:id="rId55" display="https://www.nyse.com/quote/XNYS:BBY" xr:uid="{0AA0FDDA-A7C3-FA48-9300-966B20B9B85B}"/>
-    <hyperlink ref="A56" r:id="rId56" display="https://www.nyse.com/quote/XNYS:BDX" xr:uid="{29B439C9-32A0-E44E-B5DE-F7D0BF6230C3}"/>
-    <hyperlink ref="A57" r:id="rId57" display="https://www.nyse.com/quote/XNYS:BEN" xr:uid="{3A728722-A2E9-C442-982C-0AAA6BC8637C}"/>
-    <hyperlink ref="A58" r:id="rId58" display="https://www.nyse.com/quote/XNYS:BF.B" xr:uid="{1B9D3613-9B18-2146-90A5-7AC6BE70550A}"/>
-    <hyperlink ref="A59" r:id="rId59" display="https://www.nyse.com/quote/XNYS:BG" xr:uid="{CA83E031-A192-CE40-A12A-4E7D68E621D4}"/>
-    <hyperlink ref="A60" r:id="rId60" display="https://www.nasdaq.com/market-activity/stocks/biib" xr:uid="{61DBF511-0695-A94C-8B54-BECC3DC91B63}"/>
-    <hyperlink ref="A61" r:id="rId61" display="https://www.nyse.com/quote/XNYS:BK" xr:uid="{0B37A947-4BC9-AF46-A5BF-3ECEFBF4BBEF}"/>
-    <hyperlink ref="A62" r:id="rId62" display="https://www.nasdaq.com/market-activity/stocks/bkng" xr:uid="{ADCC6D79-2F07-4C41-AC89-0930E6DBD9D7}"/>
-    <hyperlink ref="A63" r:id="rId63" display="https://www.nasdaq.com/market-activity/stocks/bkr" xr:uid="{A369EF4C-DB7D-C544-8E6B-8FF801C207C8}"/>
-    <hyperlink ref="A64" r:id="rId64" display="https://www.nyse.com/quote/XNYS:BLDR" xr:uid="{D23303C8-405C-5743-AB10-FDB214668DE4}"/>
-    <hyperlink ref="A65" r:id="rId65" display="https://www.nyse.com/quote/XNYS:BLK" xr:uid="{140462A4-7B11-3148-9E4A-2193E36B2DE3}"/>
-    <hyperlink ref="A66" r:id="rId66" display="https://www.nyse.com/quote/XNYS:BMY" xr:uid="{567D5D33-711F-A349-8B4A-0E0A04DD6AFB}"/>
-    <hyperlink ref="A67" r:id="rId67" display="https://www.nyse.com/quote/XNYS:BR" xr:uid="{AC2AFEA9-F185-0848-BFE0-0B8C00782026}"/>
-    <hyperlink ref="A68" r:id="rId68" display="https://www.nyse.com/quote/XNYS:BRK.B" xr:uid="{72B1F24D-7C81-5B4C-9500-4362DFB5E482}"/>
-    <hyperlink ref="A69" r:id="rId69" display="https://www.nyse.com/quote/XNYS:BRO" xr:uid="{74C941DB-B075-D54C-8611-C1D7EDFFECDD}"/>
-    <hyperlink ref="A70" r:id="rId70" display="https://www.nyse.com/quote/XNYS:BSX" xr:uid="{9530F6EC-3ED4-1B4C-BFAB-733FD8E7D624}"/>
-    <hyperlink ref="A71" r:id="rId71" display="https://www.nyse.com/quote/XNYS:BX" xr:uid="{0FF26B03-A4BC-B144-AF38-74E418A5C95E}"/>
-    <hyperlink ref="A72" r:id="rId72" display="https://www.nyse.com/quote/XNYS:BXP" xr:uid="{EF7BC5BB-CAF1-024C-8587-5FBC12FFDEC8}"/>
-    <hyperlink ref="A73" r:id="rId73" display="https://www.nyse.com/quote/XNYS:C" xr:uid="{B5788FB1-7130-F645-90F0-D136B02C3514}"/>
-    <hyperlink ref="A74" r:id="rId74" display="https://www.nyse.com/quote/XNYS:CAG" xr:uid="{85CF8C92-CECA-9A41-B7C5-2244211B74C2}"/>
-    <hyperlink ref="A75" r:id="rId75" display="https://www.nyse.com/quote/XNYS:CAH" xr:uid="{526EDF79-8D20-D044-AD27-D648B9AE57D7}"/>
-    <hyperlink ref="A76" r:id="rId76" display="https://www.nyse.com/quote/XNYS:CARR" xr:uid="{E92B70EB-1342-F440-8A73-75F31AA00892}"/>
-    <hyperlink ref="A77" r:id="rId77" display="https://www.nyse.com/quote/XNYS:CAT" xr:uid="{3CD2BFDB-B67D-B844-96D3-6127804DD600}"/>
-    <hyperlink ref="A78" r:id="rId78" display="https://www.nyse.com/quote/XNYS:CB" xr:uid="{F9A6397E-7A5A-3E48-B0FB-B68C4E0B5393}"/>
-    <hyperlink ref="A79" r:id="rId79" display="https://markets.cboe.com/us/equities/listings/listed_products/symbols/CBOE" xr:uid="{1ACA0DEE-D6DD-2346-8AA9-F76C84F657AF}"/>
-    <hyperlink ref="A80" r:id="rId80" display="https://www.nyse.com/quote/XNYS:CBRE" xr:uid="{78F5879C-52A5-6D44-B454-E7392696471E}"/>
-    <hyperlink ref="A81" r:id="rId81" display="https://www.nyse.com/quote/XNYS:CCI" xr:uid="{E8330C3B-6813-3347-834A-544E3B1F2EBC}"/>
-    <hyperlink ref="A82" r:id="rId82" display="https://www.nyse.com/quote/XNYS:CCL" xr:uid="{2883A044-88A5-6C4B-8003-92612566CEA9}"/>
-    <hyperlink ref="A83" r:id="rId83" display="https://www.nasdaq.com/market-activity/stocks/cdns" xr:uid="{617298A8-D4C8-6940-9E6D-C15D6C4CDA76}"/>
-    <hyperlink ref="A84" r:id="rId84" display="https://www.nasdaq.com/market-activity/stocks/cdw" xr:uid="{48620819-44CD-C746-B9A5-168AF6049BB2}"/>
-    <hyperlink ref="A85" r:id="rId85" display="https://www.nasdaq.com/market-activity/stocks/ceg" xr:uid="{8D47646D-7C51-2E4A-B2B2-CE44CAE7BA4C}"/>
-    <hyperlink ref="A86" r:id="rId86" display="https://www.nyse.com/quote/XNYS:CF" xr:uid="{23671DC2-D0F3-CF45-95F1-ABD7D7A43465}"/>
-    <hyperlink ref="A87" r:id="rId87" display="https://www.nyse.com/quote/XNYS:CFG" xr:uid="{8A0C53D8-A077-7C4A-9853-8FB22CDAB72D}"/>
-    <hyperlink ref="A88" r:id="rId88" display="https://www.nyse.com/quote/XNYS:CHD" xr:uid="{0D9D81E3-79CC-8940-9A16-C96013AE13D0}"/>
-    <hyperlink ref="A89" r:id="rId89" display="https://www.nasdaq.com/market-activity/stocks/chrw" xr:uid="{547777A8-C7F0-0C44-9245-D64EEFB80F89}"/>
-    <hyperlink ref="A90" r:id="rId90" display="https://www.nasdaq.com/market-activity/stocks/chtr" xr:uid="{9B7C06AB-F2F5-A24F-9DB3-ABA79BB443BD}"/>
-    <hyperlink ref="A91" r:id="rId91" display="https://www.nyse.com/quote/XNYS:CI" xr:uid="{9317C131-9594-8B45-A8AD-065FEEDA2566}"/>
-    <hyperlink ref="A92" r:id="rId92" display="https://www.nasdaq.com/market-activity/stocks/cinf" xr:uid="{0474BCDC-1475-3A40-9A0D-128168C53C3D}"/>
-    <hyperlink ref="A93" r:id="rId93" display="https://www.nyse.com/quote/XNYS:CL" xr:uid="{D66D1D3A-C161-3548-9BA6-52616C30E3B6}"/>
-    <hyperlink ref="A94" r:id="rId94" display="https://www.nyse.com/quote/XNYS:CLX" xr:uid="{26FF2CE1-62A5-6A4E-BA1C-B0A062CFAAA4}"/>
-    <hyperlink ref="A95" r:id="rId95" display="https://www.nasdaq.com/market-activity/stocks/cmcsa" xr:uid="{BEC43371-4A80-2F4D-B093-CC115DFC75A6}"/>
-    <hyperlink ref="A96" r:id="rId96" display="https://www.nasdaq.com/market-activity/stocks/cme" xr:uid="{E065E96D-25FA-6C4D-8D71-6A16E691928E}"/>
-    <hyperlink ref="A97" r:id="rId97" display="https://www.nyse.com/quote/XNYS:CMG" xr:uid="{35168A6E-81E1-444A-9F11-F57BE18D6162}"/>
-    <hyperlink ref="A98" r:id="rId98" display="https://www.nyse.com/quote/XNYS:CMI" xr:uid="{44E4FBBB-8249-E74A-A4A5-84D88040155A}"/>
-    <hyperlink ref="A99" r:id="rId99" display="https://www.nyse.com/quote/XNYS:CMS" xr:uid="{77C94B3D-5071-FB45-AD55-7DA7BEF1A824}"/>
-    <hyperlink ref="A100" r:id="rId100" display="https://www.nyse.com/quote/XNYS:CNC" xr:uid="{4998E722-16CB-6E4E-A31E-46D16962AE79}"/>
-    <hyperlink ref="A101" r:id="rId101" display="https://www.nyse.com/quote/XNYS:CNP" xr:uid="{8A7F927A-77AC-BA43-9CA7-BD510201ABFD}"/>
-    <hyperlink ref="A102" r:id="rId102" display="https://www.nyse.com/quote/XNYS:COF" xr:uid="{ED6D6E95-3422-4149-ADE4-6EF8C05A4DAD}"/>
-    <hyperlink ref="A103" r:id="rId103" display="https://www.nasdaq.com/market-activity/stocks/coin" xr:uid="{804D7749-DCE5-7848-AD66-8D421DF97983}"/>
-    <hyperlink ref="A104" r:id="rId104" display="https://www.nasdaq.com/market-activity/stocks/coo" xr:uid="{432A14AC-B70A-6547-98BD-B2DAB137E895}"/>
-    <hyperlink ref="A105" r:id="rId105" display="https://www.nyse.com/quote/XNYS:COP" xr:uid="{FE71A105-C596-FE40-A4F8-93D7C6E0F3FE}"/>
-    <hyperlink ref="A106" r:id="rId106" display="https://www.nyse.com/quote/XNYS:COR" xr:uid="{2913D1AD-1A1C-CD4E-BD94-07E291745210}"/>
-    <hyperlink ref="A107" r:id="rId107" display="https://www.nasdaq.com/market-activity/stocks/cost" xr:uid="{0270F89B-5BD7-3F4D-9A45-C231BBBE2A33}"/>
-    <hyperlink ref="A108" r:id="rId108" display="https://www.nyse.com/quote/XNYS:CPAY" xr:uid="{C5E60279-EE9D-9B4B-B79E-981ED29F53D1}"/>
-    <hyperlink ref="A109" r:id="rId109" display="https://www.nyse.com/quote/XNYS:CPB" xr:uid="{1E8AB940-8DE9-2E44-B0D6-B2983939D455}"/>
-    <hyperlink ref="A110" r:id="rId110" display="https://www.nasdaq.com/market-activity/stocks/cprt" xr:uid="{465902BB-0431-834D-B372-CD16846E1502}"/>
-    <hyperlink ref="A111" r:id="rId111" display="https://www.nyse.com/quote/XNYS:CPT" xr:uid="{041410F2-988F-4940-9947-82B0F0D3255F}"/>
-    <hyperlink ref="A112" r:id="rId112" display="https://www.nyse.com/quote/XNYS:CRL" xr:uid="{2055434D-929A-E64C-9098-EB04838FF58C}"/>
-    <hyperlink ref="A113" r:id="rId113" display="https://www.nyse.com/quote/XNYS:CRM" xr:uid="{2FBB9BBF-93AD-644C-B817-7B6BE41AD564}"/>
-    <hyperlink ref="A114" r:id="rId114" display="https://www.nasdaq.com/market-activity/stocks/crwd" xr:uid="{4234E51E-1E03-8A47-B977-BCEB58452617}"/>
-    <hyperlink ref="A115" r:id="rId115" display="https://www.nasdaq.com/market-activity/stocks/csco" xr:uid="{79C6E38C-6348-5345-B7F6-5AC69BFCBA6F}"/>
-    <hyperlink ref="A116" r:id="rId116" display="https://www.nasdaq.com/market-activity/stocks/csgp" xr:uid="{496E5833-C827-EE43-9F6A-59148BF88C43}"/>
-    <hyperlink ref="A117" r:id="rId117" display="https://www.nasdaq.com/market-activity/stocks/csx" xr:uid="{EDA189E8-217F-9C4E-979C-DB0274A5BF9C}"/>
-    <hyperlink ref="A118" r:id="rId118" display="https://www.nasdaq.com/market-activity/stocks/ctas" xr:uid="{83B405E4-257D-A34A-AAFB-F636952023E0}"/>
-    <hyperlink ref="A119" r:id="rId119" display="https://www.nyse.com/quote/XNYS:CTRA" xr:uid="{50077B70-71BD-2F40-8D68-CB43215381C9}"/>
-    <hyperlink ref="A120" r:id="rId120" display="https://www.nasdaq.com/market-activity/stocks/ctsh" xr:uid="{15E5945F-9904-4846-8C8F-28992AB81AB0}"/>
-    <hyperlink ref="A121" r:id="rId121" display="https://www.nyse.com/quote/XNYS:CTVA" xr:uid="{41FDC787-62B6-304F-A72C-756181E7BC4C}"/>
-    <hyperlink ref="A122" r:id="rId122" display="https://www.nyse.com/quote/XNYS:CVS" xr:uid="{9E8B9137-5235-8749-AD45-CB9CFD28A5AE}"/>
-    <hyperlink ref="A123" r:id="rId123" display="https://www.nyse.com/quote/XNYS:CVX" xr:uid="{1FD8B15E-71EC-414D-9EEA-8DB91937A4BB}"/>
-    <hyperlink ref="A124" r:id="rId124" display="https://www.nyse.com/quote/XNYS:D" xr:uid="{306EAAD0-92D2-2D48-96AC-CD5B176FA1C0}"/>
-    <hyperlink ref="A125" r:id="rId125" display="https://www.nyse.com/quote/XNYS:DAL" xr:uid="{37A8E1DE-F0BF-444D-B04B-DB8F69499EE3}"/>
-    <hyperlink ref="A126" r:id="rId126" display="https://www.nasdaq.com/market-activity/stocks/dash" xr:uid="{9314A871-A48E-D44C-8042-38A1D1F63985}"/>
-    <hyperlink ref="A127" r:id="rId127" display="https://www.nyse.com/quote/XNYS:DAY" xr:uid="{B374354B-54A8-9F4D-9BC6-2F1AA800B8D0}"/>
-    <hyperlink ref="A128" r:id="rId128" display="https://www.nyse.com/quote/XNYS:DD" xr:uid="{5F877B60-40A6-0B41-81A7-18B67EFC4DA3}"/>
-    <hyperlink ref="A129" r:id="rId129" display="https://www.nasdaq.com/market-activity/stocks/ddog" xr:uid="{11B58AC9-A6FE-B34A-90D3-A12F9A78D588}"/>
-    <hyperlink ref="A130" r:id="rId130" display="https://www.nyse.com/quote/XNYS:DE" xr:uid="{F3C8E27F-3B67-134C-BAF5-FC265EF147EA}"/>
-    <hyperlink ref="A131" r:id="rId131" display="https://www.nyse.com/quote/XNYS:DECK" xr:uid="{3ED0520D-A484-0B4B-8959-D999ED10CCD5}"/>
-    <hyperlink ref="A132" r:id="rId132" display="https://www.nyse.com/quote/XNYS:DELL" xr:uid="{A67A3A46-1D73-244C-BCEC-5640FF0C731E}"/>
-    <hyperlink ref="A133" r:id="rId133" display="https://www.nyse.com/quote/XNYS:DG" xr:uid="{F4F7B863-FA4C-9845-B721-F818F6A5620A}"/>
-    <hyperlink ref="A134" r:id="rId134" display="https://www.nyse.com/quote/XNYS:DGX" xr:uid="{34B95A06-756B-E246-A8C4-D6ABB733DA0E}"/>
-    <hyperlink ref="A135" r:id="rId135" display="https://www.nyse.com/quote/XNYS:DHI" xr:uid="{A34DBA3A-2A02-384B-A47E-6C1C95143E7D}"/>
-    <hyperlink ref="A136" r:id="rId136" display="https://www.nyse.com/quote/XNYS:DHR" xr:uid="{BA0F2A17-A99E-B448-B631-34C74B0AE641}"/>
-    <hyperlink ref="A137" r:id="rId137" display="https://www.nyse.com/quote/XNYS:DIS" xr:uid="{2529C43D-A4FD-D94A-8A5A-50C1A164FDE9}"/>
-    <hyperlink ref="A138" r:id="rId138" display="https://www.nyse.com/quote/XNYS:DLR" xr:uid="{8B3CD2CD-1D3D-8D42-9C3B-B72FFAF90877}"/>
-    <hyperlink ref="A139" r:id="rId139" display="https://www.nasdaq.com/market-activity/stocks/dltr" xr:uid="{74E782A2-5387-F54F-A22A-BA254081EE49}"/>
-    <hyperlink ref="A140" r:id="rId140" display="https://www.nyse.com/quote/XNYS:DOC" xr:uid="{65285AF9-D794-CC46-A14F-7A1A815C26DA}"/>
-    <hyperlink ref="A141" r:id="rId141" display="https://www.nyse.com/quote/XNYS:DOV" xr:uid="{4FE345F9-EB6A-2D40-BDDC-F4D32B727CD6}"/>
-    <hyperlink ref="A142" r:id="rId142" display="https://www.nyse.com/quote/XNYS:DOW" xr:uid="{67220858-8E49-0042-BB27-C45F876317E2}"/>
-    <hyperlink ref="A143" r:id="rId143" display="https://www.nyse.com/quote/XNYS:DPZ" xr:uid="{B0FB3E11-EA46-C94A-A5CC-B1A9F2DEA2CA}"/>
-    <hyperlink ref="A144" r:id="rId144" display="https://www.nyse.com/quote/XNYS:DRI" xr:uid="{68A3DCA2-2C23-CB42-8F5D-9D44B24960DD}"/>
-    <hyperlink ref="A145" r:id="rId145" display="https://www.nyse.com/quote/XNYS:DTE" xr:uid="{C2D2347C-7A82-C849-9169-F27835219BD2}"/>
-    <hyperlink ref="A146" r:id="rId146" display="https://www.nyse.com/quote/XNYS:DUK" xr:uid="{478587A8-B414-DD44-B611-963C94D58813}"/>
-    <hyperlink ref="A147" r:id="rId147" display="https://www.nyse.com/quote/XNYS:DVA" xr:uid="{8EE8916D-FA87-D84B-8E1F-5713469139DE}"/>
-    <hyperlink ref="A148" r:id="rId148" display="https://www.nyse.com/quote/XNYS:DVN" xr:uid="{068C41D5-30F9-A04C-8D8C-E53C3F5669B4}"/>
-    <hyperlink ref="A149" r:id="rId149" display="https://www.nasdaq.com/market-activity/stocks/dxcm" xr:uid="{50377D63-2B99-5F43-A592-744C71CCE043}"/>
-    <hyperlink ref="A150" r:id="rId150" display="https://www.nasdaq.com/market-activity/stocks/ea" xr:uid="{1C943FAD-9B76-1C4B-ABB6-84E625009003}"/>
-    <hyperlink ref="A151" r:id="rId151" display="https://www.nasdaq.com/market-activity/stocks/ebay" xr:uid="{4C79D00F-264C-3F46-992D-D69F2BEBC9E9}"/>
-    <hyperlink ref="A152" r:id="rId152" display="https://www.nyse.com/quote/XNYS:ECL" xr:uid="{6B70C0E4-7AFD-D947-8C31-24B2ED70AFF4}"/>
-    <hyperlink ref="A153" r:id="rId153" display="https://www.nyse.com/quote/XNYS:ED" xr:uid="{60D7DB7D-5CC7-D64C-AE0F-9F3AC32BC5F7}"/>
-    <hyperlink ref="A154" r:id="rId154" display="https://www.nyse.com/quote/XNYS:EFX" xr:uid="{EB85254D-AC40-DA4D-8948-4809B40B3A3C}"/>
-    <hyperlink ref="A155" r:id="rId155" display="https://www.nyse.com/quote/XNYS:EG" xr:uid="{BA56CF6F-BF72-AF4A-BCBB-49F8A4E8752D}"/>
-    <hyperlink ref="A156" r:id="rId156" display="https://www.nyse.com/quote/XNYS:EIX" xr:uid="{AEF0EFC4-0297-254F-92B8-976DA40FFDF8}"/>
-    <hyperlink ref="A157" r:id="rId157" display="https://www.nyse.com/quote/XNYS:EL" xr:uid="{B678ECE7-065E-7E41-8BED-0FAA57182399}"/>
-    <hyperlink ref="A158" r:id="rId158" display="https://www.nyse.com/quote/XNYS:ELV" xr:uid="{47459202-66A0-C349-A260-D8C14EDC5A1C}"/>
-    <hyperlink ref="A159" r:id="rId159" display="https://www.nyse.com/quote/XNYS:EME" xr:uid="{E3B45B61-E39D-C544-ADA5-5C5D38C8F263}"/>
-    <hyperlink ref="A160" r:id="rId160" display="https://www.nyse.com/quote/XNYS:EMN" xr:uid="{99323F7E-6671-7F48-95FC-E434FE0B4431}"/>
-    <hyperlink ref="A161" r:id="rId161" display="https://www.nyse.com/quote/XNYS:EMR" xr:uid="{B4F3FAAE-36FC-014D-A757-9451A363C61C}"/>
-    <hyperlink ref="A162" r:id="rId162" display="https://www.nyse.com/quote/XNYS:EOG" xr:uid="{B12F38F5-0A77-AE4F-867C-734992F64570}"/>
-    <hyperlink ref="A163" r:id="rId163" display="https://www.nyse.com/quote/XNYS:EPAM" xr:uid="{CF06961F-E87F-8F4E-866B-DC017148585C}"/>
-    <hyperlink ref="A164" r:id="rId164" display="https://www.nasdaq.com/market-activity/stocks/eqix" xr:uid="{BA8F6119-57AB-6242-B94C-7C9DC6A1FD56}"/>
-    <hyperlink ref="A165" r:id="rId165" display="https://www.nyse.com/quote/XNYS:EQR" xr:uid="{7998B668-40A4-9343-8BBF-8C2DC73B637B}"/>
-    <hyperlink ref="A166" r:id="rId166" display="https://www.nyse.com/quote/XNYS:EQT" xr:uid="{AC8A8178-EFCC-0241-9B0E-9B2321C51110}"/>
-    <hyperlink ref="A167" r:id="rId167" display="https://www.nasdaq.com/market-activity/stocks/erie" xr:uid="{09CEBBEA-DF78-1141-A6ED-7C8C987B1E55}"/>
-    <hyperlink ref="A168" r:id="rId168" display="https://www.nyse.com/quote/XNYS:ES" xr:uid="{A337B079-98C5-1142-843A-101518ECD5F1}"/>
-    <hyperlink ref="A169" r:id="rId169" display="https://www.nyse.com/quote/XNYS:ESS" xr:uid="{86140575-00D2-F146-8011-DA6536FD7623}"/>
-    <hyperlink ref="A170" r:id="rId170" display="https://www.nyse.com/quote/XNYS:ETN" xr:uid="{19A7714D-0A54-D244-86FF-FBB15D022C00}"/>
-    <hyperlink ref="A171" r:id="rId171" display="https://www.nyse.com/quote/XNYS:ETR" xr:uid="{E195E659-2591-2242-9D2B-C43F9E752D93}"/>
-    <hyperlink ref="A172" r:id="rId172" display="https://www.nyse.com/quote/XNYS:EVRG" xr:uid="{8E9E2FBD-FB12-734D-8CF0-59716EBCCE37}"/>
-    <hyperlink ref="A173" r:id="rId173" display="https://www.nyse.com/quote/XNYS:EW" xr:uid="{76236DE9-3CC3-0343-AB3D-F6F845689D0D}"/>
-    <hyperlink ref="A174" r:id="rId174" display="https://www.nasdaq.com/market-activity/stocks/exc" xr:uid="{8C4120D5-68ED-484D-85DD-68309BFCBBE7}"/>
-    <hyperlink ref="A175" r:id="rId175" display="https://www.nasdaq.com/market-activity/stocks/exe" xr:uid="{B55C7EEF-EDA7-BF4D-B8EF-32F7F0E8CC93}"/>
-    <hyperlink ref="A176" r:id="rId176" display="https://www.nasdaq.com/market-activity/stocks/expd" xr:uid="{1EBA637D-A0C6-7E45-A94C-C163CBBC7A59}"/>
-    <hyperlink ref="A177" r:id="rId177" display="https://www.nasdaq.com/market-activity/stocks/expe" xr:uid="{716232D9-B422-4540-A6C5-6BB40280740D}"/>
-    <hyperlink ref="A178" r:id="rId178" display="https://www.nyse.com/quote/XNYS:EXR" xr:uid="{2A350B28-8FAD-D54A-A4E6-06E709999FAD}"/>
-    <hyperlink ref="A179" r:id="rId179" display="https://www.nyse.com/quote/XNYS:F" xr:uid="{5980A6F1-883E-EE49-B434-43AE8A92EDE1}"/>
-    <hyperlink ref="A180" r:id="rId180" display="https://www.nasdaq.com/market-activity/stocks/fang" xr:uid="{7B53C20B-E740-4246-B556-5B166E95A491}"/>
-    <hyperlink ref="A181" r:id="rId181" display="https://www.nasdaq.com/market-activity/stocks/fast" xr:uid="{277E3B33-E5AE-9440-9ECC-1C999CB17002}"/>
-    <hyperlink ref="A182" r:id="rId182" display="https://www.nyse.com/quote/XNYS:FCX" xr:uid="{4A770D84-B02A-5042-994F-683DF8B629FC}"/>
-    <hyperlink ref="A183" r:id="rId183" display="https://www.nyse.com/quote/XNYS:FDS" xr:uid="{A4A9821E-99D8-4F4D-B349-FC125FC4BAAA}"/>
-    <hyperlink ref="A184" r:id="rId184" display="https://www.nyse.com/quote/XNYS:FDX" xr:uid="{DD39B4FD-6065-D644-BE78-AF0E7A40F54C}"/>
-    <hyperlink ref="A185" r:id="rId185" display="https://www.nyse.com/quote/XNYS:FE" xr:uid="{1534FD60-5A79-4C46-BC29-998DFC94A9C5}"/>
-    <hyperlink ref="A186" r:id="rId186" display="https://www.nasdaq.com/market-activity/stocks/ffiv" xr:uid="{3DAAC8E3-B4EA-084B-A02C-7633204CF1B4}"/>
-    <hyperlink ref="A187" r:id="rId187" display="https://www.nyse.com/quote/XNYS:FI" xr:uid="{3CF5A9CB-1F6B-AB4A-A63D-C5665413C9EE}"/>
-    <hyperlink ref="A188" r:id="rId188" display="https://www.nyse.com/quote/XNYS:FICO" xr:uid="{1831A289-532E-B64D-AA68-DAD46AEAE1E5}"/>
-    <hyperlink ref="A189" r:id="rId189" display="https://www.nyse.com/quote/XNYS:FIS" xr:uid="{19839A74-2BD3-3C4B-9541-252D07C2ACA0}"/>
-    <hyperlink ref="A190" r:id="rId190" display="https://www.nasdaq.com/market-activity/stocks/fitb" xr:uid="{7968B7BF-254F-4546-AE0B-4E7A00FED347}"/>
-    <hyperlink ref="A191" r:id="rId191" display="https://www.nasdaq.com/market-activity/stocks/fox" xr:uid="{6B62CF4A-ACA1-F040-AF02-B19D2EFCBDBF}"/>
-    <hyperlink ref="A192" r:id="rId192" display="https://www.nasdaq.com/market-activity/stocks/foxa" xr:uid="{FDC4C1A6-BC06-AC4C-B0FA-215CB0925309}"/>
-    <hyperlink ref="A193" r:id="rId193" display="https://www.nyse.com/quote/XNYS:FRT" xr:uid="{999F423C-3B93-F349-B19C-02A91A74FF8B}"/>
-    <hyperlink ref="A194" r:id="rId194" display="https://www.nasdaq.com/market-activity/stocks/fslr" xr:uid="{59607057-ABA6-B44D-8EC0-6A7B860A9141}"/>
-    <hyperlink ref="A195" r:id="rId195" display="https://www.nasdaq.com/market-activity/stocks/ftnt" xr:uid="{9456FC7E-9D91-FA49-B421-47702C8ED3CB}"/>
-    <hyperlink ref="A196" r:id="rId196" display="https://www.nyse.com/quote/XNYS:FTV" xr:uid="{84A0E97F-2F4E-0449-BF6D-E776C91A0256}"/>
-    <hyperlink ref="A197" r:id="rId197" display="https://www.nyse.com/quote/XNYS:GD" xr:uid="{13A55F4B-2227-EE44-8D44-8BE9230C9AEB}"/>
-    <hyperlink ref="A198" r:id="rId198" display="https://www.nyse.com/quote/XNYS:GDDY" xr:uid="{BD2AC02E-04EC-E64E-869A-6C7714832203}"/>
-    <hyperlink ref="A199" r:id="rId199" display="https://www.nyse.com/quote/XNYS:GE" xr:uid="{69D40C48-9224-7847-AF21-65ABB35032C0}"/>
-    <hyperlink ref="A200" r:id="rId200" display="https://www.nasdaq.com/market-activity/stocks/gehc" xr:uid="{9EC80EED-97F5-EF46-A155-24C2B0B5D4BD}"/>
-    <hyperlink ref="A201" r:id="rId201" display="https://www.nasdaq.com/market-activity/stocks/gen" xr:uid="{95822482-6F8C-3A42-AC87-30770424DDA2}"/>
-    <hyperlink ref="A202" r:id="rId202" display="https://www.nyse.com/quote/XNYS:GEV" xr:uid="{C434C299-48E9-6847-9EB6-7383B8D0AF7F}"/>
-    <hyperlink ref="A203" r:id="rId203" display="https://www.nasdaq.com/market-activity/stocks/gild" xr:uid="{9CE5F5F2-209C-EC47-9AC4-855405113A80}"/>
-    <hyperlink ref="A204" r:id="rId204" display="https://www.nyse.com/quote/XNYS:GIS" xr:uid="{B2BD0DB8-8238-7646-99BA-EFE60DEEA829}"/>
-    <hyperlink ref="A205" r:id="rId205" display="https://www.nyse.com/quote/XNYS:GL" xr:uid="{34B4D36A-C1DF-484E-8D29-E13BE0B66076}"/>
-    <hyperlink ref="A206" r:id="rId206" display="https://www.nyse.com/quote/XNYS:GLW" xr:uid="{0000A273-3372-0C4B-BFC0-7AE8DA51217C}"/>
-    <hyperlink ref="A207" r:id="rId207" display="https://www.nyse.com/quote/XNYS:GM" xr:uid="{9DE70AF1-66F5-CD4B-8F79-FBBF2F1C7ECC}"/>
-    <hyperlink ref="A208" r:id="rId208" display="https://www.nyse.com/quote/XNYS:GNRC" xr:uid="{45B7E118-4F7C-3347-8A6D-C31245A3D246}"/>
-    <hyperlink ref="A209" r:id="rId209" display="https://www.nasdaq.com/market-activity/stocks/goog" xr:uid="{DB6E43BA-E78D-C94F-A910-FF963FDA4269}"/>
-    <hyperlink ref="A210" r:id="rId210" display="https://www.nasdaq.com/market-activity/stocks/googl" xr:uid="{5C85BE14-0962-CE4E-8EBF-02C6B40FD667}"/>
-    <hyperlink ref="A211" r:id="rId211" display="https://www.nyse.com/quote/XNYS:GPC" xr:uid="{260CD3BE-22F0-0247-B9DE-637563A21BC4}"/>
-    <hyperlink ref="A212" r:id="rId212" display="https://www.nyse.com/quote/XNYS:GPN" xr:uid="{FDFA090A-736D-ED4F-97FE-4968D18EC996}"/>
-    <hyperlink ref="A213" r:id="rId213" display="https://www.nyse.com/quote/XNYS:GRMN" xr:uid="{203C47D7-C500-334F-97CE-4262151CC52E}"/>
-    <hyperlink ref="A214" r:id="rId214" display="https://www.nyse.com/quote/XNYS:GS" xr:uid="{5D6C016B-1E26-CA4A-B517-4E9C837519E1}"/>
-    <hyperlink ref="A215" r:id="rId215" display="https://www.nyse.com/quote/XNYS:GWW" xr:uid="{9EEC6BC1-01C2-4D4D-AB0F-7A29944689C7}"/>
-    <hyperlink ref="A216" r:id="rId216" display="https://www.nyse.com/quote/XNYS:HAL" xr:uid="{410CF685-5B6E-2140-9DEB-B488075980BF}"/>
-    <hyperlink ref="A217" r:id="rId217" display="https://www.nasdaq.com/market-activity/stocks/has" xr:uid="{1E23571E-13C1-234E-B870-905EDA173E4A}"/>
-    <hyperlink ref="A218" r:id="rId218" display="https://www.nasdaq.com/market-activity/stocks/hban" xr:uid="{497B803E-733B-D547-B6C6-238F74B7209B}"/>
-    <hyperlink ref="A219" r:id="rId219" display="https://www.nyse.com/quote/XNYS:HCA" xr:uid="{F4CD64A0-BAEE-4C43-BB81-A5FBF5E26C45}"/>
-    <hyperlink ref="A220" r:id="rId220" display="https://www.nyse.com/quote/XNYS:HD" xr:uid="{F9857387-8B3D-E746-B1F5-C8DAC52CF750}"/>
-    <hyperlink ref="A221" r:id="rId221" display="https://www.nyse.com/quote/XNYS:HIG" xr:uid="{B92F3BC6-BC38-E64D-9F98-DC755A4B8674}"/>
-    <hyperlink ref="A222" r:id="rId222" display="https://www.nyse.com/quote/XNYS:HII" xr:uid="{FD03CC34-3FCA-784F-9616-87E142793174}"/>
-    <hyperlink ref="A223" r:id="rId223" display="https://www.nyse.com/quote/XNYS:HLT" xr:uid="{68D878C3-0517-704E-9113-5B8E98AFC660}"/>
-    <hyperlink ref="A224" r:id="rId224" display="https://www.nasdaq.com/market-activity/stocks/holx" xr:uid="{437FC4F0-A4D2-494A-86C7-F17F604D5605}"/>
-    <hyperlink ref="A225" r:id="rId225" display="https://www.nasdaq.com/market-activity/stocks/hon" xr:uid="{D2165BFD-263F-CA4E-8D99-56C04D92F97C}"/>
-    <hyperlink ref="A226" r:id="rId226" display="https://www.nasdaq.com/market-activity/stocks/hood" xr:uid="{FA6AA034-556F-4D42-B921-925E85E80EB6}"/>
-    <hyperlink ref="A227" r:id="rId227" display="https://www.nyse.com/quote/XNYS:HPE" xr:uid="{EAE9088E-1BA9-7349-AC0F-F6339A5EA33A}"/>
-    <hyperlink ref="A228" r:id="rId228" display="https://www.nyse.com/quote/XNYS:HPQ" xr:uid="{D1188BA9-602B-4948-B4E3-59F989523540}"/>
-    <hyperlink ref="A229" r:id="rId229" display="https://www.nyse.com/quote/XNYS:HRL" xr:uid="{F837824A-87EB-604D-BE7C-95DD11E49CA3}"/>
-    <hyperlink ref="A230" r:id="rId230" display="https://www.nasdaq.com/market-activity/stocks/hsic" xr:uid="{44936B30-5156-5842-8C73-5EC920C1BF0C}"/>
-    <hyperlink ref="A231" r:id="rId231" display="https://www.nasdaq.com/market-activity/stocks/hst" xr:uid="{0AED5690-80C5-1240-84E9-C4EF051E9646}"/>
-    <hyperlink ref="A232" r:id="rId232" display="https://www.nyse.com/quote/XNYS:HSY" xr:uid="{C8F149BC-3380-944D-B5F4-8158A1FD764F}"/>
-    <hyperlink ref="A233" r:id="rId233" display="https://www.nyse.com/quote/XNYS:HUBB" xr:uid="{9F6E8641-3DEF-4D43-9C4A-1AA1AEB3CE1A}"/>
-    <hyperlink ref="A234" r:id="rId234" display="https://www.nyse.com/quote/XNYS:HUM" xr:uid="{6868079D-B8D6-0A41-8E43-65BD66C4E302}"/>
-    <hyperlink ref="A235" r:id="rId235" display="https://www.nyse.com/quote/XNYS:HWM" xr:uid="{ECC2003D-3A34-3748-A74B-254870507A5A}"/>
-    <hyperlink ref="A236" r:id="rId236" display="https://www.nasdaq.com/market-activity/stocks/ibkr" xr:uid="{1ACC85F1-F69F-A346-9C20-6C54B8C6BF7F}"/>
-    <hyperlink ref="A237" r:id="rId237" display="https://www.nyse.com/quote/XNYS:IBM" xr:uid="{1A090DD4-3FFD-9C41-A631-81C950477713}"/>
-    <hyperlink ref="A238" r:id="rId238" display="https://www.nyse.com/quote/XNYS:ICE" xr:uid="{DDBAE428-0140-C44E-A54E-0A991DC4788A}"/>
-    <hyperlink ref="A239" r:id="rId239" display="https://www.nasdaq.com/market-activity/stocks/idxx" xr:uid="{8BB5349F-6120-0F47-9B3A-83B9B078E7D0}"/>
-    <hyperlink ref="A240" r:id="rId240" display="https://www.nyse.com/quote/XNYS:IEX" xr:uid="{2F6528E7-97E5-C04A-86A1-062F0281FD28}"/>
-    <hyperlink ref="A241" r:id="rId241" display="https://www.nyse.com/quote/XNYS:IFF" xr:uid="{5ABBAE51-BA22-224C-948E-2CB6C6C452C0}"/>
-    <hyperlink ref="A242" r:id="rId242" display="https://www.nasdaq.com/market-activity/stocks/incy" xr:uid="{1582E21C-0860-8142-A2D9-0EA2692ED679}"/>
-    <hyperlink ref="A243" r:id="rId243" display="https://www.nasdaq.com/market-activity/stocks/intc" xr:uid="{FE07B5A9-8D7C-4D4D-8EB8-42E112726241}"/>
-    <hyperlink ref="A244" r:id="rId244" display="https://www.nasdaq.com/market-activity/stocks/intu" xr:uid="{3563D9A7-E6F2-2040-BC71-ECBFE1EE6F1D}"/>
-    <hyperlink ref="A245" r:id="rId245" display="https://www.nyse.com/quote/XNYS:INVH" xr:uid="{5EAEECD7-EA27-4B40-918D-8B9A9C347D10}"/>
-    <hyperlink ref="A246" r:id="rId246" display="https://www.nyse.com/quote/XNYS:IP" xr:uid="{A5A5A651-D681-B64E-B27D-8FDC8564514D}"/>
-    <hyperlink ref="A247" r:id="rId247" display="https://www.nyse.com/quote/XNYS:IPG" xr:uid="{EA0E77A8-5DC5-ED49-9E58-2EB3D9592A22}"/>
-    <hyperlink ref="A248" r:id="rId248" display="https://www.nyse.com/quote/XNYS:IQV" xr:uid="{ABF35066-F352-6743-850E-91D8F3B90435}"/>
-    <hyperlink ref="A249" r:id="rId249" display="https://www.nyse.com/quote/XNYS:IR" xr:uid="{F385CADB-6738-1B40-9022-45BA1D3DDF9D}"/>
-    <hyperlink ref="A250" r:id="rId250" display="https://www.nyse.com/quote/XNYS:IRM" xr:uid="{6E5048D7-B841-8146-A630-38C93EBFF30D}"/>
-    <hyperlink ref="A251" r:id="rId251" display="https://www.nasdaq.com/market-activity/stocks/isrg" xr:uid="{171AC82D-3286-F741-8C45-01865730A0A0}"/>
-    <hyperlink ref="A252" r:id="rId252" display="https://www.nyse.com/quote/XNYS:IT" xr:uid="{E126C9B3-0173-9E4B-8797-0E3CE2CF3860}"/>
-    <hyperlink ref="A253" r:id="rId253" display="https://www.nyse.com/quote/XNYS:ITW" xr:uid="{C72B99C9-F0A6-C546-9CDD-4D647E3520F9}"/>
-    <hyperlink ref="A254" r:id="rId254" display="https://www.nyse.com/quote/XNYS:IVZ" xr:uid="{BF2FC951-EBAC-5F41-B65B-4A8B8E31F4F3}"/>
-    <hyperlink ref="A255" r:id="rId255" display="https://www.nyse.com/quote/XNYS:J" xr:uid="{A1F187DC-2EF6-CB44-8346-1280B995C82D}"/>
-    <hyperlink ref="A256" r:id="rId256" display="https://www.nasdaq.com/market-activity/stocks/jbht" xr:uid="{4DC98B14-3E96-914C-9660-2227F754C6D5}"/>
-    <hyperlink ref="A257" r:id="rId257" display="https://www.nyse.com/quote/XNYS:JBL" xr:uid="{7E6CB0E5-AFE4-E446-B8E9-2AADF24FDC1A}"/>
-    <hyperlink ref="A258" r:id="rId258" display="https://www.nyse.com/quote/XNYS:JCI" xr:uid="{B6C124F0-B304-1344-998E-A578EA5F593A}"/>
-    <hyperlink ref="A259" r:id="rId259" display="https://www.nasdaq.com/market-activity/stocks/jkhy" xr:uid="{BFABB2B6-6661-2F4A-A456-C7A5A74C8EAB}"/>
-    <hyperlink ref="A260" r:id="rId260" display="https://www.nyse.com/quote/XNYS:JNJ" xr:uid="{42AFA511-6B70-8C49-8908-8A28D5E82237}"/>
-    <hyperlink ref="A261" r:id="rId261" display="https://www.nyse.com/quote/XNYS:JPM" xr:uid="{11E98EFD-DA6A-394F-995D-6B1B18F854EF}"/>
-    <hyperlink ref="A262" r:id="rId262" display="https://www.nyse.com/quote/XNYS:K" xr:uid="{A6B2C616-CB07-244E-BE66-8BA8C4CD0F37}"/>
-    <hyperlink ref="A263" r:id="rId263" display="https://www.nasdaq.com/market-activity/stocks/kdp" xr:uid="{3381C987-3A09-C748-B70E-ECCEF99C299B}"/>
-    <hyperlink ref="A264" r:id="rId264" display="https://www.nyse.com/quote/XNYS:KEY" xr:uid="{823A9A91-53D2-A04A-826F-A6EE11A63C76}"/>
-    <hyperlink ref="A265" r:id="rId265" display="https://www.nyse.com/quote/XNYS:KEYS" xr:uid="{3D098851-0B4C-C649-9C96-912147431D3D}"/>
-    <hyperlink ref="A266" r:id="rId266" display="https://www.nasdaq.com/market-activity/stocks/khc" xr:uid="{0C599AA0-10F6-3541-89F7-0A88DA1D39C6}"/>
-    <hyperlink ref="A267" r:id="rId267" display="https://www.nyse.com/quote/XNYS:KIM" xr:uid="{28A1174D-3E8C-314C-913B-68A8DCC8C684}"/>
-    <hyperlink ref="A268" r:id="rId268" display="https://www.nyse.com/quote/XNYS:KKR" xr:uid="{42414C63-F8E6-2443-B0FC-7090CF6A4007}"/>
-    <hyperlink ref="A269" r:id="rId269" display="https://www.nasdaq.com/market-activity/stocks/klac" xr:uid="{AAA2BF98-A807-9146-9ED4-CEA5F481594A}"/>
-    <hyperlink ref="A270" r:id="rId270" display="https://www.nasdaq.com/market-activity/stocks/kmb" xr:uid="{D92FB513-6C31-9C46-9ED3-F20CD39EDE00}"/>
-    <hyperlink ref="A271" r:id="rId271" display="https://www.nyse.com/quote/XNYS:KMI" xr:uid="{32A9402A-E64D-114A-AFF9-A443DFA174EC}"/>
-    <hyperlink ref="A272" r:id="rId272" display="https://www.nyse.com/quote/XNYS:KMX" xr:uid="{04D256EA-1334-FE4E-9ED0-4FB790B9B022}"/>
-    <hyperlink ref="A273" r:id="rId273" display="https://www.nyse.com/quote/XNYS:KO" xr:uid="{E57A6991-11D3-7540-AA9E-08AC31FD0C90}"/>
-    <hyperlink ref="A274" r:id="rId274" display="https://www.nyse.com/quote/XNYS:KR" xr:uid="{E67C6841-C304-654A-99C1-15F76900DD5D}"/>
-    <hyperlink ref="A275" r:id="rId275" display="https://www.nyse.com/quote/XNYS:KVUE" xr:uid="{80B051EB-8506-CF4C-B100-851D043F180A}"/>
-    <hyperlink ref="A276" r:id="rId276" display="https://www.nyse.com/quote/XNYS:L" xr:uid="{2A010A35-21AD-AC4E-B544-104559D27F86}"/>
-    <hyperlink ref="A277" r:id="rId277" display="https://www.nyse.com/quote/XNYS:LDOS" xr:uid="{BE383C9C-26BE-6949-80E8-DEF4C89E56DC}"/>
-    <hyperlink ref="A278" r:id="rId278" display="https://www.nyse.com/quote/XNYS:LEN" xr:uid="{1AD6D35E-DEDF-2C49-B56C-B22CF52A01D2}"/>
-    <hyperlink ref="A279" r:id="rId279" display="https://www.nyse.com/quote/XNYS:LH" xr:uid="{1D0BEB1D-B97B-1945-88E7-D19D14D83BA0}"/>
-    <hyperlink ref="A280" r:id="rId280" display="https://www.nyse.com/quote/XNYS:LHX" xr:uid="{BFE026E7-F2DA-C547-8350-69998FA4F8E6}"/>
-    <hyperlink ref="A281" r:id="rId281" display="https://www.nyse.com/quote/XNYS:LII" xr:uid="{0E05D2E7-DB56-9F4D-9D23-F17FA1B048AE}"/>
-    <hyperlink ref="A282" r:id="rId282" display="https://www.nasdaq.com/market-activity/stocks/lin" xr:uid="{28FDFD73-7E21-1C48-AC42-0D31475B811D}"/>
-    <hyperlink ref="A283" r:id="rId283" display="https://www.nasdaq.com/market-activity/stocks/lkq" xr:uid="{D055FFF5-0E22-BE4D-88F0-72DBE46FC7A3}"/>
-    <hyperlink ref="A284" r:id="rId284" display="https://www.nyse.com/quote/XNYS:LLY" xr:uid="{D15F4A74-7ED1-9C4C-90A1-90B717839E6B}"/>
-    <hyperlink ref="A285" r:id="rId285" display="https://www.nyse.com/quote/XNYS:LMT" xr:uid="{FCDDFFBC-06B6-0549-B0E1-2C2EE7C375E9}"/>
-    <hyperlink ref="A286" r:id="rId286" display="https://www.nasdaq.com/market-activity/stocks/lnt" xr:uid="{DCDC2821-66F4-8345-9834-DADB081E9E13}"/>
-    <hyperlink ref="A287" r:id="rId287" display="https://www.nyse.com/quote/XNYS:LOW" xr:uid="{FF3F7959-D6FB-4547-96F2-D836A846B1C1}"/>
-    <hyperlink ref="A288" r:id="rId288" display="https://www.nasdaq.com/market-activity/stocks/lrcx" xr:uid="{7AAC7474-BFF4-1240-9BD6-645B2EFF84E0}"/>
-    <hyperlink ref="A289" r:id="rId289" display="https://www.nasdaq.com/market-activity/stocks/lulu" xr:uid="{717119E8-F5DD-8643-8B8B-1407446E6EDE}"/>
-    <hyperlink ref="A290" r:id="rId290" display="https://www.nyse.com/quote/XNYS:LUV" xr:uid="{D52BF1DF-740C-044B-B558-0E08E7D9A6BA}"/>
-    <hyperlink ref="A291" r:id="rId291" display="https://www.nyse.com/quote/XNYS:LVS" xr:uid="{4E8906E2-AC94-9940-BEF5-BA2B243A30A9}"/>
-    <hyperlink ref="A292" r:id="rId292" display="https://www.nyse.com/quote/XNYS:LW" xr:uid="{AAA08419-77BF-2649-87D9-7CB7EF24F053}"/>
-    <hyperlink ref="A293" r:id="rId293" display="https://www.nyse.com/quote/XNYS:LYB" xr:uid="{79456F53-94A2-4E46-8394-3330392BCAA2}"/>
-    <hyperlink ref="A294" r:id="rId294" display="https://www.nyse.com/quote/XNYS:LYV" xr:uid="{1B732D9A-9878-024C-BE46-97633D254972}"/>
-    <hyperlink ref="A295" r:id="rId295" display="https://www.nyse.com/quote/XNYS:MA" xr:uid="{3E7CD1B0-EA7B-DF45-8FEF-CFE7FF292357}"/>
-    <hyperlink ref="A296" r:id="rId296" display="https://www.nyse.com/quote/XNYS:MAA" xr:uid="{520B5C5E-41DE-9C40-B42C-85F8DAD4ABC1}"/>
-    <hyperlink ref="A297" r:id="rId297" display="https://www.nasdaq.com/market-activity/stocks/mar" xr:uid="{761061B4-0C87-F04B-BDD6-12CB6B030362}"/>
-    <hyperlink ref="A298" r:id="rId298" display="https://www.nyse.com/quote/XNYS:MAS" xr:uid="{893855C5-EEC3-5C43-A54F-3E81C945E34E}"/>
-    <hyperlink ref="A299" r:id="rId299" display="https://www.nyse.com/quote/XNYS:MCD" xr:uid="{53FF8A65-D1A8-8543-8BC9-DD396620CEF1}"/>
-    <hyperlink ref="A300" r:id="rId300" display="https://www.nasdaq.com/market-activity/stocks/mchp" xr:uid="{F689EEC2-2786-CF47-A666-C7C31EBFDDBD}"/>
-    <hyperlink ref="A301" r:id="rId301" display="https://www.nyse.com/quote/XNYS:MCK" xr:uid="{A00B0963-E571-3047-98E3-8C24AA52C177}"/>
-    <hyperlink ref="A302" r:id="rId302" display="https://www.nyse.com/quote/XNYS:MCO" xr:uid="{9DA46D4A-F942-7642-BDD9-22A84AD04A32}"/>
-    <hyperlink ref="A303" r:id="rId303" display="https://www.nasdaq.com/market-activity/stocks/mdlz" xr:uid="{4E1206C5-C6B0-E44B-A6BF-E8B56F0EB746}"/>
-    <hyperlink ref="A304" r:id="rId304" display="https://www.nyse.com/quote/XNYS:MDT" xr:uid="{9DA57471-D544-974B-BC72-4A32F1D24C35}"/>
-    <hyperlink ref="A305" r:id="rId305" display="https://www.nyse.com/quote/XNYS:MET" xr:uid="{1EEE6973-02B2-9F41-8019-2B8DEE6971BD}"/>
-    <hyperlink ref="A306" r:id="rId306" display="https://www.nasdaq.com/market-activity/stocks/meta" xr:uid="{62F71363-D9F3-D64B-96A0-13AC394FCBBE}"/>
-    <hyperlink ref="A307" r:id="rId307" display="https://www.nyse.com/quote/XNYS:MGM" xr:uid="{BAA61BA9-A17A-5F4A-85EB-13FA65A41F05}"/>
-    <hyperlink ref="A308" r:id="rId308" display="https://www.nyse.com/quote/XNYS:MHK" xr:uid="{3A68F269-A290-154A-BFC4-E40396C1156C}"/>
-    <hyperlink ref="A309" r:id="rId309" display="https://www.nyse.com/quote/XNYS:MKC" xr:uid="{2E4E3456-793A-6E41-9B45-A472FBFB2614}"/>
-    <hyperlink ref="A310" r:id="rId310" display="https://www.nyse.com/quote/XNYS:MLM" xr:uid="{E605175A-51B1-F64B-9894-7447CD49375D}"/>
-    <hyperlink ref="A311" r:id="rId311" display="https://www.nyse.com/quote/XNYS:MMC" xr:uid="{4C849AAF-42A5-D54D-AE7F-375154380F02}"/>
-    <hyperlink ref="A312" r:id="rId312" display="https://www.nyse.com/quote/XNYS:MMM" xr:uid="{449940FA-6C6D-0840-8498-F356A25FB276}"/>
-    <hyperlink ref="A313" r:id="rId313" display="https://www.nasdaq.com/market-activity/stocks/mnst" xr:uid="{B4B93AAE-D145-3549-8D04-889BB89B206E}"/>
-    <hyperlink ref="A314" r:id="rId314" display="https://www.nyse.com/quote/XNYS:MO" xr:uid="{81084AB5-8657-8740-98A6-A870C94E1C4A}"/>
-    <hyperlink ref="A315" r:id="rId315" display="https://www.nyse.com/quote/XNYS:MOH" xr:uid="{8F9E6469-FCE4-0D44-842D-BFD9173E6A21}"/>
-    <hyperlink ref="A316" r:id="rId316" display="https://www.nyse.com/quote/XNYS:MOS" xr:uid="{90325084-A959-F741-B0E1-451C43454A11}"/>
-    <hyperlink ref="A317" r:id="rId317" display="https://www.nyse.com/quote/XNYS:MPC" xr:uid="{8741995F-085D-F641-A873-85F8A33810D5}"/>
-    <hyperlink ref="A318" r:id="rId318" display="https://www.nasdaq.com/market-activity/stocks/mpwr" xr:uid="{84B97065-3398-3348-ACBE-C06FE05F10A4}"/>
-    <hyperlink ref="A319" r:id="rId319" display="https://www.nyse.com/quote/XNYS:MRK" xr:uid="{2465682A-B5F7-4A4D-9966-18E3047772F8}"/>
-    <hyperlink ref="A320" r:id="rId320" display="https://www.nasdaq.com/market-activity/stocks/mrna" xr:uid="{BE3DC42A-4DBF-574D-B1A4-9E7E5149D8D4}"/>
-    <hyperlink ref="A321" r:id="rId321" display="https://www.nyse.com/quote/XNYS:MS" xr:uid="{F18CACBA-5049-954F-B7C7-7462C0F04F5D}"/>
-    <hyperlink ref="A322" r:id="rId322" display="https://www.nyse.com/quote/XNYS:MSCI" xr:uid="{72B23BA3-44E4-0B4D-8C3F-FE3E68241CBE}"/>
-    <hyperlink ref="A323" r:id="rId323" display="https://www.nasdaq.com/market-activity/stocks/msft" xr:uid="{329A6E60-5D19-8F4E-886F-B2D7E106E903}"/>
-    <hyperlink ref="A324" r:id="rId324" display="https://www.nyse.com/quote/XNYS:MSI" xr:uid="{FAE9FF66-7248-C94B-B853-2C42DB47D45F}"/>
-    <hyperlink ref="A325" r:id="rId325" display="https://www.nyse.com/quote/XNYS:MTB" xr:uid="{D25DB4CA-3CF0-5646-8259-72BF5DA091E9}"/>
-    <hyperlink ref="A326" r:id="rId326" display="https://www.nasdaq.com/market-activity/stocks/mtch" xr:uid="{1A7F813E-3F99-DD4E-900F-B236E146C3F4}"/>
-    <hyperlink ref="A327" r:id="rId327" display="https://www.nyse.com/quote/XNYS:MTD" xr:uid="{FE38F7AC-14AF-6C48-A6A8-224BFFF48CA6}"/>
-    <hyperlink ref="A328" r:id="rId328" display="https://www.nasdaq.com/market-activity/stocks/mu" xr:uid="{89F5EC60-8D0C-7B49-B367-CD2063126AF9}"/>
-    <hyperlink ref="A329" r:id="rId329" display="https://www.nyse.com/quote/XNYS:NCLH" xr:uid="{CB08D2C8-0250-BD4F-A413-2A177DAB8E21}"/>
-    <hyperlink ref="A330" r:id="rId330" display="https://www.nasdaq.com/market-activity/stocks/ndaq" xr:uid="{55EC6406-9914-414E-9B3C-52A743034FEB}"/>
-    <hyperlink ref="A331" r:id="rId331" display="https://www.nasdaq.com/market-activity/stocks/ndsn" xr:uid="{3887551E-998F-3345-B673-3AC210033517}"/>
-    <hyperlink ref="A332" r:id="rId332" display="https://www.nyse.com/quote/XNYS:NEE" xr:uid="{98A63CCA-3AE7-4F4A-AC3F-2BA98D19B5B3}"/>
-    <hyperlink ref="A333" r:id="rId333" display="https://www.nyse.com/quote/XNYS:NEM" xr:uid="{E5D83086-98CE-264A-AA37-F4EEDAF8981F}"/>
-    <hyperlink ref="A334" r:id="rId334" display="https://www.nasdaq.com/market-activity/stocks/nflx" xr:uid="{41231F33-93EC-6F4F-ABBC-8A8EE54A351F}"/>
-    <hyperlink ref="A335" r:id="rId335" display="https://www.nyse.com/quote/XNYS:NI" xr:uid="{9F6401AF-D421-354D-88F9-9CAE569791C6}"/>
-    <hyperlink ref="A336" r:id="rId336" display="https://www.nyse.com/quote/XNYS:NKE" xr:uid="{51E41BF9-6561-C640-AA2B-E6EBD7B467CB}"/>
-    <hyperlink ref="A337" r:id="rId337" display="https://www.nyse.com/quote/XNYS:NOC" xr:uid="{673B6FA6-5BF0-AF43-A50D-7772F212DDC3}"/>
-    <hyperlink ref="A338" r:id="rId338" display="https://www.nyse.com/quote/XNYS:NOW" xr:uid="{0CB5C0A0-EC1C-1C4E-8D66-B2AE7BBF3D59}"/>
-    <hyperlink ref="A339" r:id="rId339" display="https://www.nyse.com/quote/XNYS:NRG" xr:uid="{C7BEBB70-B408-EF4C-8BA9-3D6CB46AD9CF}"/>
-    <hyperlink ref="A340" r:id="rId340" display="https://www.nyse.com/quote/XNYS:NSC" xr:uid="{CD96930B-072E-E844-811A-249A6DA5C326}"/>
-    <hyperlink ref="A341" r:id="rId341" display="https://www.nasdaq.com/market-activity/stocks/ntap" xr:uid="{2A3B7433-984B-7D47-B826-F1F28213F2F0}"/>
-    <hyperlink ref="A342" r:id="rId342" display="https://www.nasdaq.com/market-activity/stocks/ntrs" xr:uid="{EA91C089-90CB-964B-BED9-977AE8FB5E4C}"/>
-    <hyperlink ref="A343" r:id="rId343" display="https://www.nyse.com/quote/XNYS:NUE" xr:uid="{29160797-224B-4B49-A09D-90895CA06CBF}"/>
-    <hyperlink ref="A344" r:id="rId344" display="https://www.nasdaq.com/market-activity/stocks/nvda" xr:uid="{00EDF848-634D-1243-ACD2-C51EBB662BCC}"/>
-    <hyperlink ref="A345" r:id="rId345" display="https://www.nyse.com/quote/XNYS:NVR" xr:uid="{DE46C05A-7CFD-EA40-B96B-D3F147A06F0F}"/>
-    <hyperlink ref="A346" r:id="rId346" display="https://www.nasdaq.com/market-activity/stocks/nws" xr:uid="{7A68318A-E7FB-414C-B359-B2DFE8E761B7}"/>
-    <hyperlink ref="A347" r:id="rId347" display="https://www.nasdaq.com/market-activity/stocks/nwsa" xr:uid="{26AA625A-C7D1-2645-83FB-D2995369785B}"/>
-    <hyperlink ref="A348" r:id="rId348" display="https://www.nasdaq.com/market-activity/stocks/nxpi" xr:uid="{7A908892-CA73-D041-95C6-0BA3A4CBDB75}"/>
-    <hyperlink ref="A349" r:id="rId349" display="https://www.nyse.com/quote/XNYS:O" xr:uid="{64194E49-B52C-0E40-9736-ABD14914258E}"/>
-    <hyperlink ref="A350" r:id="rId350" display="https://www.nasdaq.com/market-activity/stocks/odfl" xr:uid="{2DF351DC-919C-9E4A-9B25-B355A1ABF765}"/>
-    <hyperlink ref="A351" r:id="rId351" display="https://www.nyse.com/quote/XNYS:OKE" xr:uid="{ACCDC40A-39DF-4B4E-885A-E5DB9EA79778}"/>
-    <hyperlink ref="A352" r:id="rId352" display="https://www.nyse.com/quote/XNYS:OMC" xr:uid="{9D3BA12C-AD43-B345-9428-6159BBA484E8}"/>
-    <hyperlink ref="A353" r:id="rId353" display="https://www.nasdaq.com/market-activity/stocks/on" xr:uid="{6FCD2D43-9E60-DB4E-9BCF-278E5BACA962}"/>
-    <hyperlink ref="A354" r:id="rId354" display="https://www.nyse.com/quote/XNYS:ORCL" xr:uid="{6650ACD3-70B5-764B-B034-8E079C47DE5D}"/>
-    <hyperlink ref="A355" r:id="rId355" display="https://www.nasdaq.com/market-activity/stocks/orly" xr:uid="{BB397E1B-8AC3-B746-8A0F-3A7D119AEF5F}"/>
-    <hyperlink ref="A356" r:id="rId356" display="https://www.nyse.com/quote/XNYS:OTIS" xr:uid="{6A3F311D-AC5B-EA42-B3F3-EF215E37EFF3}"/>
-    <hyperlink ref="A357" r:id="rId357" display="https://www.nyse.com/quote/XNYS:OXY" xr:uid="{223C80A3-C25C-D342-920F-DC7DAC10A41A}"/>
-    <hyperlink ref="A358" r:id="rId358" display="https://www.nasdaq.com/market-activity/stocks/panw" xr:uid="{C74FFFC5-890A-6041-BB2A-878F437E09CB}"/>
-    <hyperlink ref="A359" r:id="rId359" display="https://www.nyse.com/quote/XNYS:PAYC" xr:uid="{73CF1F60-1787-F640-BB3D-037D14785D05}"/>
-    <hyperlink ref="A360" r:id="rId360" display="https://www.nasdaq.com/market-activity/stocks/payx" xr:uid="{7A45CD7B-CF4C-AE42-A0B2-2ACDA23B6AE1}"/>
-    <hyperlink ref="A361" r:id="rId361" display="https://www.nasdaq.com/market-activity/stocks/pcar" xr:uid="{8AC4AA8B-5D83-D14E-9D68-14D25F056EB1}"/>
-    <hyperlink ref="A362" r:id="rId362" display="https://www.nyse.com/quote/XNYS:PCG" xr:uid="{31CE48C0-96F5-2B42-A147-E774DB1FEB21}"/>
-    <hyperlink ref="A363" r:id="rId363" display="https://www.nyse.com/quote/XNYS:PEG" xr:uid="{0181F50A-9BC8-BD47-9FED-ACB48FC274D3}"/>
-    <hyperlink ref="A364" r:id="rId364" display="https://www.nasdaq.com/market-activity/stocks/pep" xr:uid="{BBF934CA-544A-9B4D-95D7-D5CA9B686BC6}"/>
-    <hyperlink ref="A365" r:id="rId365" display="https://www.nyse.com/quote/XNYS:PFE" xr:uid="{AC4479DE-1F65-FD45-B0E4-51241E55DA26}"/>
-    <hyperlink ref="A366" r:id="rId366" display="https://www.nasdaq.com/market-activity/stocks/pfg" xr:uid="{EB33D14E-A995-DF40-9940-EAE060F12545}"/>
-    <hyperlink ref="A367" r:id="rId367" display="https://www.nyse.com/quote/XNYS:PG" xr:uid="{4AA10F2F-8D29-9741-9435-0A578BA8CEEB}"/>
-    <hyperlink ref="A368" r:id="rId368" display="https://www.nyse.com/quote/XNYS:PGR" xr:uid="{2BC8FCE8-6A3A-D141-8EED-1695EDD140EB}"/>
-    <hyperlink ref="A369" r:id="rId369" display="https://www.nyse.com/quote/XNYS:PH" xr:uid="{7FEEC2E0-DC80-B541-9681-F9A88D8DF38F}"/>
-    <hyperlink ref="A370" r:id="rId370" display="https://www.nyse.com/quote/XNYS:PHM" xr:uid="{59B89AAD-523D-354B-971F-7F4DEB59612F}"/>
-    <hyperlink ref="A371" r:id="rId371" display="https://www.nyse.com/quote/XNYS:PKG" xr:uid="{6EFABA88-3E93-CD41-9311-05B9914EE80C}"/>
-    <hyperlink ref="A372" r:id="rId372" display="https://www.nyse.com/quote/XNYS:PLD" xr:uid="{54A14D81-EDE2-C14F-9C8C-D1AF3B25A0E2}"/>
-    <hyperlink ref="A373" r:id="rId373" display="https://www.nasdaq.com/market-activity/stocks/pltr" xr:uid="{25A8858D-6FC1-954F-8A60-19C1A4EE7425}"/>
-    <hyperlink ref="A374" r:id="rId374" display="https://www.nyse.com/quote/XNYS:PM" xr:uid="{C51D4C9B-08A3-4645-997C-8087401C7C3E}"/>
-    <hyperlink ref="A375" r:id="rId375" display="https://www.nyse.com/quote/XNYS:PNC" xr:uid="{45243884-D508-F041-A73A-ABD2B824B033}"/>
-    <hyperlink ref="A376" r:id="rId376" display="https://www.nyse.com/quote/XNYS:PNR" xr:uid="{8CB75B72-1D75-CD46-942E-731B14558500}"/>
-    <hyperlink ref="A377" r:id="rId377" display="https://www.nyse.com/quote/XNYS:PNW" xr:uid="{2E3F0B32-E9E0-9342-9B0B-543547D2B104}"/>
-    <hyperlink ref="A378" r:id="rId378" display="https://www.nasdaq.com/market-activity/stocks/podd" xr:uid="{59547261-1063-5643-BE9B-6B90AF8718F5}"/>
-    <hyperlink ref="A379" r:id="rId379" display="https://www.nasdaq.com/market-activity/stocks/pool" xr:uid="{7AED7451-E319-7A47-89B8-C7AC16FDF835}"/>
-    <hyperlink ref="A380" r:id="rId380" display="https://www.nyse.com/quote/XNYS:PPG" xr:uid="{12ACB3B3-7CB1-8842-A32A-83E16ED1ECA5}"/>
-    <hyperlink ref="A381" r:id="rId381" display="https://www.nyse.com/quote/XNYS:PPL" xr:uid="{50FB6E58-182C-9147-A234-CDFAE5120F68}"/>
-    <hyperlink ref="A382" r:id="rId382" display="https://www.nyse.com/quote/XNYS:PRU" xr:uid="{F499D5D8-07FB-E746-B652-EECB695B47F5}"/>
-    <hyperlink ref="A383" r:id="rId383" display="https://www.nyse.com/quote/XNYS:PSA" xr:uid="{412D79F4-4EFB-9B49-AE4A-903DD04ADDF9}"/>
-    <hyperlink ref="A384" r:id="rId384" display="https://www.nasdaq.com/market-activity/stocks/psky" xr:uid="{6E7207B9-8691-354E-B1E6-3F1A6EF171F8}"/>
-    <hyperlink ref="A385" r:id="rId385" display="https://www.nyse.com/quote/XNYS:PSX" xr:uid="{540B3689-0943-6B42-B53F-AB008F94EBCA}"/>
-    <hyperlink ref="A386" r:id="rId386" display="https://www.nasdaq.com/market-activity/stocks/ptc" xr:uid="{11BE4660-B1AD-5540-93E1-5B0D86C9063E}"/>
-    <hyperlink ref="A387" r:id="rId387" display="https://www.nyse.com/quote/XNYS:PWR" xr:uid="{474D7B04-4975-264F-AC80-9EB6A2642100}"/>
-    <hyperlink ref="A388" r:id="rId388" display="https://www.nasdaq.com/market-activity/stocks/pypl" xr:uid="{F5A5FA8E-D374-E147-8814-77C7CF60EE66}"/>
-    <hyperlink ref="A389" r:id="rId389" display="https://www.nasdaq.com/market-activity/stocks/qcom" xr:uid="{3683E370-F1C7-B14A-952A-5F6111E423D2}"/>
-    <hyperlink ref="A390" r:id="rId390" display="https://www.nyse.com/quote/XNYS:RCL" xr:uid="{1D9580F0-A17B-CF47-A212-39CDA74FFDAF}"/>
-    <hyperlink ref="A391" r:id="rId391" display="https://www.nasdaq.com/market-activity/stocks/reg" xr:uid="{B531B822-790A-B44D-862F-685207AB4763}"/>
-    <hyperlink ref="A392" r:id="rId392" display="https://www.nasdaq.com/market-activity/stocks/regn" xr:uid="{0AD97215-0E80-8F46-BCF8-BBA0B579CB0A}"/>
-    <hyperlink ref="A393" r:id="rId393" display="https://www.nyse.com/quote/XNYS:RF" xr:uid="{F91C5F26-65E9-2842-B7E7-A76ACEA43D58}"/>
-    <hyperlink ref="A394" r:id="rId394" display="https://www.nyse.com/quote/XNYS:RJF" xr:uid="{58FD82DA-CD15-3546-9F6A-5DAA847B715C}"/>
-    <hyperlink ref="A395" r:id="rId395" display="https://www.nyse.com/quote/XNYS:RL" xr:uid="{1F304E82-855B-7B42-BCC2-9EAD9E098BE5}"/>
-    <hyperlink ref="A396" r:id="rId396" display="https://www.nyse.com/quote/XNYS:RMD" xr:uid="{29A22279-3C29-9C4A-A98A-91AB973430B8}"/>
-    <hyperlink ref="A397" r:id="rId397" display="https://www.nyse.com/quote/XNYS:ROK" xr:uid="{48275E37-EBC2-9C44-A8EA-00CF08B82460}"/>
-    <hyperlink ref="A398" r:id="rId398" display="https://www.nyse.com/quote/XNYS:ROL" xr:uid="{8D1278D7-9D6E-A64A-A937-291FF9A471BD}"/>
-    <hyperlink ref="A399" r:id="rId399" display="https://www.nasdaq.com/market-activity/stocks/rop" xr:uid="{43CA0BA5-951E-DA43-8603-EDF34D2E3985}"/>
-    <hyperlink ref="A400" r:id="rId400" display="https://www.nasdaq.com/market-activity/stocks/rost" xr:uid="{C4241395-ADB8-5643-B503-67B37274C40F}"/>
-    <hyperlink ref="A401" r:id="rId401" display="https://www.nyse.com/quote/XNYS:RSG" xr:uid="{CBDDD170-B44B-0946-9552-A88785EC264A}"/>
-    <hyperlink ref="A402" r:id="rId402" display="https://www.nyse.com/quote/XNYS:RTX" xr:uid="{230AEFE9-336A-F44B-A87E-1FBA4125679A}"/>
-    <hyperlink ref="A403" r:id="rId403" display="https://www.nyse.com/quote/XNYS:RVTY" xr:uid="{1535D3B2-02C5-7141-A7B1-0BA338DA4487}"/>
-    <hyperlink ref="A404" r:id="rId404" display="https://www.nasdaq.com/market-activity/stocks/sbac" xr:uid="{EA77769C-6370-4846-A531-A1C7AC2C1813}"/>
-    <hyperlink ref="A405" r:id="rId405" display="https://www.nasdaq.com/market-activity/stocks/sbux" xr:uid="{C04F909C-8C9B-F946-8F4A-99C44F9E5C62}"/>
-    <hyperlink ref="A406" r:id="rId406" display="https://www.nyse.com/quote/XNYS:SCHW" xr:uid="{F73D3882-5566-E34D-B394-F29CFB36C5E1}"/>
-    <hyperlink ref="A407" r:id="rId407" display="https://www.nyse.com/quote/XNYS:SHW" xr:uid="{2319F657-8B22-AF4A-9F01-68B3130AFEDD}"/>
-    <hyperlink ref="A408" r:id="rId408" display="https://www.nyse.com/quote/XNYS:SJM" xr:uid="{84052077-6FD1-BE46-B339-AA730EC19491}"/>
-    <hyperlink ref="A409" r:id="rId409" display="https://www.nyse.com/quote/XNYS:SLB" xr:uid="{115196AE-69B2-D349-BC13-69C91ADB7D02}"/>
-    <hyperlink ref="A410" r:id="rId410" display="https://www.nasdaq.com/market-activity/stocks/smci" xr:uid="{70AEFB4B-C40B-3F45-9F23-2B84EA841436}"/>
-    <hyperlink ref="A411" r:id="rId411" display="https://www.nyse.com/quote/XNYS:SNA" xr:uid="{BD999369-3A61-0A4C-AF07-99F5E562CACD}"/>
-    <hyperlink ref="A412" r:id="rId412" display="https://www.nasdaq.com/market-activity/stocks/snps" xr:uid="{B789E079-4FA0-2C4F-96BE-B7B6BDDD4B44}"/>
-    <hyperlink ref="A413" r:id="rId413" display="https://www.nyse.com/quote/XNYS:SO" xr:uid="{A265E65E-2BEC-B84C-A284-5D75FED9B5E9}"/>
-    <hyperlink ref="A414" r:id="rId414" display="https://www.nyse.com/quote/XNYS:SOLV" xr:uid="{7DA098B0-013F-8543-BEBE-41A6070E3BF7}"/>
-    <hyperlink ref="A415" r:id="rId415" display="https://www.nyse.com/quote/XNYS:SPG" xr:uid="{D6BD4164-C990-A54A-BF57-85F9187405A4}"/>
-    <hyperlink ref="A416" r:id="rId416" display="https://www.nyse.com/quote/XNYS:SPGI" xr:uid="{365E02CF-97ED-3D4E-9AF4-AF471B5A3285}"/>
-    <hyperlink ref="A417" r:id="rId417" display="https://www.nyse.com/quote/XNYS:SRE" xr:uid="{32CCF3B0-4659-0042-9791-99EDA13C29A1}"/>
-    <hyperlink ref="A418" r:id="rId418" display="https://www.nyse.com/quote/XNYS:STE" xr:uid="{11CE0A88-1B14-5940-8FB5-39067BCEF193}"/>
-    <hyperlink ref="A419" r:id="rId419" display="https://www.nasdaq.com/market-activity/stocks/stld" xr:uid="{C8108F33-0609-B14A-9FEE-1148858343A1}"/>
-    <hyperlink ref="A420" r:id="rId420" display="https://www.nyse.com/quote/XNYS:STT" xr:uid="{30A9E47C-296B-2946-8CD3-00F44A902325}"/>
-    <hyperlink ref="A421" r:id="rId421" display="https://www.nasdaq.com/market-activity/stocks/stx" xr:uid="{477CB993-0E78-CC41-88AD-4859CB6337BB}"/>
-    <hyperlink ref="A422" r:id="rId422" display="https://www.nyse.com/quote/XNYS:STZ" xr:uid="{B65533BB-CA59-EC43-BFF7-17ACBC00936B}"/>
-    <hyperlink ref="A423" r:id="rId423" display="https://www.nyse.com/quote/XNYS:SW" xr:uid="{D2CE511A-81F3-7B4A-9648-FB7F6894154D}"/>
-    <hyperlink ref="A424" r:id="rId424" display="https://www.nyse.com/quote/XNYS:SWK" xr:uid="{E26635CF-F976-994B-A9A9-759633920910}"/>
-    <hyperlink ref="A425" r:id="rId425" display="https://www.nasdaq.com/market-activity/stocks/swks" xr:uid="{119C63C9-D252-5042-B65C-23F5F2EA97B6}"/>
-    <hyperlink ref="A426" r:id="rId426" display="https://www.nyse.com/quote/XNYS:SYF" xr:uid="{2D97F9D1-1A7F-074A-9CEF-FF6082B34D73}"/>
-    <hyperlink ref="A427" r:id="rId427" display="https://www.nyse.com/quote/XNYS:SYK" xr:uid="{0CB8B011-8989-8A4B-A204-AE19278C6E77}"/>
-    <hyperlink ref="A428" r:id="rId428" display="https://www.nyse.com/quote/XNYS:SYY" xr:uid="{98D51620-0F5F-804D-AD83-EC17621393CA}"/>
-    <hyperlink ref="A429" r:id="rId429" display="https://www.nyse.com/quote/XNYS:T" xr:uid="{D8AC89AF-F728-D444-8615-F38485B0A219}"/>
-    <hyperlink ref="A430" r:id="rId430" display="https://www.nyse.com/quote/XNYS:TAP" xr:uid="{4E851D3E-D35F-6B4E-A433-2C8FF7D325EB}"/>
-    <hyperlink ref="A431" r:id="rId431" display="https://www.nyse.com/quote/XNYS:TDG" xr:uid="{6385F45E-A51A-804C-BB97-7CD4205E1C11}"/>
-    <hyperlink ref="A432" r:id="rId432" display="https://www.nyse.com/quote/XNYS:TDY" xr:uid="{38FC32F0-F2CB-FF46-8534-0EB0F10A27F2}"/>
-    <hyperlink ref="A433" r:id="rId433" display="https://www.nasdaq.com/market-activity/stocks/tech" xr:uid="{45CBF9CD-0549-1D41-9456-62CC6A323E0B}"/>
-    <hyperlink ref="A434" r:id="rId434" display="https://www.nyse.com/quote/XNYS:TEL" xr:uid="{015362E5-9175-474B-896D-F70BFB46047D}"/>
-    <hyperlink ref="A435" r:id="rId435" display="https://www.nasdaq.com/market-activity/stocks/ter" xr:uid="{BC42B90F-670B-5148-ACA7-038894EC2A7F}"/>
-    <hyperlink ref="A436" r:id="rId436" display="https://www.nyse.com/quote/XNYS:TFC" xr:uid="{66F2C9B5-0F6E-1E43-9B9B-E8E56B88BD89}"/>
-    <hyperlink ref="A437" r:id="rId437" display="https://www.nyse.com/quote/XNYS:TGT" xr:uid="{3CCB3AFC-A781-7541-8E3D-29845A2A385E}"/>
-    <hyperlink ref="A438" r:id="rId438" display="https://www.nyse.com/quote/XNYS:TJX" xr:uid="{326522C3-0D67-8344-8441-47DA73CF70AD}"/>
-    <hyperlink ref="A439" r:id="rId439" display="https://www.nyse.com/quote/XNYS:TKO" xr:uid="{FEC6F21B-E71C-4C4A-8116-76CA45A1A609}"/>
-    <hyperlink ref="A440" r:id="rId440" display="https://www.nyse.com/quote/XNYS:TMO" xr:uid="{44119C58-7762-BA4B-A43D-BBF5A4FC781C}"/>
-    <hyperlink ref="A441" r:id="rId441" display="https://www.nasdaq.com/market-activity/stocks/tmus" xr:uid="{F82D2EA0-4DB4-0544-A76C-6F4244932848}"/>
-    <hyperlink ref="A442" r:id="rId442" display="https://www.nyse.com/quote/XNYS:TPL" xr:uid="{F5ECC46D-281F-5446-A3F9-2807B71FD2A1}"/>
-    <hyperlink ref="A443" r:id="rId443" display="https://www.nyse.com/quote/XNYS:TPR" xr:uid="{A57582FE-7F2E-F541-BE08-96D1E226164A}"/>
-    <hyperlink ref="A444" r:id="rId444" display="https://www.nyse.com/quote/XNYS:TRGP" xr:uid="{06405C4F-9682-BF4E-AC0D-D0AF7A5C2CD5}"/>
-    <hyperlink ref="A445" r:id="rId445" display="https://www.nasdaq.com/market-activity/stocks/trmb" xr:uid="{FD690395-07F1-5041-9969-2064595982BA}"/>
-    <hyperlink ref="A446" r:id="rId446" display="https://www.nasdaq.com/market-activity/stocks/trow" xr:uid="{92D8EC19-5007-A14F-80B3-F864823A989A}"/>
-    <hyperlink ref="A447" r:id="rId447" display="https://www.nyse.com/quote/XNYS:TRV" xr:uid="{A94E092B-770D-1C46-B88B-48A60D40BE22}"/>
-    <hyperlink ref="A448" r:id="rId448" display="https://www.nasdaq.com/market-activity/stocks/tsco" xr:uid="{9F526E21-BEF4-5B44-894A-EA4AEF4F1F98}"/>
-    <hyperlink ref="A449" r:id="rId449" display="https://www.nasdaq.com/market-activity/stocks/tsla" xr:uid="{90610183-CCAC-B945-8296-2EBF13E1D77F}"/>
-    <hyperlink ref="A450" r:id="rId450" display="https://www.nyse.com/quote/XNYS:TSN" xr:uid="{F8D8B973-3B1C-4C4A-B1DD-E2313DBD0D63}"/>
-    <hyperlink ref="A451" r:id="rId451" display="https://www.nyse.com/quote/XNYS:TT" xr:uid="{F950DB78-F0F1-F54C-995D-DD333FF97EEA}"/>
-    <hyperlink ref="A452" r:id="rId452" display="https://www.nasdaq.com/market-activity/stocks/ttd" xr:uid="{B92C0FA0-114B-7343-BBDD-4C334AEE8A1C}"/>
-    <hyperlink ref="A453" r:id="rId453" display="https://www.nasdaq.com/market-activity/stocks/ttwo" xr:uid="{8BE81D07-A79D-974A-AF48-8428DF63B55E}"/>
-    <hyperlink ref="A454" r:id="rId454" display="https://www.nasdaq.com/market-activity/stocks/txn" xr:uid="{514A0DEB-5454-C448-B03F-CC4B5F983BB2}"/>
-    <hyperlink ref="A455" r:id="rId455" display="https://www.nyse.com/quote/XNYS:TXT" xr:uid="{3FF8A7BB-DD6B-0240-B382-44B01BD0BB2E}"/>
-    <hyperlink ref="A456" r:id="rId456" display="https://www.nyse.com/quote/XNYS:TYL" xr:uid="{8181ED24-2A5D-8145-A632-8685D25CF5E5}"/>
-    <hyperlink ref="A457" r:id="rId457" display="https://www.nasdaq.com/market-activity/stocks/ual" xr:uid="{9DF39175-306C-5C46-BD98-1133CB8462F8}"/>
-    <hyperlink ref="A458" r:id="rId458" display="https://www.nyse.com/quote/XNYS:UBER" xr:uid="{3509005C-1E6F-3F4E-8217-E3613AC9A93F}"/>
-    <hyperlink ref="A459" r:id="rId459" display="https://www.nyse.com/quote/XNYS:UDR" xr:uid="{151904FD-DD6F-C14D-AEFB-EB434B9AA24B}"/>
-    <hyperlink ref="A460" r:id="rId460" display="https://www.nyse.com/quote/XNYS:UHS" xr:uid="{C917854D-A741-B94A-B1C2-03C2A7909C14}"/>
-    <hyperlink ref="A461" r:id="rId461" display="https://www.nasdaq.com/market-activity/stocks/ulta" xr:uid="{299089E8-C8BD-1E42-9024-5486058140FA}"/>
-    <hyperlink ref="A462" r:id="rId462" display="https://www.nyse.com/quote/XNYS:UNH" xr:uid="{A1C206DE-9261-B845-93B4-9ABA0ADE6858}"/>
-    <hyperlink ref="A463" r:id="rId463" display="https://www.nyse.com/quote/XNYS:UNP" xr:uid="{035BDF58-CF4B-DE44-9A14-180A583C064F}"/>
-    <hyperlink ref="A464" r:id="rId464" display="https://www.nyse.com/quote/XNYS:UPS" xr:uid="{7F4CCF1F-47FA-584C-9721-511CB13DE421}"/>
-    <hyperlink ref="A465" r:id="rId465" display="https://www.nyse.com/quote/XNYS:URI" xr:uid="{CAA81F55-033A-4043-BC42-CA9DA73E7D18}"/>
-    <hyperlink ref="A466" r:id="rId466" display="https://www.nyse.com/quote/XNYS:USB" xr:uid="{7CACE059-0AFC-F74E-8646-A4FEC5CA65E6}"/>
-    <hyperlink ref="A467" r:id="rId467" display="https://www.nyse.com/quote/XNYS:V" xr:uid="{66E2069E-A0CC-D84C-B9CE-BF935B098497}"/>
-    <hyperlink ref="A468" r:id="rId468" display="https://www.nyse.com/quote/XNYS:VICI" xr:uid="{6D983B57-D687-2D4F-842E-556846218726}"/>
-    <hyperlink ref="A469" r:id="rId469" display="https://www.nyse.com/quote/XNYS:VLO" xr:uid="{AA9DB606-A74E-4545-ADFE-28D51336525C}"/>
-    <hyperlink ref="A470" r:id="rId470" display="https://www.nyse.com/quote/XNYS:VLTO" xr:uid="{FA599649-9AE5-2D46-9409-EEF26812BA58}"/>
-    <hyperlink ref="A471" r:id="rId471" display="https://www.nyse.com/quote/XNYS:VMC" xr:uid="{547C92E6-7C83-6140-8996-A7F95A8F8AD1}"/>
-    <hyperlink ref="A472" r:id="rId472" display="https://www.nasdaq.com/market-activity/stocks/vrsk" xr:uid="{FAE7572D-E22E-194C-B3F4-AAC47347EDF8}"/>
-    <hyperlink ref="A473" r:id="rId473" display="https://www.nasdaq.com/market-activity/stocks/vrsn" xr:uid="{D19C4FB1-79C2-2542-8C0B-1F2970198627}"/>
-    <hyperlink ref="A474" r:id="rId474" display="https://www.nasdaq.com/market-activity/stocks/vrtx" xr:uid="{CBEE8C1F-F62B-5040-B75A-2C6721FB8C9E}"/>
-    <hyperlink ref="A475" r:id="rId475" display="https://www.nyse.com/quote/XNYS:VST" xr:uid="{69EC6E5C-0119-0E44-A787-341AE60E41DE}"/>
-    <hyperlink ref="A476" r:id="rId476" display="https://www.nyse.com/quote/XNYS:VTR" xr:uid="{4D1C01A6-517C-9F4B-994E-20C9E79D56D6}"/>
-    <hyperlink ref="A477" r:id="rId477" display="https://www.nasdaq.com/market-activity/stocks/vtrs" xr:uid="{BF403597-40E8-5549-80BB-15C1971E17FA}"/>
-    <hyperlink ref="A478" r:id="rId478" display="https://www.nyse.com/quote/XNYS:VZ" xr:uid="{FFEC42CC-8A87-D041-BE64-248BE672BA39}"/>
-    <hyperlink ref="A479" r:id="rId479" display="https://www.nyse.com/quote/XNYS:WAB" xr:uid="{25FD60BD-1981-0C4F-A440-AAECE557BF1C}"/>
-    <hyperlink ref="A480" r:id="rId480" display="https://www.nyse.com/quote/XNYS:WAT" xr:uid="{F9A01575-C6E9-D148-8692-8CE5532183ED}"/>
-    <hyperlink ref="A481" r:id="rId481" display="https://www.nasdaq.com/market-activity/stocks/wbd" xr:uid="{9A855483-CDE6-6E42-BF09-E31D9378598F}"/>
-    <hyperlink ref="A482" r:id="rId482" display="https://www.nasdaq.com/market-activity/stocks/wday" xr:uid="{0B799925-7FE9-2945-94B0-16C9A8623ABE}"/>
-    <hyperlink ref="A483" r:id="rId483" display="https://www.nasdaq.com/market-activity/stocks/wdc" xr:uid="{086D84EB-FC9E-4440-990C-C68E24B33C92}"/>
-    <hyperlink ref="A484" r:id="rId484" display="https://www.nyse.com/quote/XNYS:WEC" xr:uid="{CD7D8F22-2C69-BF40-B1FC-0638A0EEE480}"/>
-    <hyperlink ref="A485" r:id="rId485" display="https://www.nyse.com/quote/XNYS:WELL" xr:uid="{869E26E2-6627-A946-A4C0-6B933AACDCB0}"/>
-    <hyperlink ref="A486" r:id="rId486" display="https://www.nyse.com/quote/XNYS:WFC" xr:uid="{C45B53AC-8DBF-A741-A3D7-64E59BB411D7}"/>
-    <hyperlink ref="A487" r:id="rId487" display="https://www.nyse.com/quote/XNYS:WM" xr:uid="{91263B3B-11D1-8744-B58D-1D002CC4132D}"/>
-    <hyperlink ref="A488" r:id="rId488" display="https://www.nyse.com/quote/XNYS:WMB" xr:uid="{0DC9BCC9-05CD-E042-A049-B7E97F9B50AB}"/>
-    <hyperlink ref="A489" r:id="rId489" display="https://www.nyse.com/quote/XNYS:WMT" xr:uid="{AE76A7D4-679D-E14F-BD69-7AE9377D70CE}"/>
-    <hyperlink ref="A490" r:id="rId490" display="https://www.nyse.com/quote/XNYS:WRB" xr:uid="{5C8B1965-E00E-1443-B5AF-320056228ECC}"/>
-    <hyperlink ref="A491" r:id="rId491" display="https://www.nyse.com/quote/XNYS:WSM" xr:uid="{C2A76827-202E-D043-919D-B74D9441D3F8}"/>
-    <hyperlink ref="A492" r:id="rId492" display="https://www.nyse.com/quote/XNYS:WST" xr:uid="{0B0C9A82-BEAA-7843-94A0-805BE457D650}"/>
-    <hyperlink ref="A493" r:id="rId493" display="https://www.nasdaq.com/market-activity/stocks/wtw" xr:uid="{D575DCD3-10C1-B44B-867A-E7561727D894}"/>
-    <hyperlink ref="A494" r:id="rId494" display="https://www.nyse.com/quote/XNYS:WY" xr:uid="{901E02A3-E66B-1C4F-A7D1-D1E5C98E79C1}"/>
-    <hyperlink ref="A495" r:id="rId495" display="https://www.nasdaq.com/market-activity/stocks/wynn" xr:uid="{84EAA1BA-4503-5B4A-8D1C-EB9A8B2AAF48}"/>
-    <hyperlink ref="A496" r:id="rId496" display="https://www.nasdaq.com/market-activity/stocks/xel" xr:uid="{3039DC1C-9293-5745-BDF6-E28813D326E3}"/>
-    <hyperlink ref="A497" r:id="rId497" display="https://www.nyse.com/quote/XNYS:XOM" xr:uid="{4381D83F-072F-D445-9970-7A5D080B3392}"/>
-    <hyperlink ref="A498" r:id="rId498" display="https://www.nyse.com/quote/XNYS:XYL" xr:uid="{7DBC3674-102C-FC4D-9524-3235BC4C07BF}"/>
-    <hyperlink ref="A499" r:id="rId499" display="https://www.nyse.com/quote/XNYS:XYZ" xr:uid="{CECAEB1E-7E6F-E04D-92AA-033A447D3422}"/>
-    <hyperlink ref="A500" r:id="rId500" display="https://www.nyse.com/quote/XNYS:YUM" xr:uid="{571A9ABA-21B7-4E4A-AD5B-6FAC7A4E1F8D}"/>
-    <hyperlink ref="A501" r:id="rId501" display="https://www.nyse.com/quote/XNYS:ZBH" xr:uid="{C55C9A5D-20B5-D548-8294-5BC41F389A3D}"/>
-    <hyperlink ref="A502" r:id="rId502" display="https://www.nasdaq.com/market-activity/stocks/zbra" xr:uid="{BE080523-C33B-4D49-8565-61BD021FE9BD}"/>
-    <hyperlink ref="A503" r:id="rId503" display="https://www.nyse.com/quote/XNYS:ZTS" xr:uid="{044421C5-379D-3240-BC5B-752DAFF94FD9}"/>
+    <hyperlink ref="A2" r:id="rId1" display="https://www.nyse.com/quote/XNYS:A" xr:uid="{B677E7E2-D9A0-484D-AEBE-207B88E9E360}"/>
+    <hyperlink ref="A3" r:id="rId2" display="https://www.nasdaq.com/market-activity/stocks/aapl" xr:uid="{7DE6A81F-4C0C-2442-90EE-B0DC994F65DC}"/>
+    <hyperlink ref="A4" r:id="rId3" display="https://www.nyse.com/quote/XNYS:ABBV" xr:uid="{707B21A3-7AC5-F844-8283-80373766D5DD}"/>
+    <hyperlink ref="A5" r:id="rId4" display="https://www.nasdaq.com/market-activity/stocks/abnb" xr:uid="{D0CE58CB-6CE5-7F41-93F9-C2A93FE21B5D}"/>
+    <hyperlink ref="A6" r:id="rId5" display="https://www.nyse.com/quote/XNYS:ABT" xr:uid="{FEF90C77-2BFC-C349-BCBE-6FF80C8C38EE}"/>
+    <hyperlink ref="A7" r:id="rId6" display="https://www.nasdaq.com/market-activity/stocks/acgl" xr:uid="{86EB05E8-6F5A-4B4A-88AB-8736D053F62F}"/>
+    <hyperlink ref="A8" r:id="rId7" display="https://www.nyse.com/quote/XNYS:ACN" xr:uid="{206D1A09-61A0-FE4E-BE76-3950E0FFD219}"/>
+    <hyperlink ref="A9" r:id="rId8" display="https://www.nasdaq.com/market-activity/stocks/adbe" xr:uid="{D8F512C1-9031-D34F-A396-636D6EBC2CF4}"/>
+    <hyperlink ref="A10" r:id="rId9" display="https://www.nasdaq.com/market-activity/stocks/adi" xr:uid="{D9823A54-00AC-8F43-8405-494BB7E9B44E}"/>
+    <hyperlink ref="A11" r:id="rId10" display="https://www.nyse.com/quote/XNYS:ADM" xr:uid="{8DC53D66-2713-8B49-B853-63A8FCCA9126}"/>
+    <hyperlink ref="A12" r:id="rId11" display="https://www.nasdaq.com/market-activity/stocks/adp" xr:uid="{91EBE334-83F2-BA47-A1C7-BAF01F975088}"/>
+    <hyperlink ref="A13" r:id="rId12" display="https://www.nasdaq.com/market-activity/stocks/adsk" xr:uid="{D8C9118C-21E3-4249-AD03-95CE80DD109B}"/>
+    <hyperlink ref="A14" r:id="rId13" display="https://www.nyse.com/quote/XNYS:AEE" xr:uid="{AAA5D011-8033-AA4D-B7AC-3993C94805BB}"/>
+    <hyperlink ref="A15" r:id="rId14" display="https://www.nasdaq.com/market-activity/stocks/aep" xr:uid="{F6E4922F-DB65-4340-99EC-B16C5E0C4A62}"/>
+    <hyperlink ref="A16" r:id="rId15" display="https://www.nyse.com/quote/XNYS:AES" xr:uid="{2630E663-8BA5-D341-B229-275D211D791F}"/>
+    <hyperlink ref="A17" r:id="rId16" display="https://www.nyse.com/quote/XNYS:AFL" xr:uid="{878DBBC2-9931-DF46-AB3D-A33E271012A2}"/>
+    <hyperlink ref="A18" r:id="rId17" display="https://www.nyse.com/quote/XNYS:AIG" xr:uid="{35A39E0B-AD34-A743-86F3-38EE69C6C499}"/>
+    <hyperlink ref="A19" r:id="rId18" display="https://www.nyse.com/quote/XNYS:AIZ" xr:uid="{918BA76D-75FF-D94E-A2B9-B64D2F696416}"/>
+    <hyperlink ref="A20" r:id="rId19" display="https://www.nyse.com/quote/XNYS:AJG" xr:uid="{127B7D18-5DAE-C744-B072-03E0AEB25E5A}"/>
+    <hyperlink ref="A21" r:id="rId20" display="https://www.nasdaq.com/market-activity/stocks/akam" xr:uid="{959EDF9B-5B96-DB41-9809-5DFD91DC9105}"/>
+    <hyperlink ref="A22" r:id="rId21" display="https://www.nyse.com/quote/XNYS:ALB" xr:uid="{2E54EF01-4A06-4A4B-B67B-C5D76C6C1807}"/>
+    <hyperlink ref="A23" r:id="rId22" display="https://www.nasdaq.com/market-activity/stocks/algn" xr:uid="{5802A803-5C11-804B-9377-9884F56CB365}"/>
+    <hyperlink ref="A24" r:id="rId23" display="https://www.nyse.com/quote/XNYS:ALL" xr:uid="{B4FD8F12-052A-354C-9461-040431CB289A}"/>
+    <hyperlink ref="A25" r:id="rId24" display="https://www.nyse.com/quote/XNYS:ALLE" xr:uid="{A977F9BC-11F3-9141-B044-C5040F14152D}"/>
+    <hyperlink ref="A26" r:id="rId25" display="https://www.nasdaq.com/market-activity/stocks/amat" xr:uid="{7B29B435-FC6C-7448-9ADB-2ED6F4F7CC93}"/>
+    <hyperlink ref="A27" r:id="rId26" display="https://www.nyse.com/quote/XNYS:AMCR" xr:uid="{5E0C4903-FD03-9149-A61A-4E3BEC1113C1}"/>
+    <hyperlink ref="A28" r:id="rId27" display="https://www.nasdaq.com/market-activity/stocks/amd" xr:uid="{E8D094F5-BCDF-204F-B52C-A2B1DB34373A}"/>
+    <hyperlink ref="A29" r:id="rId28" display="https://www.nyse.com/quote/XNYS:AME" xr:uid="{9178BCA7-072F-A04B-9765-FDB1E68CFE76}"/>
+    <hyperlink ref="A30" r:id="rId29" display="https://www.nasdaq.com/market-activity/stocks/amgn" xr:uid="{5FB436CA-6101-CB4F-9297-17A9E7FA04CA}"/>
+    <hyperlink ref="A31" r:id="rId30" display="https://www.nyse.com/quote/XNYS:AMP" xr:uid="{A0E0B85B-0761-874C-8164-3E63E14B4D7E}"/>
+    <hyperlink ref="A32" r:id="rId31" display="https://www.nyse.com/quote/XNYS:AMT" xr:uid="{207965AF-2F4D-4F41-9382-404B67F58EA5}"/>
+    <hyperlink ref="A33" r:id="rId32" display="https://www.nasdaq.com/market-activity/stocks/amzn" xr:uid="{C0C3A928-E8CD-1344-9E9C-5F58FC88B2A6}"/>
+    <hyperlink ref="A34" r:id="rId33" display="https://www.nyse.com/quote/XNYS:ANET" xr:uid="{447B8518-A380-7645-81DE-D503DFE6D626}"/>
+    <hyperlink ref="A35" r:id="rId34" display="https://www.nyse.com/quote/XNYS:AON" xr:uid="{56C12CB8-3952-0240-97DF-FF77245D0D07}"/>
+    <hyperlink ref="A36" r:id="rId35" display="https://www.nyse.com/quote/XNYS:AOS" xr:uid="{8D913B35-64EE-4745-9861-E87D637F74B2}"/>
+    <hyperlink ref="A37" r:id="rId36" display="https://www.nasdaq.com/market-activity/stocks/apa" xr:uid="{2A534FB8-27D8-3D43-9EDC-8202B95E29FC}"/>
+    <hyperlink ref="A38" r:id="rId37" display="https://www.nyse.com/quote/XNYS:APD" xr:uid="{F27E7B99-FD07-4347-AED3-C2F60580A039}"/>
+    <hyperlink ref="A39" r:id="rId38" display="https://www.nyse.com/quote/XNYS:APH" xr:uid="{AFCD0056-A16B-8748-819C-8B811AE927EA}"/>
+    <hyperlink ref="A40" r:id="rId39" display="https://www.nyse.com/quote/XNYS:APO" xr:uid="{8EA4193A-0E89-4E49-88C3-00187C8B9B4A}"/>
+    <hyperlink ref="A41" r:id="rId40" display="https://www.nasdaq.com/market-activity/stocks/app" xr:uid="{7DA33E09-14F5-094B-9BC0-8B01746DA9D5}"/>
+    <hyperlink ref="A42" r:id="rId41" display="https://www.nyse.com/quote/XNYS:APTV" xr:uid="{9F123F4D-D4F0-E94A-A025-887D01818887}"/>
+    <hyperlink ref="A43" r:id="rId42" display="https://www.nyse.com/quote/XNYS:ARE" xr:uid="{7BF28F6A-FEE8-9D4B-AEB7-58C25CAF2C41}"/>
+    <hyperlink ref="A44" r:id="rId43" display="https://www.nyse.com/quote/XNYS:ATO" xr:uid="{5E3A94FB-9A80-9641-870E-55CD3B11C526}"/>
+    <hyperlink ref="A45" r:id="rId44" display="https://www.nyse.com/quote/XNYS:AVB" xr:uid="{72CC2DA4-C76E-B049-98BA-6B1CD0EF9E57}"/>
+    <hyperlink ref="A46" r:id="rId45" display="https://www.nasdaq.com/market-activity/stocks/avgo" xr:uid="{ABB2F68A-74D6-C44F-9E6D-D73FB4148AC2}"/>
+    <hyperlink ref="A47" r:id="rId46" display="https://www.nyse.com/quote/XNYS:AVY" xr:uid="{B3AC83C9-D20E-974A-AE30-404704C3BE4A}"/>
+    <hyperlink ref="A48" r:id="rId47" display="https://www.nyse.com/quote/XNYS:AWK" xr:uid="{D572A379-C1CC-7E4A-883E-AA0E3FA1126A}"/>
+    <hyperlink ref="A49" r:id="rId48" display="https://www.nasdaq.com/market-activity/stocks/axon" xr:uid="{5354A9C1-D9FF-8245-9263-52D99C6505AD}"/>
+    <hyperlink ref="A50" r:id="rId49" display="https://www.nyse.com/quote/XNYS:AXP" xr:uid="{DC6E6818-1A9D-6C40-BCAF-6F92E156C471}"/>
+    <hyperlink ref="A51" r:id="rId50" display="https://www.nyse.com/quote/XNYS:AZO" xr:uid="{150D9E7A-5F8E-EF47-8C3E-191467171DBE}"/>
+    <hyperlink ref="A52" r:id="rId51" display="https://www.nyse.com/quote/XNYS:BA" xr:uid="{4873D06A-7B6D-5F43-989B-8774E906E0E6}"/>
+    <hyperlink ref="A53" r:id="rId52" display="https://www.nyse.com/quote/XNYS:BAC" xr:uid="{4FB67CCF-7F84-E846-88C2-A91A5751B14A}"/>
+    <hyperlink ref="A54" r:id="rId53" display="https://www.nyse.com/quote/XNYS:BALL" xr:uid="{8DFFD3A5-C6DE-FE45-83BF-BA84DD058AB3}"/>
+    <hyperlink ref="A55" r:id="rId54" display="https://www.nyse.com/quote/XNYS:BAX" xr:uid="{D5EB5288-4DBB-9F4A-8AEB-2AD77A47187B}"/>
+    <hyperlink ref="A56" r:id="rId55" display="https://www.nyse.com/quote/XNYS:BBY" xr:uid="{0AA0FDDA-A7C3-FA48-9300-966B20B9B85B}"/>
+    <hyperlink ref="A57" r:id="rId56" display="https://www.nyse.com/quote/XNYS:BDX" xr:uid="{29B439C9-32A0-E44E-B5DE-F7D0BF6230C3}"/>
+    <hyperlink ref="A58" r:id="rId57" display="https://www.nyse.com/quote/XNYS:BEN" xr:uid="{3A728722-A2E9-C442-982C-0AAA6BC8637C}"/>
+    <hyperlink ref="A59" r:id="rId58" display="https://www.nyse.com/quote/XNYS:BF.B" xr:uid="{1B9D3613-9B18-2146-90A5-7AC6BE70550A}"/>
+    <hyperlink ref="A60" r:id="rId59" display="https://www.nyse.com/quote/XNYS:BG" xr:uid="{CA83E031-A192-CE40-A12A-4E7D68E621D4}"/>
+    <hyperlink ref="A61" r:id="rId60" display="https://www.nasdaq.com/market-activity/stocks/biib" xr:uid="{61DBF511-0695-A94C-8B54-BECC3DC91B63}"/>
+    <hyperlink ref="A62" r:id="rId61" display="https://www.nyse.com/quote/XNYS:BK" xr:uid="{0B37A947-4BC9-AF46-A5BF-3ECEFBF4BBEF}"/>
+    <hyperlink ref="A63" r:id="rId62" display="https://www.nasdaq.com/market-activity/stocks/bkng" xr:uid="{ADCC6D79-2F07-4C41-AC89-0930E6DBD9D7}"/>
+    <hyperlink ref="A64" r:id="rId63" display="https://www.nasdaq.com/market-activity/stocks/bkr" xr:uid="{A369EF4C-DB7D-C544-8E6B-8FF801C207C8}"/>
+    <hyperlink ref="A65" r:id="rId64" display="https://www.nyse.com/quote/XNYS:BLDR" xr:uid="{D23303C8-405C-5743-AB10-FDB214668DE4}"/>
+    <hyperlink ref="A66" r:id="rId65" display="https://www.nyse.com/quote/XNYS:BLK" xr:uid="{140462A4-7B11-3148-9E4A-2193E36B2DE3}"/>
+    <hyperlink ref="A67" r:id="rId66" display="https://www.nyse.com/quote/XNYS:BMY" xr:uid="{567D5D33-711F-A349-8B4A-0E0A04DD6AFB}"/>
+    <hyperlink ref="A68" r:id="rId67" display="https://www.nyse.com/quote/XNYS:BR" xr:uid="{AC2AFEA9-F185-0848-BFE0-0B8C00782026}"/>
+    <hyperlink ref="A69" r:id="rId68" display="https://www.nyse.com/quote/XNYS:BRK.B" xr:uid="{72B1F24D-7C81-5B4C-9500-4362DFB5E482}"/>
+    <hyperlink ref="A70" r:id="rId69" display="https://www.nyse.com/quote/XNYS:BRO" xr:uid="{74C941DB-B075-D54C-8611-C1D7EDFFECDD}"/>
+    <hyperlink ref="A71" r:id="rId70" display="https://www.nyse.com/quote/XNYS:BSX" xr:uid="{9530F6EC-3ED4-1B4C-BFAB-733FD8E7D624}"/>
+    <hyperlink ref="A72" r:id="rId71" display="https://www.nyse.com/quote/XNYS:BX" xr:uid="{0FF26B03-A4BC-B144-AF38-74E418A5C95E}"/>
+    <hyperlink ref="A73" r:id="rId72" display="https://www.nyse.com/quote/XNYS:BXP" xr:uid="{EF7BC5BB-CAF1-024C-8587-5FBC12FFDEC8}"/>
+    <hyperlink ref="A74" r:id="rId73" display="https://www.nyse.com/quote/XNYS:C" xr:uid="{B5788FB1-7130-F645-90F0-D136B02C3514}"/>
+    <hyperlink ref="A75" r:id="rId74" display="https://www.nyse.com/quote/XNYS:CAG" xr:uid="{85CF8C92-CECA-9A41-B7C5-2244211B74C2}"/>
+    <hyperlink ref="A76" r:id="rId75" display="https://www.nyse.com/quote/XNYS:CAH" xr:uid="{526EDF79-8D20-D044-AD27-D648B9AE57D7}"/>
+    <hyperlink ref="A77" r:id="rId76" display="https://www.nyse.com/quote/XNYS:CARR" xr:uid="{E92B70EB-1342-F440-8A73-75F31AA00892}"/>
+    <hyperlink ref="A78" r:id="rId77" display="https://www.nyse.com/quote/XNYS:CAT" xr:uid="{3CD2BFDB-B67D-B844-96D3-6127804DD600}"/>
+    <hyperlink ref="A79" r:id="rId78" display="https://www.nyse.com/quote/XNYS:CB" xr:uid="{F9A6397E-7A5A-3E48-B0FB-B68C4E0B5393}"/>
+    <hyperlink ref="A80" r:id="rId79" display="https://markets.cboe.com/us/equities/listings/listed_products/symbols/CBOE" xr:uid="{1ACA0DEE-D6DD-2346-8AA9-F76C84F657AF}"/>
+    <hyperlink ref="A81" r:id="rId80" display="https://www.nyse.com/quote/XNYS:CBRE" xr:uid="{78F5879C-52A5-6D44-B454-E7392696471E}"/>
+    <hyperlink ref="A82" r:id="rId81" display="https://www.nyse.com/quote/XNYS:CCI" xr:uid="{E8330C3B-6813-3347-834A-544E3B1F2EBC}"/>
+    <hyperlink ref="A83" r:id="rId82" display="https://www.nyse.com/quote/XNYS:CCL" xr:uid="{2883A044-88A5-6C4B-8003-92612566CEA9}"/>
+    <hyperlink ref="A84" r:id="rId83" display="https://www.nasdaq.com/market-activity/stocks/cdns" xr:uid="{617298A8-D4C8-6940-9E6D-C15D6C4CDA76}"/>
+    <hyperlink ref="A85" r:id="rId84" display="https://www.nasdaq.com/market-activity/stocks/cdw" xr:uid="{48620819-44CD-C746-B9A5-168AF6049BB2}"/>
+    <hyperlink ref="A86" r:id="rId85" display="https://www.nasdaq.com/market-activity/stocks/ceg" xr:uid="{8D47646D-7C51-2E4A-B2B2-CE44CAE7BA4C}"/>
+    <hyperlink ref="A87" r:id="rId86" display="https://www.nyse.com/quote/XNYS:CF" xr:uid="{23671DC2-D0F3-CF45-95F1-ABD7D7A43465}"/>
+    <hyperlink ref="A88" r:id="rId87" display="https://www.nyse.com/quote/XNYS:CFG" xr:uid="{8A0C53D8-A077-7C4A-9853-8FB22CDAB72D}"/>
+    <hyperlink ref="A89" r:id="rId88" display="https://www.nyse.com/quote/XNYS:CHD" xr:uid="{0D9D81E3-79CC-8940-9A16-C96013AE13D0}"/>
+    <hyperlink ref="A90" r:id="rId89" display="https://www.nasdaq.com/market-activity/stocks/chrw" xr:uid="{547777A8-C7F0-0C44-9245-D64EEFB80F89}"/>
+    <hyperlink ref="A91" r:id="rId90" display="https://www.nasdaq.com/market-activity/stocks/chtr" xr:uid="{9B7C06AB-F2F5-A24F-9DB3-ABA79BB443BD}"/>
+    <hyperlink ref="A92" r:id="rId91" display="https://www.nyse.com/quote/XNYS:CI" xr:uid="{9317C131-9594-8B45-A8AD-065FEEDA2566}"/>
+    <hyperlink ref="A93" r:id="rId92" display="https://www.nasdaq.com/market-activity/stocks/cinf" xr:uid="{0474BCDC-1475-3A40-9A0D-128168C53C3D}"/>
+    <hyperlink ref="A94" r:id="rId93" display="https://www.nyse.com/quote/XNYS:CL" xr:uid="{D66D1D3A-C161-3548-9BA6-52616C30E3B6}"/>
+    <hyperlink ref="A95" r:id="rId94" display="https://www.nyse.com/quote/XNYS:CLX" xr:uid="{26FF2CE1-62A5-6A4E-BA1C-B0A062CFAAA4}"/>
+    <hyperlink ref="A96" r:id="rId95" display="https://www.nasdaq.com/market-activity/stocks/cmcsa" xr:uid="{BEC43371-4A80-2F4D-B093-CC115DFC75A6}"/>
+    <hyperlink ref="A97" r:id="rId96" display="https://www.nasdaq.com/market-activity/stocks/cme" xr:uid="{E065E96D-25FA-6C4D-8D71-6A16E691928E}"/>
+    <hyperlink ref="A98" r:id="rId97" display="https://www.nyse.com/quote/XNYS:CMG" xr:uid="{35168A6E-81E1-444A-9F11-F57BE18D6162}"/>
+    <hyperlink ref="A99" r:id="rId98" display="https://www.nyse.com/quote/XNYS:CMI" xr:uid="{44E4FBBB-8249-E74A-A4A5-84D88040155A}"/>
+    <hyperlink ref="A100" r:id="rId99" display="https://www.nyse.com/quote/XNYS:CMS" xr:uid="{77C94B3D-5071-FB45-AD55-7DA7BEF1A824}"/>
+    <hyperlink ref="A101" r:id="rId100" display="https://www.nyse.com/quote/XNYS:CNC" xr:uid="{4998E722-16CB-6E4E-A31E-46D16962AE79}"/>
+    <hyperlink ref="A102" r:id="rId101" display="https://www.nyse.com/quote/XNYS:CNP" xr:uid="{8A7F927A-77AC-BA43-9CA7-BD510201ABFD}"/>
+    <hyperlink ref="A103" r:id="rId102" display="https://www.nyse.com/quote/XNYS:COF" xr:uid="{ED6D6E95-3422-4149-ADE4-6EF8C05A4DAD}"/>
+    <hyperlink ref="A104" r:id="rId103" display="https://www.nasdaq.com/market-activity/stocks/coin" xr:uid="{804D7749-DCE5-7848-AD66-8D421DF97983}"/>
+    <hyperlink ref="A105" r:id="rId104" display="https://www.nasdaq.com/market-activity/stocks/coo" xr:uid="{432A14AC-B70A-6547-98BD-B2DAB137E895}"/>
+    <hyperlink ref="A106" r:id="rId105" display="https://www.nyse.com/quote/XNYS:COP" xr:uid="{FE71A105-C596-FE40-A4F8-93D7C6E0F3FE}"/>
+    <hyperlink ref="A107" r:id="rId106" display="https://www.nyse.com/quote/XNYS:COR" xr:uid="{2913D1AD-1A1C-CD4E-BD94-07E291745210}"/>
+    <hyperlink ref="A108" r:id="rId107" display="https://www.nasdaq.com/market-activity/stocks/cost" xr:uid="{0270F89B-5BD7-3F4D-9A45-C231BBBE2A33}"/>
+    <hyperlink ref="A109" r:id="rId108" display="https://www.nyse.com/quote/XNYS:CPAY" xr:uid="{C5E60279-EE9D-9B4B-B79E-981ED29F53D1}"/>
+    <hyperlink ref="A110" r:id="rId109" display="https://www.nyse.com/quote/XNYS:CPB" xr:uid="{1E8AB940-8DE9-2E44-B0D6-B2983939D455}"/>
+    <hyperlink ref="A111" r:id="rId110" display="https://www.nasdaq.com/market-activity/stocks/cprt" xr:uid="{465902BB-0431-834D-B372-CD16846E1502}"/>
+    <hyperlink ref="A112" r:id="rId111" display="https://www.nyse.com/quote/XNYS:CPT" xr:uid="{041410F2-988F-4940-9947-82B0F0D3255F}"/>
+    <hyperlink ref="A113" r:id="rId112" display="https://www.nyse.com/quote/XNYS:CRL" xr:uid="{2055434D-929A-E64C-9098-EB04838FF58C}"/>
+    <hyperlink ref="A114" r:id="rId113" display="https://www.nyse.com/quote/XNYS:CRM" xr:uid="{2FBB9BBF-93AD-644C-B817-7B6BE41AD564}"/>
+    <hyperlink ref="A115" r:id="rId114" display="https://www.nasdaq.com/market-activity/stocks/crwd" xr:uid="{4234E51E-1E03-8A47-B977-BCEB58452617}"/>
+    <hyperlink ref="A116" r:id="rId115" display="https://www.nasdaq.com/market-activity/stocks/csco" xr:uid="{79C6E38C-6348-5345-B7F6-5AC69BFCBA6F}"/>
+    <hyperlink ref="A117" r:id="rId116" display="https://www.nasdaq.com/market-activity/stocks/csgp" xr:uid="{496E5833-C827-EE43-9F6A-59148BF88C43}"/>
+    <hyperlink ref="A118" r:id="rId117" display="https://www.nasdaq.com/market-activity/stocks/csx" xr:uid="{EDA189E8-217F-9C4E-979C-DB0274A5BF9C}"/>
+    <hyperlink ref="A119" r:id="rId118" display="https://www.nasdaq.com/market-activity/stocks/ctas" xr:uid="{83B405E4-257D-A34A-AAFB-F636952023E0}"/>
+    <hyperlink ref="A120" r:id="rId119" display="https://www.nyse.com/quote/XNYS:CTRA" xr:uid="{50077B70-71BD-2F40-8D68-CB43215381C9}"/>
+    <hyperlink ref="A121" r:id="rId120" display="https://www.nasdaq.com/market-activity/stocks/ctsh" xr:uid="{15E5945F-9904-4846-8C8F-28992AB81AB0}"/>
+    <hyperlink ref="A122" r:id="rId121" display="https://www.nyse.com/quote/XNYS:CTVA" xr:uid="{41FDC787-62B6-304F-A72C-756181E7BC4C}"/>
+    <hyperlink ref="A123" r:id="rId122" display="https://www.nyse.com/quote/XNYS:CVS" xr:uid="{9E8B9137-5235-8749-AD45-CB9CFD28A5AE}"/>
+    <hyperlink ref="A124" r:id="rId123" display="https://www.nyse.com/quote/XNYS:CVX" xr:uid="{1FD8B15E-71EC-414D-9EEA-8DB91937A4BB}"/>
+    <hyperlink ref="A125" r:id="rId124" display="https://www.nyse.com/quote/XNYS:D" xr:uid="{306EAAD0-92D2-2D48-96AC-CD5B176FA1C0}"/>
+    <hyperlink ref="A126" r:id="rId125" display="https://www.nyse.com/quote/XNYS:DAL" xr:uid="{37A8E1DE-F0BF-444D-B04B-DB8F69499EE3}"/>
+    <hyperlink ref="A127" r:id="rId126" display="https://www.nasdaq.com/market-activity/stocks/dash" xr:uid="{9314A871-A48E-D44C-8042-38A1D1F63985}"/>
+    <hyperlink ref="A128" r:id="rId127" display="https://www.nyse.com/quote/XNYS:DAY" xr:uid="{B374354B-54A8-9F4D-9BC6-2F1AA800B8D0}"/>
+    <hyperlink ref="A129" r:id="rId128" display="https://www.nyse.com/quote/XNYS:DD" xr:uid="{5F877B60-40A6-0B41-81A7-18B67EFC4DA3}"/>
+    <hyperlink ref="A130" r:id="rId129" display="https://www.nasdaq.com/market-activity/stocks/ddog" xr:uid="{11B58AC9-A6FE-B34A-90D3-A12F9A78D588}"/>
+    <hyperlink ref="A131" r:id="rId130" display="https://www.nyse.com/quote/XNYS:DE" xr:uid="{F3C8E27F-3B67-134C-BAF5-FC265EF147EA}"/>
+    <hyperlink ref="A132" r:id="rId131" display="https://www.nyse.com/quote/XNYS:DECK" xr:uid="{3ED0520D-A484-0B4B-8959-D999ED10CCD5}"/>
+    <hyperlink ref="A133" r:id="rId132" display="https://www.nyse.com/quote/XNYS:DELL" xr:uid="{A67A3A46-1D73-244C-BCEC-5640FF0C731E}"/>
+    <hyperlink ref="A134" r:id="rId133" display="https://www.nyse.com/quote/XNYS:DG" xr:uid="{F4F7B863-FA4C-9845-B721-F818F6A5620A}"/>
+    <hyperlink ref="A135" r:id="rId134" display="https://www.nyse.com/quote/XNYS:DGX" xr:uid="{34B95A06-756B-E246-A8C4-D6ABB733DA0E}"/>
+    <hyperlink ref="A136" r:id="rId135" display="https://www.nyse.com/quote/XNYS:DHI" xr:uid="{A34DBA3A-2A02-384B-A47E-6C1C95143E7D}"/>
+    <hyperlink ref="A137" r:id="rId136" display="https://www.nyse.com/quote/XNYS:DHR" xr:uid="{BA0F2A17-A99E-B448-B631-34C74B0AE641}"/>
+    <hyperlink ref="A138" r:id="rId137" display="https://www.nyse.com/quote/XNYS:DIS" xr:uid="{2529C43D-A4FD-D94A-8A5A-50C1A164FDE9}"/>
+    <hyperlink ref="A139" r:id="rId138" display="https://www.nyse.com/quote/XNYS:DLR" xr:uid="{8B3CD2CD-1D3D-8D42-9C3B-B72FFAF90877}"/>
+    <hyperlink ref="A140" r:id="rId139" display="https://www.nasdaq.com/market-activity/stocks/dltr" xr:uid="{74E782A2-5387-F54F-A22A-BA254081EE49}"/>
+    <hyperlink ref="A141" r:id="rId140" display="https://www.nyse.com/quote/XNYS:DOC" xr:uid="{65285AF9-D794-CC46-A14F-7A1A815C26DA}"/>
+    <hyperlink ref="A142" r:id="rId141" display="https://www.nyse.com/quote/XNYS:DOV" xr:uid="{4FE345F9-EB6A-2D40-BDDC-F4D32B727CD6}"/>
+    <hyperlink ref="A143" r:id="rId142" display="https://www.nyse.com/quote/XNYS:DOW" xr:uid="{67220858-8E49-0042-BB27-C45F876317E2}"/>
+    <hyperlink ref="A144" r:id="rId143" display="https://www.nyse.com/quote/XNYS:DPZ" xr:uid="{B0FB3E11-EA46-C94A-A5CC-B1A9F2DEA2CA}"/>
+    <hyperlink ref="A145" r:id="rId144" display="https://www.nyse.com/quote/XNYS:DRI" xr:uid="{68A3DCA2-2C23-CB42-8F5D-9D44B24960DD}"/>
+    <hyperlink ref="A146" r:id="rId145" display="https://www.nyse.com/quote/XNYS:DTE" xr:uid="{C2D2347C-7A82-C849-9169-F27835219BD2}"/>
+    <hyperlink ref="A147" r:id="rId146" display="https://www.nyse.com/quote/XNYS:DUK" xr:uid="{478587A8-B414-DD44-B611-963C94D58813}"/>
+    <hyperlink ref="A148" r:id="rId147" display="https://www.nyse.com/quote/XNYS:DVA" xr:uid="{8EE8916D-FA87-D84B-8E1F-5713469139DE}"/>
+    <hyperlink ref="A149" r:id="rId148" display="https://www.nyse.com/quote/XNYS:DVN" xr:uid="{068C41D5-30F9-A04C-8D8C-E53C3F5669B4}"/>
+    <hyperlink ref="A150" r:id="rId149" display="https://www.nasdaq.com/market-activity/stocks/dxcm" xr:uid="{50377D63-2B99-5F43-A592-744C71CCE043}"/>
+    <hyperlink ref="A151" r:id="rId150" display="https://www.nasdaq.com/market-activity/stocks/ea" xr:uid="{1C943FAD-9B76-1C4B-ABB6-84E625009003}"/>
+    <hyperlink ref="A152" r:id="rId151" display="https://www.nasdaq.com/market-activity/stocks/ebay" xr:uid="{4C79D00F-264C-3F46-992D-D69F2BEBC9E9}"/>
+    <hyperlink ref="A153" r:id="rId152" display="https://www.nyse.com/quote/XNYS:ECL" xr:uid="{6B70C0E4-7AFD-D947-8C31-24B2ED70AFF4}"/>
+    <hyperlink ref="A154" r:id="rId153" display="https://www.nyse.com/quote/XNYS:ED" xr:uid="{60D7DB7D-5CC7-D64C-AE0F-9F3AC32BC5F7}"/>
+    <hyperlink ref="A155" r:id="rId154" display="https://www.nyse.com/quote/XNYS:EFX" xr:uid="{EB85254D-AC40-DA4D-8948-4809B40B3A3C}"/>
+    <hyperlink ref="A156" r:id="rId155" display="https://www.nyse.com/quote/XNYS:EG" xr:uid="{BA56CF6F-BF72-AF4A-BCBB-49F8A4E8752D}"/>
+    <hyperlink ref="A157" r:id="rId156" display="https://www.nyse.com/quote/XNYS:EIX" xr:uid="{AEF0EFC4-0297-254F-92B8-976DA40FFDF8}"/>
+    <hyperlink ref="A158" r:id="rId157" display="https://www.nyse.com/quote/XNYS:EL" xr:uid="{B678ECE7-065E-7E41-8BED-0FAA57182399}"/>
+    <hyperlink ref="A159" r:id="rId158" display="https://www.nyse.com/quote/XNYS:ELV" xr:uid="{47459202-66A0-C349-A260-D8C14EDC5A1C}"/>
+    <hyperlink ref="A160" r:id="rId159" display="https://www.nyse.com/quote/XNYS:EME" xr:uid="{E3B45B61-E39D-C544-ADA5-5C5D38C8F263}"/>
+    <hyperlink ref="A161" r:id="rId160" display="https://www.nyse.com/quote/XNYS:EMN" xr:uid="{99323F7E-6671-7F48-95FC-E434FE0B4431}"/>
+    <hyperlink ref="A162" r:id="rId161" display="https://www.nyse.com/quote/XNYS:EMR" xr:uid="{B4F3FAAE-36FC-014D-A757-9451A363C61C}"/>
+    <hyperlink ref="A163" r:id="rId162" display="https://www.nyse.com/quote/XNYS:EOG" xr:uid="{B12F38F5-0A77-AE4F-867C-734992F64570}"/>
+    <hyperlink ref="A164" r:id="rId163" display="https://www.nyse.com/quote/XNYS:EPAM" xr:uid="{CF06961F-E87F-8F4E-866B-DC017148585C}"/>
+    <hyperlink ref="A165" r:id="rId164" display="https://www.nasdaq.com/market-activity/stocks/eqix" xr:uid="{BA8F6119-57AB-6242-B94C-7C9DC6A1FD56}"/>
+    <hyperlink ref="A166" r:id="rId165" display="https://www.nyse.com/quote/XNYS:EQR" xr:uid="{7998B668-40A4-9343-8BBF-8C2DC73B637B}"/>
+    <hyperlink ref="A167" r:id="rId166" display="https://www.nyse.com/quote/XNYS:EQT" xr:uid="{AC8A8178-EFCC-0241-9B0E-9B2321C51110}"/>
+    <hyperlink ref="A168" r:id="rId167" display="https://www.nasdaq.com/market-activity/stocks/erie" xr:uid="{09CEBBEA-DF78-1141-A6ED-7C8C987B1E55}"/>
+    <hyperlink ref="A169" r:id="rId168" display="https://www.nyse.com/quote/XNYS:ES" xr:uid="{A337B079-98C5-1142-843A-101518ECD5F1}"/>
+    <hyperlink ref="A170" r:id="rId169" display="https://www.nyse.com/quote/XNYS:ESS" xr:uid="{86140575-00D2-F146-8011-DA6536FD7623}"/>
+    <hyperlink ref="A171" r:id="rId170" display="https://www.nyse.com/quote/XNYS:ETN" xr:uid="{19A7714D-0A54-D244-86FF-FBB15D022C00}"/>
+    <hyperlink ref="A172" r:id="rId171" display="https://www.nyse.com/quote/XNYS:ETR" xr:uid="{E195E659-2591-2242-9D2B-C43F9E752D93}"/>
+    <hyperlink ref="A173" r:id="rId172" display="https://www.nyse.com/quote/XNYS:EVRG" xr:uid="{8E9E2FBD-FB12-734D-8CF0-59716EBCCE37}"/>
+    <hyperlink ref="A174" r:id="rId173" display="https://www.nyse.com/quote/XNYS:EW" xr:uid="{76236DE9-3CC3-0343-AB3D-F6F845689D0D}"/>
+    <hyperlink ref="A175" r:id="rId174" display="https://www.nasdaq.com/market-activity/stocks/exc" xr:uid="{8C4120D5-68ED-484D-85DD-68309BFCBBE7}"/>
+    <hyperlink ref="A176" r:id="rId175" display="https://www.nasdaq.com/market-activity/stocks/exe" xr:uid="{B55C7EEF-EDA7-BF4D-B8EF-32F7F0E8CC93}"/>
+    <hyperlink ref="A177" r:id="rId176" display="https://www.nasdaq.com/market-activity/stocks/expd" xr:uid="{1EBA637D-A0C6-7E45-A94C-C163CBBC7A59}"/>
+    <hyperlink ref="A178" r:id="rId177" display="https://www.nasdaq.com/market-activity/stocks/expe" xr:uid="{716232D9-B422-4540-A6C5-6BB40280740D}"/>
+    <hyperlink ref="A179" r:id="rId178" display="https://www.nyse.com/quote/XNYS:EXR" xr:uid="{2A350B28-8FAD-D54A-A4E6-06E709999FAD}"/>
+    <hyperlink ref="A180" r:id="rId179" display="https://www.nyse.com/quote/XNYS:F" xr:uid="{5980A6F1-883E-EE49-B434-43AE8A92EDE1}"/>
+    <hyperlink ref="A181" r:id="rId180" display="https://www.nasdaq.com/market-activity/stocks/fang" xr:uid="{7B53C20B-E740-4246-B556-5B166E95A491}"/>
+    <hyperlink ref="A182" r:id="rId181" display="https://www.nasdaq.com/market-activity/stocks/fast" xr:uid="{277E3B33-E5AE-9440-9ECC-1C999CB17002}"/>
+    <hyperlink ref="A183" r:id="rId182" display="https://www.nyse.com/quote/XNYS:FCX" xr:uid="{4A770D84-B02A-5042-994F-683DF8B629FC}"/>
+    <hyperlink ref="A184" r:id="rId183" display="https://www.nyse.com/quote/XNYS:FDS" xr:uid="{A4A9821E-99D8-4F4D-B349-FC125FC4BAAA}"/>
+    <hyperlink ref="A185" r:id="rId184" display="https://www.nyse.com/quote/XNYS:FDX" xr:uid="{DD39B4FD-6065-D644-BE78-AF0E7A40F54C}"/>
+    <hyperlink ref="A186" r:id="rId185" display="https://www.nyse.com/quote/XNYS:FE" xr:uid="{1534FD60-5A79-4C46-BC29-998DFC94A9C5}"/>
+    <hyperlink ref="A187" r:id="rId186" display="https://www.nasdaq.com/market-activity/stocks/ffiv" xr:uid="{3DAAC8E3-B4EA-084B-A02C-7633204CF1B4}"/>
+    <hyperlink ref="A188" r:id="rId187" display="https://www.nyse.com/quote/XNYS:FI" xr:uid="{3CF5A9CB-1F6B-AB4A-A63D-C5665413C9EE}"/>
+    <hyperlink ref="A189" r:id="rId188" display="https://www.nyse.com/quote/XNYS:FICO" xr:uid="{1831A289-532E-B64D-AA68-DAD46AEAE1E5}"/>
+    <hyperlink ref="A190" r:id="rId189" display="https://www.nyse.com/quote/XNYS:FIS" xr:uid="{19839A74-2BD3-3C4B-9541-252D07C2ACA0}"/>
+    <hyperlink ref="A191" r:id="rId190" display="https://www.nasdaq.com/market-activity/stocks/fitb" xr:uid="{7968B7BF-254F-4546-AE0B-4E7A00FED347}"/>
+    <hyperlink ref="A192" r:id="rId191" display="https://www.nasdaq.com/market-activity/stocks/fox" xr:uid="{6B62CF4A-ACA1-F040-AF02-B19D2EFCBDBF}"/>
+    <hyperlink ref="A193" r:id="rId192" display="https://www.nasdaq.com/market-activity/stocks/foxa" xr:uid="{FDC4C1A6-BC06-AC4C-B0FA-215CB0925309}"/>
+    <hyperlink ref="A194" r:id="rId193" display="https://www.nyse.com/quote/XNYS:FRT" xr:uid="{999F423C-3B93-F349-B19C-02A91A74FF8B}"/>
+    <hyperlink ref="A195" r:id="rId194" display="https://www.nasdaq.com/market-activity/stocks/fslr" xr:uid="{59607057-ABA6-B44D-8EC0-6A7B860A9141}"/>
+    <hyperlink ref="A196" r:id="rId195" display="https://www.nasdaq.com/market-activity/stocks/ftnt" xr:uid="{9456FC7E-9D91-FA49-B421-47702C8ED3CB}"/>
+    <hyperlink ref="A197" r:id="rId196" display="https://www.nyse.com/quote/XNYS:FTV" xr:uid="{84A0E97F-2F4E-0449-BF6D-E776C91A0256}"/>
+    <hyperlink ref="A198" r:id="rId197" display="https://www.nyse.com/quote/XNYS:GD" xr:uid="{13A55F4B-2227-EE44-8D44-8BE9230C9AEB}"/>
+    <hyperlink ref="A199" r:id="rId198" display="https://www.nyse.com/quote/XNYS:GDDY" xr:uid="{BD2AC02E-04EC-E64E-869A-6C7714832203}"/>
+    <hyperlink ref="A200" r:id="rId199" display="https://www.nyse.com/quote/XNYS:GE" xr:uid="{69D40C48-9224-7847-AF21-65ABB35032C0}"/>
+    <hyperlink ref="A201" r:id="rId200" display="https://www.nasdaq.com/market-activity/stocks/gehc" xr:uid="{9EC80EED-97F5-EF46-A155-24C2B0B5D4BD}"/>
+    <hyperlink ref="A202" r:id="rId201" display="https://www.nasdaq.com/market-activity/stocks/gen" xr:uid="{95822482-6F8C-3A42-AC87-30770424DDA2}"/>
+    <hyperlink ref="A203" r:id="rId202" display="https://www.nyse.com/quote/XNYS:GEV" xr:uid="{C434C299-48E9-6847-9EB6-7383B8D0AF7F}"/>
+    <hyperlink ref="A204" r:id="rId203" display="https://www.nasdaq.com/market-activity/stocks/gild" xr:uid="{9CE5F5F2-209C-EC47-9AC4-855405113A80}"/>
+    <hyperlink ref="A205" r:id="rId204" display="https://www.nyse.com/quote/XNYS:GIS" xr:uid="{B2BD0DB8-8238-7646-99BA-EFE60DEEA829}"/>
+    <hyperlink ref="A206" r:id="rId205" display="https://www.nyse.com/quote/XNYS:GL" xr:uid="{34B4D36A-C1DF-484E-8D29-E13BE0B66076}"/>
+    <hyperlink ref="A207" r:id="rId206" display="https://www.nyse.com/quote/XNYS:GLW" xr:uid="{0000A273-3372-0C4B-BFC0-7AE8DA51217C}"/>
+    <hyperlink ref="A208" r:id="rId207" display="https://www.nyse.com/quote/XNYS:GM" xr:uid="{9DE70AF1-66F5-CD4B-8F79-FBBF2F1C7ECC}"/>
+    <hyperlink ref="A209" r:id="rId208" display="https://www.nyse.com/quote/XNYS:GNRC" xr:uid="{45B7E118-4F7C-3347-8A6D-C31245A3D246}"/>
+    <hyperlink ref="A210" r:id="rId209" display="https://www.nasdaq.com/market-activity/stocks/goog" xr:uid="{DB6E43BA-E78D-C94F-A910-FF963FDA4269}"/>
+    <hyperlink ref="A211" r:id="rId210" display="https://www.nasdaq.com/market-activity/stocks/googl" xr:uid="{5C85BE14-0962-CE4E-8EBF-02C6B40FD667}"/>
+    <hyperlink ref="A212" r:id="rId211" display="https://www.nyse.com/quote/XNYS:GPC" xr:uid="{260CD3BE-22F0-0247-B9DE-637563A21BC4}"/>
+    <hyperlink ref="A213" r:id="rId212" display="https://www.nyse.com/quote/XNYS:GPN" xr:uid="{FDFA090A-736D-ED4F-97FE-4968D18EC996}"/>
+    <hyperlink ref="A214" r:id="rId213" display="https://www.nyse.com/quote/XNYS:GRMN" xr:uid="{203C47D7-C500-334F-97CE-4262151CC52E}"/>
+    <hyperlink ref="A215" r:id="rId214" display="https://www.nyse.com/quote/XNYS:GS" xr:uid="{5D6C016B-1E26-CA4A-B517-4E9C837519E1}"/>
+    <hyperlink ref="A216" r:id="rId215" display="https://www.nyse.com/quote/XNYS:GWW" xr:uid="{9EEC6BC1-01C2-4D4D-AB0F-7A29944689C7}"/>
+    <hyperlink ref="A217" r:id="rId216" display="https://www.nyse.com/quote/XNYS:HAL" xr:uid="{410CF685-5B6E-2140-9DEB-B488075980BF}"/>
+    <hyperlink ref="A218" r:id="rId217" display="https://www.nasdaq.com/market-activity/stocks/has" xr:uid="{1E23571E-13C1-234E-B870-905EDA173E4A}"/>
+    <hyperlink ref="A219" r:id="rId218" display="https://www.nasdaq.com/market-activity/stocks/hban" xr:uid="{497B803E-733B-D547-B6C6-238F74B7209B}"/>
+    <hyperlink ref="A220" r:id="rId219" display="https://www.nyse.com/quote/XNYS:HCA" xr:uid="{F4CD64A0-BAEE-4C43-BB81-A5FBF5E26C45}"/>
+    <hyperlink ref="A221" r:id="rId220" display="https://www.nyse.com/quote/XNYS:HD" xr:uid="{F9857387-8B3D-E746-B1F5-C8DAC52CF750}"/>
+    <hyperlink ref="A222" r:id="rId221" display="https://www.nyse.com/quote/XNYS:HIG" xr:uid="{B92F3BC6-BC38-E64D-9F98-DC755A4B8674}"/>
+    <hyperlink ref="A223" r:id="rId222" display="https://www.nyse.com/quote/XNYS:HII" xr:uid="{FD03CC34-3FCA-784F-9616-87E142793174}"/>
+    <hyperlink ref="A224" r:id="rId223" display="https://www.nyse.com/quote/XNYS:HLT" xr:uid="{68D878C3-0517-704E-9113-5B8E98AFC660}"/>
+    <hyperlink ref="A225" r:id="rId224" display="https://www.nasdaq.com/market-activity/stocks/holx" xr:uid="{437FC4F0-A4D2-494A-86C7-F17F604D5605}"/>
+    <hyperlink ref="A226" r:id="rId225" display="https://www.nasdaq.com/market-activity/stocks/hon" xr:uid="{D2165BFD-263F-CA4E-8D99-56C04D92F97C}"/>
+    <hyperlink ref="A227" r:id="rId226" display="https://www.nasdaq.com/market-activity/stocks/hood" xr:uid="{FA6AA034-556F-4D42-B921-925E85E80EB6}"/>
+    <hyperlink ref="A228" r:id="rId227" display="https://www.nyse.com/quote/XNYS:HPE" xr:uid="{EAE9088E-1BA9-7349-AC0F-F6339A5EA33A}"/>
+    <hyperlink ref="A229" r:id="rId228" display="https://www.nyse.com/quote/XNYS:HPQ" xr:uid="{D1188BA9-602B-4948-B4E3-59F989523540}"/>
+    <hyperlink ref="A230" r:id="rId229" display="https://www.nyse.com/quote/XNYS:HRL" xr:uid="{F837824A-87EB-604D-BE7C-95DD11E49CA3}"/>
+    <hyperlink ref="A231" r:id="rId230" display="https://www.nasdaq.com/market-activity/stocks/hsic" xr:uid="{44936B30-5156-5842-8C73-5EC920C1BF0C}"/>
+    <hyperlink ref="A232" r:id="rId231" display="https://www.nasdaq.com/market-activity/stocks/hst" xr:uid="{0AED5690-80C5-1240-84E9-C4EF051E9646}"/>
+    <hyperlink ref="A233" r:id="rId232" display="https://www.nyse.com/quote/XNYS:HSY" xr:uid="{C8F149BC-3380-944D-B5F4-8158A1FD764F}"/>
+    <hyperlink ref="A234" r:id="rId233" display="https://www.nyse.com/quote/XNYS:HUBB" xr:uid="{9F6E8641-3DEF-4D43-9C4A-1AA1AEB3CE1A}"/>
+    <hyperlink ref="A235" r:id="rId234" display="https://www.nyse.com/quote/XNYS:HUM" xr:uid="{6868079D-B8D6-0A41-8E43-65BD66C4E302}"/>
+    <hyperlink ref="A236" r:id="rId235" display="https://www.nyse.com/quote/XNYS:HWM" xr:uid="{ECC2003D-3A34-3748-A74B-254870507A5A}"/>
+    <hyperlink ref="A237" r:id="rId236" display="https://www.nasdaq.com/market-activity/stocks/ibkr" xr:uid="{1ACC85F1-F69F-A346-9C20-6C54B8C6BF7F}"/>
+    <hyperlink ref="A238" r:id="rId237" display="https://www.nyse.com/quote/XNYS:IBM" xr:uid="{1A090DD4-3FFD-9C41-A631-81C950477713}"/>
+    <hyperlink ref="A239" r:id="rId238" display="https://www.nyse.com/quote/XNYS:ICE" xr:uid="{DDBAE428-0140-C44E-A54E-0A991DC4788A}"/>
+    <hyperlink ref="A240" r:id="rId239" display="https://www.nasdaq.com/market-activity/stocks/idxx" xr:uid="{8BB5349F-6120-0F47-9B3A-83B9B078E7D0}"/>
+    <hyperlink ref="A241" r:id="rId240" display="https://www.nyse.com/quote/XNYS:IEX" xr:uid="{2F6528E7-97E5-C04A-86A1-062F0281FD28}"/>
+    <hyperlink ref="A242" r:id="rId241" display="https://www.nyse.com/quote/XNYS:IFF" xr:uid="{5ABBAE51-BA22-224C-948E-2CB6C6C452C0}"/>
+    <hyperlink ref="A243" r:id="rId242" display="https://www.nasdaq.com/market-activity/stocks/incy" xr:uid="{1582E21C-0860-8142-A2D9-0EA2692ED679}"/>
+    <hyperlink ref="A244" r:id="rId243" display="https://www.nasdaq.com/market-activity/stocks/intc" xr:uid="{FE07B5A9-8D7C-4D4D-8EB8-42E112726241}"/>
+    <hyperlink ref="A245" r:id="rId244" display="https://www.nasdaq.com/market-activity/stocks/intu" xr:uid="{3563D9A7-E6F2-2040-BC71-ECBFE1EE6F1D}"/>
+    <hyperlink ref="A246" r:id="rId245" display="https://www.nyse.com/quote/XNYS:INVH" xr:uid="{5EAEECD7-EA27-4B40-918D-8B9A9C347D10}"/>
+    <hyperlink ref="A247" r:id="rId246" display="https://www.nyse.com/quote/XNYS:IP" xr:uid="{A5A5A651-D681-B64E-B27D-8FDC8564514D}"/>
+    <hyperlink ref="A248" r:id="rId247" display="https://www.nyse.com/quote/XNYS:IPG" xr:uid="{EA0E77A8-5DC5-ED49-9E58-2EB3D9592A22}"/>
+    <hyperlink ref="A249" r:id="rId248" display="https://www.nyse.com/quote/XNYS:IQV" xr:uid="{ABF35066-F352-6743-850E-91D8F3B90435}"/>
+    <hyperlink ref="A250" r:id="rId249" display="https://www.nyse.com/quote/XNYS:IR" xr:uid="{F385CADB-6738-1B40-9022-45BA1D3DDF9D}"/>
+    <hyperlink ref="A251" r:id="rId250" display="https://www.nyse.com/quote/XNYS:IRM" xr:uid="{6E5048D7-B841-8146-A630-38C93EBFF30D}"/>
+    <hyperlink ref="A252" r:id="rId251" display="https://www.nasdaq.com/market-activity/stocks/isrg" xr:uid="{171AC82D-3286-F741-8C45-01865730A0A0}"/>
+    <hyperlink ref="A253" r:id="rId252" display="https://www.nyse.com/quote/XNYS:IT" xr:uid="{E126C9B3-0173-9E4B-8797-0E3CE2CF3860}"/>
+    <hyperlink ref="A254" r:id="rId253" display="https://www.nyse.com/quote/XNYS:ITW" xr:uid="{C72B99C9-F0A6-C546-9CDD-4D647E3520F9}"/>
+    <hyperlink ref="A255" r:id="rId254" display="https://www.nyse.com/quote/XNYS:IVZ" xr:uid="{BF2FC951-EBAC-5F41-B65B-4A8B8E31F4F3}"/>
+    <hyperlink ref="A256" r:id="rId255" display="https://www.nyse.com/quote/XNYS:J" xr:uid="{A1F187DC-2EF6-CB44-8346-1280B995C82D}"/>
+    <hyperlink ref="A257" r:id="rId256" display="https://www.nasdaq.com/market-activity/stocks/jbht" xr:uid="{4DC98B14-3E96-914C-9660-2227F754C6D5}"/>
+    <hyperlink ref="A258" r:id="rId257" display="https://www.nyse.com/quote/XNYS:JBL" xr:uid="{7E6CB0E5-AFE4-E446-B8E9-2AADF24FDC1A}"/>
+    <hyperlink ref="A259" r:id="rId258" display="https://www.nyse.com/quote/XNYS:JCI" xr:uid="{B6C124F0-B304-1344-998E-A578EA5F593A}"/>
+    <hyperlink ref="A260" r:id="rId259" display="https://www.nasdaq.com/market-activity/stocks/jkhy" xr:uid="{BFABB2B6-6661-2F4A-A456-C7A5A74C8EAB}"/>
+    <hyperlink ref="A261" r:id="rId260" display="https://www.nyse.com/quote/XNYS:JNJ" xr:uid="{42AFA511-6B70-8C49-8908-8A28D5E82237}"/>
+    <hyperlink ref="A262" r:id="rId261" display="https://www.nyse.com/quote/XNYS:JPM" xr:uid="{11E98EFD-DA6A-394F-995D-6B1B18F854EF}"/>
+    <hyperlink ref="A263" r:id="rId262" display="https://www.nyse.com/quote/XNYS:K" xr:uid="{A6B2C616-CB07-244E-BE66-8BA8C4CD0F37}"/>
+    <hyperlink ref="A264" r:id="rId263" display="https://www.nasdaq.com/market-activity/stocks/kdp" xr:uid="{3381C987-3A09-C748-B70E-ECCEF99C299B}"/>
+    <hyperlink ref="A265" r:id="rId264" display="https://www.nyse.com/quote/XNYS:KEY" xr:uid="{823A9A91-53D2-A04A-826F-A6EE11A63C76}"/>
+    <hyperlink ref="A266" r:id="rId265" display="https://www.nyse.com/quote/XNYS:KEYS" xr:uid="{3D098851-0B4C-C649-9C96-912147431D3D}"/>
+    <hyperlink ref="A267" r:id="rId266" display="https://www.nasdaq.com/market-activity/stocks/khc" xr:uid="{0C599AA0-10F6-3541-89F7-0A88DA1D39C6}"/>
+    <hyperlink ref="A268" r:id="rId267" display="https://www.nyse.com/quote/XNYS:KIM" xr:uid="{28A1174D-3E8C-314C-913B-68A8DCC8C684}"/>
+    <hyperlink ref="A269" r:id="rId268" display="https://www.nyse.com/quote/XNYS:KKR" xr:uid="{42414C63-F8E6-2443-B0FC-7090CF6A4007}"/>
+    <hyperlink ref="A270" r:id="rId269" display="https://www.nasdaq.com/market-activity/stocks/klac" xr:uid="{AAA2BF98-A807-9146-9ED4-CEA5F481594A}"/>
+    <hyperlink ref="A271" r:id="rId270" display="https://www.nasdaq.com/market-activity/stocks/kmb" xr:uid="{D92FB513-6C31-9C46-9ED3-F20CD39EDE00}"/>
+    <hyperlink ref="A272" r:id="rId271" display="https://www.nyse.com/quote/XNYS:KMI" xr:uid="{32A9402A-E64D-114A-AFF9-A443DFA174EC}"/>
+    <hyperlink ref="A273" r:id="rId272" display="https://www.nyse.com/quote/XNYS:KMX" xr:uid="{04D256EA-1334-FE4E-9ED0-4FB790B9B022}"/>
+    <hyperlink ref="A274" r:id="rId273" display="https://www.nyse.com/quote/XNYS:KO" xr:uid="{E57A6991-11D3-7540-AA9E-08AC31FD0C90}"/>
+    <hyperlink ref="A275" r:id="rId274" display="https://www.nyse.com/quote/XNYS:KR" xr:uid="{E67C6841-C304-654A-99C1-15F76900DD5D}"/>
+    <hyperlink ref="A276" r:id="rId275" display="https://www.nyse.com/quote/XNYS:KVUE" xr:uid="{80B051EB-8506-CF4C-B100-851D043F180A}"/>
+    <hyperlink ref="A277" r:id="rId276" display="https://www.nyse.com/quote/XNYS:L" xr:uid="{2A010A35-21AD-AC4E-B544-104559D27F86}"/>
+    <hyperlink ref="A278" r:id="rId277" display="https://www.nyse.com/quote/XNYS:LDOS" xr:uid="{BE383C9C-26BE-6949-80E8-DEF4C89E56DC}"/>
+    <hyperlink ref="A279" r:id="rId278" display="https://www.nyse.com/quote/XNYS:LEN" xr:uid="{1AD6D35E-DEDF-2C49-B56C-B22CF52A01D2}"/>
+    <hyperlink ref="A280" r:id="rId279" display="https://www.nyse.com/quote/XNYS:LH" xr:uid="{1D0BEB1D-B97B-1945-88E7-D19D14D83BA0}"/>
+    <hyperlink ref="A281" r:id="rId280" display="https://www.nyse.com/quote/XNYS:LHX" xr:uid="{BFE026E7-F2DA-C547-8350-69998FA4F8E6}"/>
+    <hyperlink ref="A282" r:id="rId281" display="https://www.nyse.com/quote/XNYS:LII" xr:uid="{0E05D2E7-DB56-9F4D-9D23-F17FA1B048AE}"/>
+    <hyperlink ref="A283" r:id="rId282" display="https://www.nasdaq.com/market-activity/stocks/lin" xr:uid="{28FDFD73-7E21-1C48-AC42-0D31475B811D}"/>
+    <hyperlink ref="A284" r:id="rId283" display="https://www.nasdaq.com/market-activity/stocks/lkq" xr:uid="{D055FFF5-0E22-BE4D-88F0-72DBE46FC7A3}"/>
+    <hyperlink ref="A285" r:id="rId284" display="https://www.nyse.com/quote/XNYS:LLY" xr:uid="{D15F4A74-7ED1-9C4C-90A1-90B717839E6B}"/>
+    <hyperlink ref="A286" r:id="rId285" display="https://www.nyse.com/quote/XNYS:LMT" xr:uid="{FCDDFFBC-06B6-0549-B0E1-2C2EE7C375E9}"/>
+    <hyperlink ref="A287" r:id="rId286" display="https://www.nasdaq.com/market-activity/stocks/lnt" xr:uid="{DCDC2821-66F4-8345-9834-DADB081E9E13}"/>
+    <hyperlink ref="A288" r:id="rId287" display="https://www.nyse.com/quote/XNYS:LOW" xr:uid="{FF3F7959-D6FB-4547-96F2-D836A846B1C1}"/>
+    <hyperlink ref="A289" r:id="rId288" display="https://www.nasdaq.com/market-activity/stocks/lrcx" xr:uid="{7AAC7474-BFF4-1240-9BD6-645B2EFF84E0}"/>
+    <hyperlink ref="A290" r:id="rId289" display="https://www.nasdaq.com/market-activity/stocks/lulu" xr:uid="{717119E8-F5DD-8643-8B8B-1407446E6EDE}"/>
+    <hyperlink ref="A291" r:id="rId290" display="https://www.nyse.com/quote/XNYS:LUV" xr:uid="{D52BF1DF-740C-044B-B558-0E08E7D9A6BA}"/>
+    <hyperlink ref="A292" r:id="rId291" display="https://www.nyse.com/quote/XNYS:LVS" xr:uid="{4E8906E2-AC94-9940-BEF5-BA2B243A30A9}"/>
+    <hyperlink ref="A293" r:id="rId292" display="https://www.nyse.com/quote/XNYS:LW" xr:uid="{AAA08419-77BF-2649-87D9-7CB7EF24F053}"/>
+    <hyperlink ref="A294" r:id="rId293" display="https://www.nyse.com/quote/XNYS:LYB" xr:uid="{79456F53-94A2-4E46-8394-3330392BCAA2}"/>
+    <hyperlink ref="A295" r:id="rId294" display="https://www.nyse.com/quote/XNYS:LYV" xr:uid="{1B732D9A-9878-024C-BE46-97633D254972}"/>
+    <hyperlink ref="A296" r:id="rId295" display="https://www.nyse.com/quote/XNYS:MA" xr:uid="{3E7CD1B0-EA7B-DF45-8FEF-CFE7FF292357}"/>
+    <hyperlink ref="A297" r:id="rId296" display="https://www.nyse.com/quote/XNYS:MAA" xr:uid="{520B5C5E-41DE-9C40-B42C-85F8DAD4ABC1}"/>
+    <hyperlink ref="A298" r:id="rId297" display="https://www.nasdaq.com/market-activity/stocks/mar" xr:uid="{761061B4-0C87-F04B-BDD6-12CB6B030362}"/>
+    <hyperlink ref="A299" r:id="rId298" display="https://www.nyse.com/quote/XNYS:MAS" xr:uid="{893855C5-EEC3-5C43-A54F-3E81C945E34E}"/>
+    <hyperlink ref="A300" r:id="rId299" display="https://www.nyse.com/quote/XNYS:MCD" xr:uid="{53FF8A65-D1A8-8543-8BC9-DD396620CEF1}"/>
+    <hyperlink ref="A301" r:id="rId300" display="https://www.nasdaq.com/market-activity/stocks/mchp" xr:uid="{F689EEC2-2786-CF47-A666-C7C31EBFDDBD}"/>
+    <hyperlink ref="A302" r:id="rId301" display="https://www.nyse.com/quote/XNYS:MCK" xr:uid="{A00B0963-E571-3047-98E3-8C24AA52C177}"/>
+    <hyperlink ref="A303" r:id="rId302" display="https://www.nyse.com/quote/XNYS:MCO" xr:uid="{9DA46D4A-F942-7642-BDD9-22A84AD04A32}"/>
+    <hyperlink ref="A304" r:id="rId303" display="https://www.nasdaq.com/market-activity/stocks/mdlz" xr:uid="{4E1206C5-C6B0-E44B-A6BF-E8B56F0EB746}"/>
+    <hyperlink ref="A305" r:id="rId304" display="https://www.nyse.com/quote/XNYS:MDT" xr:uid="{9DA57471-D544-974B-BC72-4A32F1D24C35}"/>
+    <hyperlink ref="A306" r:id="rId305" display="https://www.nyse.com/quote/XNYS:MET" xr:uid="{1EEE6973-02B2-9F41-8019-2B8DEE6971BD}"/>
+    <hyperlink ref="A307" r:id="rId306" display="https://www.nasdaq.com/market-activity/stocks/meta" xr:uid="{62F71363-D9F3-D64B-96A0-13AC394FCBBE}"/>
+    <hyperlink ref="A308" r:id="rId307" display="https://www.nyse.com/quote/XNYS:MGM" xr:uid="{BAA61BA9-A17A-5F4A-85EB-13FA65A41F05}"/>
+    <hyperlink ref="A309" r:id="rId308" display="https://www.nyse.com/quote/XNYS:MHK" xr:uid="{3A68F269-A290-154A-BFC4-E40396C1156C}"/>
+    <hyperlink ref="A310" r:id="rId309" display="https://www.nyse.com/quote/XNYS:MKC" xr:uid="{2E4E3456-793A-6E41-9B45-A472FBFB2614}"/>
+    <hyperlink ref="A311" r:id="rId310" display="https://www.nyse.com/quote/XNYS:MLM" xr:uid="{E605175A-51B1-F64B-9894-7447CD49375D}"/>
+    <hyperlink ref="A312" r:id="rId311" display="https://www.nyse.com/quote/XNYS:MMC" xr:uid="{4C849AAF-42A5-D54D-AE7F-375154380F02}"/>
+    <hyperlink ref="A313" r:id="rId312" display="https://www.nyse.com/quote/XNYS:MMM" xr:uid="{449940FA-6C6D-0840-8498-F356A25FB276}"/>
+    <hyperlink ref="A314" r:id="rId313" display="https://www.nasdaq.com/market-activity/stocks/mnst" xr:uid="{B4B93AAE-D145-3549-8D04-889BB89B206E}"/>
+    <hyperlink ref="A315" r:id="rId314" display="https://www.nyse.com/quote/XNYS:MO" xr:uid="{81084AB5-8657-8740-98A6-A870C94E1C4A}"/>
+    <hyperlink ref="A316" r:id="rId315" display="https://www.nyse.com/quote/XNYS:MOH" xr:uid="{8F9E6469-FCE4-0D44-842D-BFD9173E6A21}"/>
+    <hyperlink ref="A317" r:id="rId316" display="https://www.nyse.com/quote/XNYS:MOS" xr:uid="{90325084-A959-F741-B0E1-451C43454A11}"/>
+    <hyperlink ref="A318" r:id="rId317" display="https://www.nyse.com/quote/XNYS:MPC" xr:uid="{8741995F-085D-F641-A873-85F8A33810D5}"/>
+    <hyperlink ref="A319" r:id="rId318" display="https://www.nasdaq.com/market-activity/stocks/mpwr" xr:uid="{84B97065-3398-3348-ACBE-C06FE05F10A4}"/>
+    <hyperlink ref="A320" r:id="rId319" display="https://www.nyse.com/quote/XNYS:MRK" xr:uid="{2465682A-B5F7-4A4D-9966-18E3047772F8}"/>
+    <hyperlink ref="A321" r:id="rId320" display="https://www.nasdaq.com/market-activity/stocks/mrna" xr:uid="{BE3DC42A-4DBF-574D-B1A4-9E7E5149D8D4}"/>
+    <hyperlink ref="A322" r:id="rId321" display="https://www.nyse.com/quote/XNYS:MS" xr:uid="{F18CACBA-5049-954F-B7C7-7462C0F04F5D}"/>
+    <hyperlink ref="A323" r:id="rId322" display="https://www.nyse.com/quote/XNYS:MSCI" xr:uid="{72B23BA3-44E4-0B4D-8C3F-FE3E68241CBE}"/>
+    <hyperlink ref="A324" r:id="rId323" display="https://www.nasdaq.com/market-activity/stocks/msft" xr:uid="{329A6E60-5D19-8F4E-886F-B2D7E106E903}"/>
+    <hyperlink ref="A325" r:id="rId324" display="https://www.nyse.com/quote/XNYS:MSI" xr:uid="{FAE9FF66-7248-C94B-B853-2C42DB47D45F}"/>
+    <hyperlink ref="A326" r:id="rId325" display="https://www.nyse.com/quote/XNYS:MTB" xr:uid="{D25DB4CA-3CF0-5646-8259-72BF5DA091E9}"/>
+    <hyperlink ref="A327" r:id="rId326" display="https://www.nasdaq.com/market-activity/stocks/mtch" xr:uid="{1A7F813E-3F99-DD4E-900F-B236E146C3F4}"/>
+    <hyperlink ref="A328" r:id="rId327" display="https://www.nyse.com/quote/XNYS:MTD" xr:uid="{FE38F7AC-14AF-6C48-A6A8-224BFFF48CA6}"/>
+    <hyperlink ref="A329" r:id="rId328" display="https://www.nasdaq.com/market-activity/stocks/mu" xr:uid="{89F5EC60-8D0C-7B49-B367-CD2063126AF9}"/>
+    <hyperlink ref="A330" r:id="rId329" display="https://www.nyse.com/quote/XNYS:NCLH" xr:uid="{CB08D2C8-0250-BD4F-A413-2A177DAB8E21}"/>
+    <hyperlink ref="A331" r:id="rId330" display="https://www.nasdaq.com/market-activity/stocks/ndaq" xr:uid="{55EC6406-9914-414E-9B3C-52A743034FEB}"/>
+    <hyperlink ref="A332" r:id="rId331" display="https://www.nasdaq.com/market-activity/stocks/ndsn" xr:uid="{3887551E-998F-3345-B673-3AC210033517}"/>
+    <hyperlink ref="A333" r:id="rId332" display="https://www.nyse.com/quote/XNYS:NEE" xr:uid="{98A63CCA-3AE7-4F4A-AC3F-2BA98D19B5B3}"/>
+    <hyperlink ref="A334" r:id="rId333" display="https://www.nyse.com/quote/XNYS:NEM" xr:uid="{E5D83086-98CE-264A-AA37-F4EEDAF8981F}"/>
+    <hyperlink ref="A335" r:id="rId334" display="https://www.nasdaq.com/market-activity/stocks/nflx" xr:uid="{41231F33-93EC-6F4F-ABBC-8A8EE54A351F}"/>
+    <hyperlink ref="A336" r:id="rId335" display="https://www.nyse.com/quote/XNYS:NI" xr:uid="{9F6401AF-D421-354D-88F9-9CAE569791C6}"/>
+    <hyperlink ref="A337" r:id="rId336" display="https://www.nyse.com/quote/XNYS:NKE" xr:uid="{51E41BF9-6561-C640-AA2B-E6EBD7B467CB}"/>
+    <hyperlink ref="A338" r:id="rId337" display="https://www.nyse.com/quote/XNYS:NOC" xr:uid="{673B6FA6-5BF0-AF43-A50D-7772F212DDC3}"/>
+    <hyperlink ref="A339" r:id="rId338" display="https://www.nyse.com/quote/XNYS:NOW" xr:uid="{0CB5C0A0-EC1C-1C4E-8D66-B2AE7BBF3D59}"/>
+    <hyperlink ref="A340" r:id="rId339" display="https://www.nyse.com/quote/XNYS:NRG" xr:uid="{C7BEBB70-B408-EF4C-8BA9-3D6CB46AD9CF}"/>
+    <hyperlink ref="A341" r:id="rId340" display="https://www.nyse.com/quote/XNYS:NSC" xr:uid="{CD96930B-072E-E844-811A-249A6DA5C326}"/>
+    <hyperlink ref="A342" r:id="rId341" display="https://www.nasdaq.com/market-activity/stocks/ntap" xr:uid="{2A3B7433-984B-7D47-B826-F1F28213F2F0}"/>
+    <hyperlink ref="A343" r:id="rId342" display="https://www.nasdaq.com/market-activity/stocks/ntrs" xr:uid="{EA91C089-90CB-964B-BED9-977AE8FB5E4C}"/>
+    <hyperlink ref="A344" r:id="rId343" display="https://www.nyse.com/quote/XNYS:NUE" xr:uid="{29160797-224B-4B49-A09D-90895CA06CBF}"/>
+    <hyperlink ref="A345" r:id="rId344" display="https://www.nasdaq.com/market-activity/stocks/nvda" xr:uid="{00EDF848-634D-1243-ACD2-C51EBB662BCC}"/>
+    <hyperlink ref="A346" r:id="rId345" display="https://www.nyse.com/quote/XNYS:NVR" xr:uid="{DE46C05A-7CFD-EA40-B96B-D3F147A06F0F}"/>
+    <hyperlink ref="A347" r:id="rId346" display="https://www.nasdaq.com/market-activity/stocks/nws" xr:uid="{7A68318A-E7FB-414C-B359-B2DFE8E761B7}"/>
+    <hyperlink ref="A348" r:id="rId347" display="https://www.nasdaq.com/market-activity/stocks/nwsa" xr:uid="{26AA625A-C7D1-2645-83FB-D2995369785B}"/>
+    <hyperlink ref="A349" r:id="rId348" display="https://www.nasdaq.com/market-activity/stocks/nxpi" xr:uid="{7A908892-CA73-D041-95C6-0BA3A4CBDB75}"/>
+    <hyperlink ref="A350" r:id="rId349" display="https://www.nyse.com/quote/XNYS:O" xr:uid="{64194E49-B52C-0E40-9736-ABD14914258E}"/>
+    <hyperlink ref="A351" r:id="rId350" display="https://www.nasdaq.com/market-activity/stocks/odfl" xr:uid="{2DF351DC-919C-9E4A-9B25-B355A1ABF765}"/>
+    <hyperlink ref="A352" r:id="rId351" display="https://www.nyse.com/quote/XNYS:OKE" xr:uid="{ACCDC40A-39DF-4B4E-885A-E5DB9EA79778}"/>
+    <hyperlink ref="A353" r:id="rId352" display="https://www.nyse.com/quote/XNYS:OMC" xr:uid="{9D3BA12C-AD43-B345-9428-6159BBA484E8}"/>
+    <hyperlink ref="A354" r:id="rId353" display="https://www.nasdaq.com/market-activity/stocks/on" xr:uid="{6FCD2D43-9E60-DB4E-9BCF-278E5BACA962}"/>
+    <hyperlink ref="A355" r:id="rId354" display="https://www.nyse.com/quote/XNYS:ORCL" xr:uid="{6650ACD3-70B5-764B-B034-8E079C47DE5D}"/>
+    <hyperlink ref="A356" r:id="rId355" display="https://www.nasdaq.com/market-activity/stocks/orly" xr:uid="{BB397E1B-8AC3-B746-8A0F-3A7D119AEF5F}"/>
+    <hyperlink ref="A357" r:id="rId356" display="https://www.nyse.com/quote/XNYS:OTIS" xr:uid="{6A3F311D-AC5B-EA42-B3F3-EF215E37EFF3}"/>
+    <hyperlink ref="A358" r:id="rId357" display="https://www.nyse.com/quote/XNYS:OXY" xr:uid="{223C80A3-C25C-D342-920F-DC7DAC10A41A}"/>
+    <hyperlink ref="A359" r:id="rId358" display="https://www.nasdaq.com/market-activity/stocks/panw" xr:uid="{C74FFFC5-890A-6041-BB2A-878F437E09CB}"/>
+    <hyperlink ref="A360" r:id="rId359" display="https://www.nyse.com/quote/XNYS:PAYC" xr:uid="{73CF1F60-1787-F640-BB3D-037D14785D05}"/>
+    <hyperlink ref="A361" r:id="rId360" display="https://www.nasdaq.com/market-activity/stocks/payx" xr:uid="{7A45CD7B-CF4C-AE42-A0B2-2ACDA23B6AE1}"/>
+    <hyperlink ref="A362" r:id="rId361" display="https://www.nasdaq.com/market-activity/stocks/pcar" xr:uid="{8AC4AA8B-5D83-D14E-9D68-14D25F056EB1}"/>
+    <hyperlink ref="A363" r:id="rId362" display="https://www.nyse.com/quote/XNYS:PCG" xr:uid="{31CE48C0-96F5-2B42-A147-E774DB1FEB21}"/>
+    <hyperlink ref="A364" r:id="rId363" display="https://www.nyse.com/quote/XNYS:PEG" xr:uid="{0181F50A-9BC8-BD47-9FED-ACB48FC274D3}"/>
+    <hyperlink ref="A365" r:id="rId364" display="https://www.nasdaq.com/market-activity/stocks/pep" xr:uid="{BBF934CA-544A-9B4D-95D7-D5CA9B686BC6}"/>
+    <hyperlink ref="A366" r:id="rId365" display="https://www.nyse.com/quote/XNYS:PFE" xr:uid="{AC4479DE-1F65-FD45-B0E4-51241E55DA26}"/>
+    <hyperlink ref="A367" r:id="rId366" display="https://www.nasdaq.com/market-activity/stocks/pfg" xr:uid="{EB33D14E-A995-DF40-9940-EAE060F12545}"/>
+    <hyperlink ref="A368" r:id="rId367" display="https://www.nyse.com/quote/XNYS:PG" xr:uid="{4AA10F2F-8D29-9741-9435-0A578BA8CEEB}"/>
+    <hyperlink ref="A369" r:id="rId368" display="https://www.nyse.com/quote/XNYS:PGR" xr:uid="{2BC8FCE8-6A3A-D141-8EED-1695EDD140EB}"/>
+    <hyperlink ref="A370" r:id="rId369" display="https://www.nyse.com/quote/XNYS:PH" xr:uid="{7FEEC2E0-DC80-B541-9681-F9A88D8DF38F}"/>
+    <hyperlink ref="A371" r:id="rId370" display="https://www.nyse.com/quote/XNYS:PHM" xr:uid="{59B89AAD-523D-354B-971F-7F4DEB59612F}"/>
+    <hyperlink ref="A372" r:id="rId371" display="https://www.nyse.com/quote/XNYS:PKG" xr:uid="{6EFABA88-3E93-CD41-9311-05B9914EE80C}"/>
+    <hyperlink ref="A373" r:id="rId372" display="https://www.nyse.com/quote/XNYS:PLD" xr:uid="{54A14D81-EDE2-C14F-9C8C-D1AF3B25A0E2}"/>
+    <hyperlink ref="A374" r:id="rId373" display="https://www.nasdaq.com/market-activity/stocks/pltr" xr:uid="{25A8858D-6FC1-954F-8A60-19C1A4EE7425}"/>
+    <hyperlink ref="A375" r:id="rId374" display="https://www.nyse.com/quote/XNYS:PM" xr:uid="{C51D4C9B-08A3-4645-997C-8087401C7C3E}"/>
+    <hyperlink ref="A376" r:id="rId375" display="https://www.nyse.com/quote/XNYS:PNC" xr:uid="{45243884-D508-F041-A73A-ABD2B824B033}"/>
+    <hyperlink ref="A377" r:id="rId376" display="https://www.nyse.com/quote/XNYS:PNR" xr:uid="{8CB75B72-1D75-CD46-942E-731B14558500}"/>
+    <hyperlink ref="A378" r:id="rId377" display="https://www.nyse.com/quote/XNYS:PNW" xr:uid="{2E3F0B32-E9E0-9342-9B0B-543547D2B104}"/>
+    <hyperlink ref="A379" r:id="rId378" display="https://www.nasdaq.com/market-activity/stocks/podd" xr:uid="{59547261-1063-5643-BE9B-6B90AF8718F5}"/>
+    <hyperlink ref="A380" r:id="rId379" display="https://www.nasdaq.com/market-activity/stocks/pool" xr:uid="{7AED7451-E319-7A47-89B8-C7AC16FDF835}"/>
+    <hyperlink ref="A381" r:id="rId380" display="https://www.nyse.com/quote/XNYS:PPG" xr:uid="{12ACB3B3-7CB1-8842-A32A-83E16ED1ECA5}"/>
+    <hyperlink ref="A382" r:id="rId381" display="https://www.nyse.com/quote/XNYS:PPL" xr:uid="{50FB6E58-182C-9147-A234-CDFAE5120F68}"/>
+    <hyperlink ref="A383" r:id="rId382" display="https://www.nyse.com/quote/XNYS:PRU" xr:uid="{F499D5D8-07FB-E746-B652-EECB695B47F5}"/>
+    <hyperlink ref="A384" r:id="rId383" display="https://www.nyse.com/quote/XNYS:PSA" xr:uid="{412D79F4-4EFB-9B49-AE4A-903DD04ADDF9}"/>
+    <hyperlink ref="A385" r:id="rId384" display="https://www.nasdaq.com/market-activity/stocks/psky" xr:uid="{6E7207B9-8691-354E-B1E6-3F1A6EF171F8}"/>
+    <hyperlink ref="A386" r:id="rId385" display="https://www.nyse.com/quote/XNYS:PSX" xr:uid="{540B3689-0943-6B42-B53F-AB008F94EBCA}"/>
+    <hyperlink ref="A387" r:id="rId386" display="https://www.nasdaq.com/market-activity/stocks/ptc" xr:uid="{11BE4660-B1AD-5540-93E1-5B0D86C9063E}"/>
+    <hyperlink ref="A388" r:id="rId387" display="https://www.nyse.com/quote/XNYS:PWR" xr:uid="{474D7B04-4975-264F-AC80-9EB6A2642100}"/>
+    <hyperlink ref="A389" r:id="rId388" display="https://www.nasdaq.com/market-activity/stocks/pypl" xr:uid="{F5A5FA8E-D374-E147-8814-77C7CF60EE66}"/>
+    <hyperlink ref="A390" r:id="rId389" display="https://www.nasdaq.com/market-activity/stocks/qcom" xr:uid="{3683E370-F1C7-B14A-952A-5F6111E423D2}"/>
+    <hyperlink ref="A391" r:id="rId390" display="https://www.nyse.com/quote/XNYS:RCL" xr:uid="{1D9580F0-A17B-CF47-A212-39CDA74FFDAF}"/>
+    <hyperlink ref="A392" r:id="rId391" display="https://www.nasdaq.com/market-activity/stocks/reg" xr:uid="{B531B822-790A-B44D-862F-685207AB4763}"/>
+    <hyperlink ref="A393" r:id="rId392" display="https://www.nasdaq.com/market-activity/stocks/regn" xr:uid="{0AD97215-0E80-8F46-BCF8-BBA0B579CB0A}"/>
+    <hyperlink ref="A394" r:id="rId393" display="https://www.nyse.com/quote/XNYS:RF" xr:uid="{F91C5F26-65E9-2842-B7E7-A76ACEA43D58}"/>
+    <hyperlink ref="A395" r:id="rId394" display="https://www.nyse.com/quote/XNYS:RJF" xr:uid="{58FD82DA-CD15-3546-9F6A-5DAA847B715C}"/>
+    <hyperlink ref="A396" r:id="rId395" display="https://www.nyse.com/quote/XNYS:RL" xr:uid="{1F304E82-855B-7B42-BCC2-9EAD9E098BE5}"/>
+    <hyperlink ref="A397" r:id="rId396" display="https://www.nyse.com/quote/XNYS:RMD" xr:uid="{29A22279-3C29-9C4A-A98A-91AB973430B8}"/>
+    <hyperlink ref="A398" r:id="rId397" display="https://www.nyse.com/quote/XNYS:ROK" xr:uid="{48275E37-EBC2-9C44-A8EA-00CF08B82460}"/>
+    <hyperlink ref="A399" r:id="rId398" display="https://www.nyse.com/quote/XNYS:ROL" xr:uid="{8D1278D7-9D6E-A64A-A937-291FF9A471BD}"/>
+    <hyperlink ref="A400" r:id="rId399" display="https://www.nasdaq.com/market-activity/stocks/rop" xr:uid="{43CA0BA5-951E-DA43-8603-EDF34D2E3985}"/>
+    <hyperlink ref="A401" r:id="rId400" display="https://www.nasdaq.com/market-activity/stocks/rost" xr:uid="{C4241395-ADB8-5643-B503-67B37274C40F}"/>
+    <hyperlink ref="A402" r:id="rId401" display="https://www.nyse.com/quote/XNYS:RSG" xr:uid="{CBDDD170-B44B-0946-9552-A88785EC264A}"/>
+    <hyperlink ref="A403" r:id="rId402" display="https://www.nyse.com/quote/XNYS:RTX" xr:uid="{230AEFE9-336A-F44B-A87E-1FBA4125679A}"/>
+    <hyperlink ref="A404" r:id="rId403" display="https://www.nyse.com/quote/XNYS:RVTY" xr:uid="{1535D3B2-02C5-7141-A7B1-0BA338DA4487}"/>
+    <hyperlink ref="A405" r:id="rId404" display="https://www.nasdaq.com/market-activity/stocks/sbac" xr:uid="{EA77769C-6370-4846-A531-A1C7AC2C1813}"/>
+    <hyperlink ref="A406" r:id="rId405" display="https://www.nasdaq.com/market-activity/stocks/sbux" xr:uid="{C04F909C-8C9B-F946-8F4A-99C44F9E5C62}"/>
+    <hyperlink ref="A407" r:id="rId406" display="https://www.nyse.com/quote/XNYS:SCHW" xr:uid="{F73D3882-5566-E34D-B394-F29CFB36C5E1}"/>
+    <hyperlink ref="A408" r:id="rId407" display="https://www.nyse.com/quote/XNYS:SHW" xr:uid="{2319F657-8B22-AF4A-9F01-68B3130AFEDD}"/>
+    <hyperlink ref="A409" r:id="rId408" display="https://www.nyse.com/quote/XNYS:SJM" xr:uid="{84052077-6FD1-BE46-B339-AA730EC19491}"/>
+    <hyperlink ref="A410" r:id="rId409" display="https://www.nyse.com/quote/XNYS:SLB" xr:uid="{115196AE-69B2-D349-BC13-69C91ADB7D02}"/>
+    <hyperlink ref="A411" r:id="rId410" display="https://www.nasdaq.com/market-activity/stocks/smci" xr:uid="{70AEFB4B-C40B-3F45-9F23-2B84EA841436}"/>
+    <hyperlink ref="A412" r:id="rId411" display="https://www.nyse.com/quote/XNYS:SNA" xr:uid="{BD999369-3A61-0A4C-AF07-99F5E562CACD}"/>
+    <hyperlink ref="A413" r:id="rId412" display="https://www.nasdaq.com/market-activity/stocks/snps" xr:uid="{B789E079-4FA0-2C4F-96BE-B7B6BDDD4B44}"/>
+    <hyperlink ref="A414" r:id="rId413" display="https://www.nyse.com/quote/XNYS:SO" xr:uid="{A265E65E-2BEC-B84C-A284-5D75FED9B5E9}"/>
+    <hyperlink ref="A415" r:id="rId414" display="https://www.nyse.com/quote/XNYS:SOLV" xr:uid="{7DA098B0-013F-8543-BEBE-41A6070E3BF7}"/>
+    <hyperlink ref="A416" r:id="rId415" display="https://www.nyse.com/quote/XNYS:SPG" xr:uid="{D6BD4164-C990-A54A-BF57-85F9187405A4}"/>
+    <hyperlink ref="A417" r:id="rId416" display="https://www.nyse.com/quote/XNYS:SPGI" xr:uid="{365E02CF-97ED-3D4E-9AF4-AF471B5A3285}"/>
+    <hyperlink ref="A418" r:id="rId417" display="https://www.nyse.com/quote/XNYS:SRE" xr:uid="{32CCF3B0-4659-0042-9791-99EDA13C29A1}"/>
+    <hyperlink ref="A419" r:id="rId418" display="https://www.nyse.com/quote/XNYS:STE" xr:uid="{11CE0A88-1B14-5940-8FB5-39067BCEF193}"/>
+    <hyperlink ref="A420" r:id="rId419" display="https://www.nasdaq.com/market-activity/stocks/stld" xr:uid="{C8108F33-0609-B14A-9FEE-1148858343A1}"/>
+    <hyperlink ref="A421" r:id="rId420" display="https://www.nyse.com/quote/XNYS:STT" xr:uid="{30A9E47C-296B-2946-8CD3-00F44A902325}"/>
+    <hyperlink ref="A422" r:id="rId421" display="https://www.nasdaq.com/market-activity/stocks/stx" xr:uid="{477CB993-0E78-CC41-88AD-4859CB6337BB}"/>
+    <hyperlink ref="A423" r:id="rId422" display="https://www.nyse.com/quote/XNYS:STZ" xr:uid="{B65533BB-CA59-EC43-BFF7-17ACBC00936B}"/>
+    <hyperlink ref="A424" r:id="rId423" display="https://www.nyse.com/quote/XNYS:SW" xr:uid="{D2CE511A-81F3-7B4A-9648-FB7F6894154D}"/>
+    <hyperlink ref="A425" r:id="rId424" display="https://www.nyse.com/quote/XNYS:SWK" xr:uid="{E26635CF-F976-994B-A9A9-759633920910}"/>
+    <hyperlink ref="A426" r:id="rId425" display="https://www.nasdaq.com/market-activity/stocks/swks" xr:uid="{119C63C9-D252-5042-B65C-23F5F2EA97B6}"/>
+    <hyperlink ref="A427" r:id="rId426" display="https://www.nyse.com/quote/XNYS:SYF" xr:uid="{2D97F9D1-1A7F-074A-9CEF-FF6082B34D73}"/>
+    <hyperlink ref="A428" r:id="rId427" display="https://www.nyse.com/quote/XNYS:SYK" xr:uid="{0CB8B011-8989-8A4B-A204-AE19278C6E77}"/>
+    <hyperlink ref="A429" r:id="rId428" display="https://www.nyse.com/quote/XNYS:SYY" xr:uid="{98D51620-0F5F-804D-AD83-EC17621393CA}"/>
+    <hyperlink ref="A430" r:id="rId429" display="https://www.nyse.com/quote/XNYS:T" xr:uid="{D8AC89AF-F728-D444-8615-F38485B0A219}"/>
+    <hyperlink ref="A431" r:id="rId430" display="https://www.nyse.com/quote/XNYS:TAP" xr:uid="{4E851D3E-D35F-6B4E-A433-2C8FF7D325EB}"/>
+    <hyperlink ref="A432" r:id="rId431" display="https://www.nyse.com/quote/XNYS:TDG" xr:uid="{6385F45E-A51A-804C-BB97-7CD4205E1C11}"/>
+    <hyperlink ref="A433" r:id="rId432" display="https://www.nyse.com/quote/XNYS:TDY" xr:uid="{38FC32F0-F2CB-FF46-8534-0EB0F10A27F2}"/>
+    <hyperlink ref="A434" r:id="rId433" display="https://www.nasdaq.com/market-activity/stocks/tech" xr:uid="{45CBF9CD-0549-1D41-9456-62CC6A323E0B}"/>
+    <hyperlink ref="A435" r:id="rId434" display="https://www.nyse.com/quote/XNYS:TEL" xr:uid="{015362E5-9175-474B-896D-F70BFB46047D}"/>
+    <hyperlink ref="A436" r:id="rId435" display="https://www.nasdaq.com/market-activity/stocks/ter" xr:uid="{BC42B90F-670B-5148-ACA7-038894EC2A7F}"/>
+    <hyperlink ref="A437" r:id="rId436" display="https://www.nyse.com/quote/XNYS:TFC" xr:uid="{66F2C9B5-0F6E-1E43-9B9B-E8E56B88BD89}"/>
+    <hyperlink ref="A438" r:id="rId437" display="https://www.nyse.com/quote/XNYS:TGT" xr:uid="{3CCB3AFC-A781-7541-8E3D-29845A2A385E}"/>
+    <hyperlink ref="A439" r:id="rId438" display="https://www.nyse.com/quote/XNYS:TJX" xr:uid="{326522C3-0D67-8344-8441-47DA73CF70AD}"/>
+    <hyperlink ref="A440" r:id="rId439" display="https://www.nyse.com/quote/XNYS:TKO" xr:uid="{FEC6F21B-E71C-4C4A-8116-76CA45A1A609}"/>
+    <hyperlink ref="A441" r:id="rId440" display="https://www.nyse.com/quote/XNYS:TMO" xr:uid="{44119C58-7762-BA4B-A43D-BBF5A4FC781C}"/>
+    <hyperlink ref="A442" r:id="rId441" display="https://www.nasdaq.com/market-activity/stocks/tmus" xr:uid="{F82D2EA0-4DB4-0544-A76C-6F4244932848}"/>
+    <hyperlink ref="A443" r:id="rId442" display="https://www.nyse.com/quote/XNYS:TPL" xr:uid="{F5ECC46D-281F-5446-A3F9-2807B71FD2A1}"/>
+    <hyperlink ref="A444" r:id="rId443" display="https://www.nyse.com/quote/XNYS:TPR" xr:uid="{A57582FE-7F2E-F541-BE08-96D1E226164A}"/>
+    <hyperlink ref="A445" r:id="rId444" display="https://www.nyse.com/quote/XNYS:TRGP" xr:uid="{06405C4F-9682-BF4E-AC0D-D0AF7A5C2CD5}"/>
+    <hyperlink ref="A446" r:id="rId445" display="https://www.nasdaq.com/market-activity/stocks/trmb" xr:uid="{FD690395-07F1-5041-9969-2064595982BA}"/>
+    <hyperlink ref="A447" r:id="rId446" display="https://www.nasdaq.com/market-activity/stocks/trow" xr:uid="{92D8EC19-5007-A14F-80B3-F864823A989A}"/>
+    <hyperlink ref="A448" r:id="rId447" display="https://www.nyse.com/quote/XNYS:TRV" xr:uid="{A94E092B-770D-1C46-B88B-48A60D40BE22}"/>
+    <hyperlink ref="A449" r:id="rId448" display="https://www.nasdaq.com/market-activity/stocks/tsco" xr:uid="{9F526E21-BEF4-5B44-894A-EA4AEF4F1F98}"/>
+    <hyperlink ref="A450" r:id="rId449" display="https://www.nasdaq.com/market-activity/stocks/tsla" xr:uid="{90610183-CCAC-B945-8296-2EBF13E1D77F}"/>
+    <hyperlink ref="A451" r:id="rId450" display="https://www.nyse.com/quote/XNYS:TSN" xr:uid="{F8D8B973-3B1C-4C4A-B1DD-E2313DBD0D63}"/>
+    <hyperlink ref="A452" r:id="rId451" display="https://www.nyse.com/quote/XNYS:TT" xr:uid="{F950DB78-F0F1-F54C-995D-DD333FF97EEA}"/>
+    <hyperlink ref="A453" r:id="rId452" display="https://www.nasdaq.com/market-activity/stocks/ttd" xr:uid="{B92C0FA0-114B-7343-BBDD-4C334AEE8A1C}"/>
+    <hyperlink ref="A454" r:id="rId453" display="https://www.nasdaq.com/market-activity/stocks/ttwo" xr:uid="{8BE81D07-A79D-974A-AF48-8428DF63B55E}"/>
+    <hyperlink ref="A455" r:id="rId454" display="https://www.nasdaq.com/market-activity/stocks/txn" xr:uid="{514A0DEB-5454-C448-B03F-CC4B5F983BB2}"/>
+    <hyperlink ref="A456" r:id="rId455" display="https://www.nyse.com/quote/XNYS:TXT" xr:uid="{3FF8A7BB-DD6B-0240-B382-44B01BD0BB2E}"/>
+    <hyperlink ref="A457" r:id="rId456" display="https://www.nyse.com/quote/XNYS:TYL" xr:uid="{8181ED24-2A5D-8145-A632-8685D25CF5E5}"/>
+    <hyperlink ref="A458" r:id="rId457" display="https://www.nasdaq.com/market-activity/stocks/ual" xr:uid="{9DF39175-306C-5C46-BD98-1133CB8462F8}"/>
+    <hyperlink ref="A459" r:id="rId458" display="https://www.nyse.com/quote/XNYS:UBER" xr:uid="{3509005C-1E6F-3F4E-8217-E3613AC9A93F}"/>
+    <hyperlink ref="A460" r:id="rId459" display="https://www.nyse.com/quote/XNYS:UDR" xr:uid="{151904FD-DD6F-C14D-AEFB-EB434B9AA24B}"/>
+    <hyperlink ref="A461" r:id="rId460" display="https://www.nyse.com/quote/XNYS:UHS" xr:uid="{C917854D-A741-B94A-B1C2-03C2A7909C14}"/>
+    <hyperlink ref="A462" r:id="rId461" display="https://www.nasdaq.com/market-activity/stocks/ulta" xr:uid="{299089E8-C8BD-1E42-9024-5486058140FA}"/>
+    <hyperlink ref="A463" r:id="rId462" display="https://www.nyse.com/quote/XNYS:UNH" xr:uid="{A1C206DE-9261-B845-93B4-9ABA0ADE6858}"/>
+    <hyperlink ref="A464" r:id="rId463" display="https://www.nyse.com/quote/XNYS:UNP" xr:uid="{035BDF58-CF4B-DE44-9A14-180A583C064F}"/>
+    <hyperlink ref="A465" r:id="rId464" display="https://www.nyse.com/quote/XNYS:UPS" xr:uid="{7F4CCF1F-47FA-584C-9721-511CB13DE421}"/>
+    <hyperlink ref="A466" r:id="rId465" display="https://www.nyse.com/quote/XNYS:URI" xr:uid="{CAA81F55-033A-4043-BC42-CA9DA73E7D18}"/>
+    <hyperlink ref="A467" r:id="rId466" display="https://www.nyse.com/quote/XNYS:USB" xr:uid="{7CACE059-0AFC-F74E-8646-A4FEC5CA65E6}"/>
+    <hyperlink ref="A468" r:id="rId467" display="https://www.nyse.com/quote/XNYS:V" xr:uid="{66E2069E-A0CC-D84C-B9CE-BF935B098497}"/>
+    <hyperlink ref="A469" r:id="rId468" display="https://www.nyse.com/quote/XNYS:VICI" xr:uid="{6D983B57-D687-2D4F-842E-556846218726}"/>
+    <hyperlink ref="A470" r:id="rId469" display="https://www.nyse.com/quote/XNYS:VLO" xr:uid="{AA9DB606-A74E-4545-ADFE-28D51336525C}"/>
+    <hyperlink ref="A471" r:id="rId470" display="https://www.nyse.com/quote/XNYS:VLTO" xr:uid="{FA599649-9AE5-2D46-9409-EEF26812BA58}"/>
+    <hyperlink ref="A472" r:id="rId471" display="https://www.nyse.com/quote/XNYS:VMC" xr:uid="{547C92E6-7C83-6140-8996-A7F95A8F8AD1}"/>
+    <hyperlink ref="A473" r:id="rId472" display="https://www.nasdaq.com/market-activity/stocks/vrsk" xr:uid="{FAE7572D-E22E-194C-B3F4-AAC47347EDF8}"/>
+    <hyperlink ref="A474" r:id="rId473" display="https://www.nasdaq.com/market-activity/stocks/vrsn" xr:uid="{D19C4FB1-79C2-2542-8C0B-1F2970198627}"/>
+    <hyperlink ref="A475" r:id="rId474" display="https://www.nasdaq.com/market-activity/stocks/vrtx" xr:uid="{CBEE8C1F-F62B-5040-B75A-2C6721FB8C9E}"/>
+    <hyperlink ref="A476" r:id="rId475" display="https://www.nyse.com/quote/XNYS:VST" xr:uid="{69EC6E5C-0119-0E44-A787-341AE60E41DE}"/>
+    <hyperlink ref="A477" r:id="rId476" display="https://www.nyse.com/quote/XNYS:VTR" xr:uid="{4D1C01A6-517C-9F4B-994E-20C9E79D56D6}"/>
+    <hyperlink ref="A478" r:id="rId477" display="https://www.nasdaq.com/market-activity/stocks/vtrs" xr:uid="{BF403597-40E8-5549-80BB-15C1971E17FA}"/>
+    <hyperlink ref="A479" r:id="rId478" display="https://www.nyse.com/quote/XNYS:VZ" xr:uid="{FFEC42CC-8A87-D041-BE64-248BE672BA39}"/>
+    <hyperlink ref="A480" r:id="rId479" display="https://www.nyse.com/quote/XNYS:WAB" xr:uid="{25FD60BD-1981-0C4F-A440-AAECE557BF1C}"/>
+    <hyperlink ref="A481" r:id="rId480" display="https://www.nyse.com/quote/XNYS:WAT" xr:uid="{F9A01575-C6E9-D148-8692-8CE5532183ED}"/>
+    <hyperlink ref="A482" r:id="rId481" display="https://www.nasdaq.com/market-activity/stocks/wbd" xr:uid="{9A855483-CDE6-6E42-BF09-E31D9378598F}"/>
+    <hyperlink ref="A483" r:id="rId482" display="https://www.nasdaq.com/market-activity/stocks/wday" xr:uid="{0B799925-7FE9-2945-94B0-16C9A8623ABE}"/>
+    <hyperlink ref="A484" r:id="rId483" display="https://www.nasdaq.com/market-activity/stocks/wdc" xr:uid="{086D84EB-FC9E-4440-990C-C68E24B33C92}"/>
+    <hyperlink ref="A485" r:id="rId484" display="https://www.nyse.com/quote/XNYS:WEC" xr:uid="{CD7D8F22-2C69-BF40-B1FC-0638A0EEE480}"/>
+    <hyperlink ref="A486" r:id="rId485" display="https://www.nyse.com/quote/XNYS:WELL" xr:uid="{869E26E2-6627-A946-A4C0-6B933AACDCB0}"/>
+    <hyperlink ref="A487" r:id="rId486" display="https://www.nyse.com/quote/XNYS:WFC" xr:uid="{C45B53AC-8DBF-A741-A3D7-64E59BB411D7}"/>
+    <hyperlink ref="A488" r:id="rId487" display="https://www.nyse.com/quote/XNYS:WM" xr:uid="{91263B3B-11D1-8744-B58D-1D002CC4132D}"/>
+    <hyperlink ref="A489" r:id="rId488" display="https://www.nyse.com/quote/XNYS:WMB" xr:uid="{0DC9BCC9-05CD-E042-A049-B7E97F9B50AB}"/>
+    <hyperlink ref="A490" r:id="rId489" display="https://www.nyse.com/quote/XNYS:WMT" xr:uid="{AE76A7D4-679D-E14F-BD69-7AE9377D70CE}"/>
+    <hyperlink ref="A491" r:id="rId490" display="https://www.nyse.com/quote/XNYS:WRB" xr:uid="{5C8B1965-E00E-1443-B5AF-320056228ECC}"/>
+    <hyperlink ref="A492" r:id="rId491" display="https://www.nyse.com/quote/XNYS:WSM" xr:uid="{C2A76827-202E-D043-919D-B74D9441D3F8}"/>
+    <hyperlink ref="A493" r:id="rId492" display="https://www.nyse.com/quote/XNYS:WST" xr:uid="{0B0C9A82-BEAA-7843-94A0-805BE457D650}"/>
+    <hyperlink ref="A494" r:id="rId493" display="https://www.nasdaq.com/market-activity/stocks/wtw" xr:uid="{D575DCD3-10C1-B44B-867A-E7561727D894}"/>
+    <hyperlink ref="A495" r:id="rId494" display="https://www.nyse.com/quote/XNYS:WY" xr:uid="{901E02A3-E66B-1C4F-A7D1-D1E5C98E79C1}"/>
+    <hyperlink ref="A496" r:id="rId495" display="https://www.nasdaq.com/market-activity/stocks/wynn" xr:uid="{84EAA1BA-4503-5B4A-8D1C-EB9A8B2AAF48}"/>
+    <hyperlink ref="A497" r:id="rId496" display="https://www.nasdaq.com/market-activity/stocks/xel" xr:uid="{3039DC1C-9293-5745-BDF6-E28813D326E3}"/>
+    <hyperlink ref="A498" r:id="rId497" display="https://www.nyse.com/quote/XNYS:XOM" xr:uid="{4381D83F-072F-D445-9970-7A5D080B3392}"/>
+    <hyperlink ref="A499" r:id="rId498" display="https://www.nyse.com/quote/XNYS:XYL" xr:uid="{7DBC3674-102C-FC4D-9524-3235BC4C07BF}"/>
+    <hyperlink ref="A500" r:id="rId499" display="https://www.nyse.com/quote/XNYS:XYZ" xr:uid="{CECAEB1E-7E6F-E04D-92AA-033A447D3422}"/>
+    <hyperlink ref="A501" r:id="rId500" display="https://www.nyse.com/quote/XNYS:YUM" xr:uid="{571A9ABA-21B7-4E4A-AD5B-6FAC7A4E1F8D}"/>
+    <hyperlink ref="A502" r:id="rId501" display="https://www.nyse.com/quote/XNYS:ZBH" xr:uid="{C55C9A5D-20B5-D548-8294-5BC41F389A3D}"/>
+    <hyperlink ref="A503" r:id="rId502" display="https://www.nasdaq.com/market-activity/stocks/zbra" xr:uid="{BE080523-C33B-4D49-8565-61BD021FE9BD}"/>
+    <hyperlink ref="A504" r:id="rId503" display="https://www.nyse.com/quote/XNYS:ZTS" xr:uid="{044421C5-379D-3240-BC5B-752DAFF94FD9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
